--- a/data/MY/Waypoints.xlsx
+++ b/data/MY/Waypoints.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Projects\VFR Waypoints\data\MY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998BD4CB-BE4F-4E1D-A931-63E2BB1AE7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC703721-8D5B-441C-A275-D7E7E36A93C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="21705" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="975" windowWidth="25470" windowHeight="20235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Google My Maps Output" sheetId="3" r:id="rId1"/>
@@ -1123,9 +1123,6 @@
     <t>East of Kg Sg Tiram</t>
   </si>
   <si>
-    <t>South Of Kg Semangar</t>
-  </si>
-  <si>
     <t>KAMPUNG</t>
   </si>
   <si>
@@ -2180,6 +2177,9 @@
   </si>
   <si>
     <t>BTGJAH</t>
+  </si>
+  <si>
+    <t>South of Kg Semangar</t>
   </si>
 </sst>
 </file>
@@ -2598,12 +2598,12 @@
         <v>Sungai Besar Stadium</v>
       </c>
       <c r="C2" s="2" cm="1">
-        <f t="array" ref="C2:C184">_xlfn.XLOOKUP('Source Data'!I1,'Source Data'!$E$1:$J$1,'Source Data'!$E$2:$J$184)</f>
-        <v>3.6744444444444442</v>
+        <f t="array" ref="C2:C184">ROUND(_xlfn.XLOOKUP('Source Data'!I1,'Source Data'!$E$1:$J$1,'Source Data'!$E$2:$J$184), 5)</f>
+        <v>3.6744400000000002</v>
       </c>
       <c r="D2" s="2" cm="1">
-        <f t="array" ref="D2:D184">_xlfn.XLOOKUP('Source Data'!J1,'Source Data'!$E$1:$J$1,'Source Data'!$E$2:$J$184)</f>
-        <v>100.98666666666666</v>
+        <f t="array" ref="D2:D184">ROUND(_xlfn.XLOOKUP('Source Data'!J1,'Source Data'!$E$1:$J$1,'Source Data'!$E$2:$J$184), 5)</f>
+        <v>100.98667</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2614,7 +2614,7 @@
         <v>Kuala Selangor Bridge</v>
       </c>
       <c r="C3" s="2">
-        <v>3.3405555555555555</v>
+        <v>3.34056</v>
       </c>
       <c r="D3" s="2">
         <v>101.2525</v>
@@ -2628,10 +2628,10 @@
         <v>Kapar Junction</v>
       </c>
       <c r="C4" s="2">
-        <v>3.1361111111111111</v>
+        <v>3.13611</v>
       </c>
       <c r="D4" s="2">
-        <v>101.37583333333333</v>
+        <v>101.37582999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2642,10 +2642,10 @@
         <v>Pulau Indah Bridge</v>
       </c>
       <c r="C5" s="2">
-        <v>3.0322222222222224</v>
+        <v>3.0322200000000001</v>
       </c>
       <c r="D5" s="2">
-        <v>101.3611111111111</v>
+        <v>101.36111</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2656,10 +2656,10 @@
         <v>Golf Course</v>
       </c>
       <c r="C6" s="2">
-        <v>2.7433333333333332</v>
+        <v>2.7433299999999998</v>
       </c>
       <c r="D6" s="2">
-        <v>101.44638888888889</v>
+        <v>101.44638999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2670,10 +2670,10 @@
         <v>Jetty Tanjung Sepat</v>
       </c>
       <c r="C7" s="2">
-        <v>2.6591666666666667</v>
+        <v>2.65917</v>
       </c>
       <c r="D7" s="2">
-        <v>101.55611111111111</v>
+        <v>101.55611</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2684,10 +2684,10 @@
         <v>Lighthouse</v>
       </c>
       <c r="C8" s="2">
-        <v>2.4069444444444446</v>
+        <v>2.4069400000000001</v>
       </c>
       <c r="D8" s="2">
-        <v>101.85194444444444</v>
+        <v>101.85194</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2698,10 +2698,10 @@
         <v>Slim River Hospital</v>
       </c>
       <c r="C9" s="2">
-        <v>3.8372222222222225</v>
+        <v>3.8372199999999999</v>
       </c>
       <c r="D9" s="2">
-        <v>101.40416666666667</v>
+        <v>101.40416999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2715,7 +2715,7 @@
         <v>3.6850000000000001</v>
       </c>
       <c r="D10" s="2">
-        <v>101.52388888888889</v>
+        <v>101.52388999999999</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2726,10 +2726,10 @@
         <v>Lafarge plant</v>
       </c>
       <c r="C11" s="2">
-        <v>3.3091666666666666</v>
+        <v>3.3091699999999999</v>
       </c>
       <c r="D11" s="2">
-        <v>101.57111111111111</v>
+        <v>101.57111</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2740,10 +2740,10 @@
         <v>Hindu Temple</v>
       </c>
       <c r="C12" s="2">
-        <v>3.2375000000000003</v>
+        <v>3.2374999999999998</v>
       </c>
       <c r="D12" s="2">
-        <v>101.68388888888889</v>
+        <v>101.68389000000001</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2754,10 +2754,10 @@
         <v>Smart Toll Plaza</v>
       </c>
       <c r="C13" s="2">
-        <v>3.108888888888889</v>
+        <v>3.1088900000000002</v>
       </c>
       <c r="D13" s="2">
-        <v>101.70222222222222</v>
+        <v>101.70222</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2768,10 +2768,10 @@
         <v>Stadium</v>
       </c>
       <c r="C14" s="2">
-        <v>2.9944444444444445</v>
+        <v>2.99444</v>
       </c>
       <c r="D14" s="2">
-        <v>101.78694444444444</v>
+        <v>101.78694</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2782,10 +2782,10 @@
         <v>Seremban Mosque</v>
       </c>
       <c r="C15" s="2">
-        <v>2.7219444444444445</v>
+        <v>2.72194</v>
       </c>
       <c r="D15" s="2">
-        <v>101.94222222222223</v>
+        <v>101.94222000000001</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2796,10 +2796,10 @@
         <v>Dataran Bentong</v>
       </c>
       <c r="C16" s="2">
-        <v>3.5291666666666668</v>
+        <v>3.5291700000000001</v>
       </c>
       <c r="D16" s="2">
-        <v>101.90472222222223</v>
+        <v>101.90472</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2810,10 +2810,10 @@
         <v>TNB Substation</v>
       </c>
       <c r="C17" s="2">
-        <v>2.5947222222222224</v>
+        <v>2.5947200000000001</v>
       </c>
       <c r="D17" s="2">
-        <v>101.96194444444444</v>
+        <v>101.96194</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2824,10 +2824,10 @@
         <v>Jelebu District Council</v>
       </c>
       <c r="C18" s="2">
-        <v>2.9408333333333334</v>
+        <v>2.9408300000000001</v>
       </c>
       <c r="D18" s="2">
-        <v>102.06944444444444</v>
+        <v>102.06944</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2838,10 +2838,10 @@
         <v>Menara TM</v>
       </c>
       <c r="C19" s="2">
-        <v>3.1158333333333332</v>
+        <v>3.1158299999999999</v>
       </c>
       <c r="D19" s="2">
-        <v>101.66555555555556</v>
+        <v>101.66556</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2852,10 +2852,10 @@
         <v>Tol Sungai Penchala</v>
       </c>
       <c r="C20" s="2">
-        <v>3.1774999999999998</v>
+        <v>3.1775000000000002</v>
       </c>
       <c r="D20" s="2">
-        <v>101.61944444444444</v>
+        <v>101.61944</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2866,10 +2866,10 @@
         <v>Puncak Perdana Interchange</v>
       </c>
       <c r="C21" s="2">
-        <v>3.1344444444444446</v>
+        <v>3.1344400000000001</v>
       </c>
       <c r="D21" s="2">
-        <v>101.49611111111111</v>
+        <v>101.49611</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2880,10 +2880,10 @@
         <v>Sultan Salahudin Abdul Aziz Mosque</v>
       </c>
       <c r="C22" s="2">
-        <v>3.0788888888888892</v>
+        <v>3.0788899999999999</v>
       </c>
       <c r="D22" s="2">
-        <v>101.52055555555556</v>
+        <v>101.52056</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2894,10 +2894,10 @@
         <v>Guthrie – LATAR Expressway Kuang Exit</v>
       </c>
       <c r="C23" s="2">
-        <v>3.2694444444444444</v>
+        <v>3.2694399999999999</v>
       </c>
       <c r="D23" s="2">
-        <v>101.54583333333333</v>
+        <v>101.54583</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2908,10 +2908,10 @@
         <v>Met Weather Radar</v>
       </c>
       <c r="C24" s="2">
-        <v>3.1447222222222222</v>
+        <v>3.14472</v>
       </c>
       <c r="D24" s="2">
-        <v>101.55861111111111</v>
+        <v>101.55861</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2922,10 +2922,10 @@
         <v>Titiwangsa Lake</v>
       </c>
       <c r="C25" s="2">
-        <v>3.1774999999999998</v>
+        <v>3.1775000000000002</v>
       </c>
       <c r="D25" s="2">
-        <v>101.70444444444445</v>
+        <v>101.70444000000001</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2936,10 +2936,10 @@
         <v>DUKE Jalan Kuching Interchange</v>
       </c>
       <c r="C26" s="2">
-        <v>3.1919444444444443</v>
+        <v>3.1919400000000002</v>
       </c>
       <c r="D26" s="2">
-        <v>101.66888888888889</v>
+        <v>101.66889</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2950,7 +2950,7 @@
         <v>UTM Mosque</v>
       </c>
       <c r="C27" s="2">
-        <v>1.5591666666666668</v>
+        <v>1.5591699999999999</v>
       </c>
       <c r="D27" s="2">
         <v>103.6375</v>
@@ -2964,10 +2964,10 @@
         <v>Benut</v>
       </c>
       <c r="C28" s="2">
-        <v>1.6441666666666666</v>
+        <v>1.6441699999999999</v>
       </c>
       <c r="D28" s="2">
-        <v>103.25944444444444</v>
+        <v>103.25944</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2981,7 +2981,7 @@
         <v>1.65</v>
       </c>
       <c r="D29" s="2">
-        <v>103.55499999999999</v>
+        <v>103.55500000000001</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2992,10 +2992,10 @@
         <v>East of Johor Bahru Airfield</v>
       </c>
       <c r="C30" s="2">
-        <v>1.6680555555555554</v>
+        <v>1.6680600000000001</v>
       </c>
       <c r="D30" s="2">
-        <v>103.71638888888889</v>
+        <v>103.71639</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3006,10 +3006,10 @@
         <v>Kota Tinggi Bridge</v>
       </c>
       <c r="C31" s="2">
-        <v>1.7288888888888889</v>
+        <v>1.72889</v>
       </c>
       <c r="D31" s="2">
-        <v>103.90166666666667</v>
+        <v>103.90167</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3020,10 +3020,10 @@
         <v>East of Kg Sg Tiram</v>
       </c>
       <c r="C32" s="2">
-        <v>1.5833333333333335</v>
+        <v>1.5833299999999999</v>
       </c>
       <c r="D32" s="2">
-        <v>103.91666666666667</v>
+        <v>103.91667</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3034,7 +3034,7 @@
         <v>East of Johor Bahru Town</v>
       </c>
       <c r="C33" s="2">
-        <v>1.5038888888888888</v>
+        <v>1.5038899999999999</v>
       </c>
       <c r="D33" s="2">
         <v>103.86499999999999</v>
@@ -3048,10 +3048,10 @@
         <v>Felda Ulu Tebrau</v>
       </c>
       <c r="C34" s="2">
-        <v>1.6308333333333334</v>
+        <v>1.63083</v>
       </c>
       <c r="D34" s="2">
-        <v>103.75277777777778</v>
+        <v>103.75278</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3062,10 +3062,10 @@
         <v>Tebrau City Mall</v>
       </c>
       <c r="C35" s="2">
-        <v>1.549722222222222</v>
+        <v>1.54972</v>
       </c>
       <c r="D35" s="2">
-        <v>103.79666666666667</v>
+        <v>103.79667000000001</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3073,13 +3073,13 @@
         <v>SOUTH_KG_SEMANGAR</v>
       </c>
       <c r="B36" t="str">
-        <v>South Of Kg Semangar</v>
+        <v>South of Kg Semangar</v>
       </c>
       <c r="C36" s="2">
-        <v>1.7416666666666667</v>
+        <v>1.7416700000000001</v>
       </c>
       <c r="D36" s="2">
-        <v>103.78333333333333</v>
+        <v>103.78333000000001</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3090,10 +3090,10 @@
         <v>Kampung Sedili Besar</v>
       </c>
       <c r="C37" s="2">
-        <v>1.9266666666666665</v>
+        <v>1.9266700000000001</v>
       </c>
       <c r="D37" s="2">
-        <v>104.11611111111111</v>
+        <v>104.11611000000001</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3104,10 +3104,10 @@
         <v>Simpang Renggam Town</v>
       </c>
       <c r="C38" s="2">
-        <v>1.8277777777777777</v>
+        <v>1.82778</v>
       </c>
       <c r="D38" s="2">
-        <v>103.30944444444444</v>
+        <v>103.30944</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3118,10 +3118,10 @@
         <v>Air Hitam</v>
       </c>
       <c r="C39" s="2">
-        <v>1.931111111111111</v>
+        <v>1.9311100000000001</v>
       </c>
       <c r="D39" s="2">
-        <v>103.17583333333334</v>
+        <v>103.17583</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3132,10 +3132,10 @@
         <v>Yong Peng</v>
       </c>
       <c r="C40" s="2">
-        <v>2.0172222222222222</v>
+        <v>2.01722</v>
       </c>
       <c r="D40" s="2">
-        <v>103.06305555555555</v>
+        <v>103.06305999999999</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3149,7 +3149,7 @@
         <v>1.4750000000000001</v>
       </c>
       <c r="D41" s="2">
-        <v>103.83166666666666</v>
+        <v>103.83167</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3160,10 +3160,10 @@
         <v>Tass Andrassy</v>
       </c>
       <c r="C42" s="2">
-        <v>4.3213888888888885</v>
+        <v>4.3213900000000001</v>
       </c>
       <c r="D42" s="2">
-        <v>118.02138888888889</v>
+        <v>118.02139</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3174,10 +3174,10 @@
         <v>Old Airport</v>
       </c>
       <c r="C43" s="2">
-        <v>4.2669444444444444</v>
+        <v>4.26694</v>
       </c>
       <c r="D43" s="2">
-        <v>117.88666666666667</v>
+        <v>117.88667</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3188,10 +3188,10 @@
         <v>Sebatik Island</v>
       </c>
       <c r="C44" s="2">
-        <v>4.2230555555555558</v>
+        <v>4.2230600000000003</v>
       </c>
       <c r="D44" s="2">
-        <v>117.78055555555555</v>
+        <v>117.78055999999999</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -3202,7 +3202,7 @@
         <v>Kalabakan</v>
       </c>
       <c r="C45" s="2">
-        <v>4.3988888888888891</v>
+        <v>4.3988899999999997</v>
       </c>
       <c r="D45" s="2">
         <v>117.495</v>
@@ -3216,10 +3216,10 @@
         <v>Balung</v>
       </c>
       <c r="C46" s="2">
-        <v>4.3644444444444437</v>
+        <v>4.3644400000000001</v>
       </c>
       <c r="D46" s="2">
-        <v>118.12777777777777</v>
+        <v>118.12778</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3230,10 +3230,10 @@
         <v>Kawa Hill</v>
       </c>
       <c r="C47" s="2">
-        <v>4.3938888888888892</v>
+        <v>4.3938899999999999</v>
       </c>
       <c r="D47" s="2">
-        <v>118.08694444444444</v>
+        <v>118.08694</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3244,10 +3244,10 @@
         <v>Mt Pyramid</v>
       </c>
       <c r="C48" s="2">
-        <v>4.4733333333333336</v>
+        <v>4.4733299999999998</v>
       </c>
       <c r="D48" s="2">
-        <v>118.06916666666666</v>
+        <v>118.06917</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3258,7 +3258,7 @@
         <v>Baturong</v>
       </c>
       <c r="C49" s="2">
-        <v>4.6994444444444445</v>
+        <v>4.6994400000000001</v>
       </c>
       <c r="D49" s="2">
         <v>118.0025</v>
@@ -3272,10 +3272,10 @@
         <v>Danum</v>
       </c>
       <c r="C50" s="2">
-        <v>4.8519444444444444</v>
+        <v>4.8519399999999999</v>
       </c>
       <c r="D50" s="2">
-        <v>117.78638888888889</v>
+        <v>117.78639</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3286,10 +3286,10 @@
         <v>Junction (49KM)</v>
       </c>
       <c r="C51" s="2">
-        <v>4.4266666666666667</v>
+        <v>4.4266699999999997</v>
       </c>
       <c r="D51" s="2">
-        <v>118.17833333333334</v>
+        <v>118.17833</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3300,10 +3300,10 @@
         <v>Kampung Aman</v>
       </c>
       <c r="C52" s="2">
-        <v>4.6036111111111104</v>
+        <v>4.6036099999999998</v>
       </c>
       <c r="D52" s="2">
-        <v>118.18972222222223</v>
+        <v>118.18971999999999</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3314,10 +3314,10 @@
         <v>Tanjung Batai</v>
       </c>
       <c r="C53" s="2">
-        <v>4.8386111111111108</v>
+        <v>4.8386100000000001</v>
       </c>
       <c r="D53" s="2">
-        <v>118.16777777777779</v>
+        <v>118.16777999999999</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -3328,10 +3328,10 @@
         <v>Saddle Hill</v>
       </c>
       <c r="C54" s="2">
-        <v>4.2988888888888885</v>
+        <v>4.2988900000000001</v>
       </c>
       <c r="D54" s="2">
-        <v>118.18555555555555</v>
+        <v>118.18556</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3342,10 +3342,10 @@
         <v>Nagos</v>
       </c>
       <c r="C55" s="2">
-        <v>4.3477777777777771</v>
+        <v>4.3477800000000002</v>
       </c>
       <c r="D55" s="2">
-        <v>118.39305555555556</v>
+        <v>118.39306000000001</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3356,10 +3356,10 @@
         <v>Semporna</v>
       </c>
       <c r="C56" s="2">
-        <v>4.4497222222222224</v>
+        <v>4.4497200000000001</v>
       </c>
       <c r="D56" s="2">
-        <v>118.59638888888888</v>
+        <v>118.59639</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3370,10 +3370,10 @@
         <v>Gaya Island</v>
       </c>
       <c r="C57" s="2">
-        <v>4.6222222222222227</v>
+        <v>4.6222200000000004</v>
       </c>
       <c r="D57" s="2">
-        <v>118.74027777777778</v>
+        <v>118.74028</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3384,10 +3384,10 @@
         <v>Sipadan Island</v>
       </c>
       <c r="C58" s="2">
-        <v>4.1405555555555562</v>
+        <v>4.1405599999999998</v>
       </c>
       <c r="D58" s="2">
-        <v>118.6438888888889</v>
+        <v>118.64389</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3398,10 +3398,10 @@
         <v>Bandar Indah (Road Junction)</v>
       </c>
       <c r="C59" s="2">
-        <v>5.855833333333333</v>
+        <v>5.8558300000000001</v>
       </c>
       <c r="D59" s="2">
-        <v>118.07222222222222</v>
+        <v>118.07222</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3412,10 +3412,10 @@
         <v>Kampong Tobanka</v>
       </c>
       <c r="C60" s="2">
-        <v>6.019166666666667</v>
+        <v>6.0191699999999999</v>
       </c>
       <c r="D60" s="2">
-        <v>118.03944444444444</v>
+        <v>118.03944</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3426,10 +3426,10 @@
         <v>Bai Island</v>
       </c>
       <c r="C61" s="2">
-        <v>5.7752777777777773</v>
+        <v>5.7752800000000004</v>
       </c>
       <c r="D61" s="2">
-        <v>118.10027777777778</v>
+        <v>118.10028</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3440,10 +3440,10 @@
         <v>Tanjung Bidadari</v>
       </c>
       <c r="C62" s="2">
-        <v>5.8244444444444445</v>
+        <v>5.8244400000000001</v>
       </c>
       <c r="D62" s="2">
-        <v>118.34916666666666</v>
+        <v>118.34917</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -3454,7 +3454,7 @@
         <v>Kuala Kinabatangan Besar</v>
       </c>
       <c r="C63" s="2">
-        <v>5.642777777777777</v>
+        <v>5.6427800000000001</v>
       </c>
       <c r="D63" s="2">
         <v>118.6125</v>
@@ -3468,10 +3468,10 @@
         <v>Kampung Bilit</v>
       </c>
       <c r="C64" s="2">
-        <v>5.4975000000000005</v>
+        <v>5.4974999999999996</v>
       </c>
       <c r="D64" s="2">
-        <v>118.20805555555556</v>
+        <v>118.20806</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3482,10 +3482,10 @@
         <v>Sungai Seguntor</v>
       </c>
       <c r="C65" s="2">
-        <v>5.8066666666666666</v>
+        <v>5.8066700000000004</v>
       </c>
       <c r="D65" s="2">
-        <v>117.99361111111111</v>
+        <v>117.99361</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -3496,7 +3496,7 @@
         <v>Kota Kinabatangan</v>
       </c>
       <c r="C66" s="2">
-        <v>5.5888888888888886</v>
+        <v>5.5888900000000001</v>
       </c>
       <c r="D66" s="2">
         <v>117.845</v>
@@ -3510,10 +3510,10 @@
         <v>Kampung Kuala Lokan</v>
       </c>
       <c r="C67" s="2">
-        <v>5.4369444444444444</v>
+        <v>5.4369399999999999</v>
       </c>
       <c r="D67" s="2">
-        <v>117.74861111111112</v>
+        <v>117.74861</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -3524,10 +3524,10 @@
         <v>Mile 32 Rd Junction</v>
       </c>
       <c r="C68" s="2">
-        <v>5.7577777777777781</v>
+        <v>5.7577800000000003</v>
       </c>
       <c r="D68" s="2">
-        <v>117.75861111111111</v>
+        <v>117.75861</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3541,7 +3541,7 @@
         <v>5.6275000000000004</v>
       </c>
       <c r="D69" s="2">
-        <v>117.13055555555555</v>
+        <v>117.13056</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -3552,10 +3552,10 @@
         <v>Kampung GumGum Laut</v>
       </c>
       <c r="C70" s="2">
-        <v>5.969444444444445</v>
+        <v>5.9694399999999996</v>
       </c>
       <c r="D70" s="2">
-        <v>117.90972222222223</v>
+        <v>117.90971999999999</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -3566,10 +3566,10 @@
         <v>Kampung Semawang</v>
       </c>
       <c r="C71" s="2">
-        <v>5.9197222222222221</v>
+        <v>5.9197199999999999</v>
       </c>
       <c r="D71" s="2">
-        <v>117.76222222222222</v>
+        <v>117.76222</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -3583,7 +3583,7 @@
         <v>5.8949999999999996</v>
       </c>
       <c r="D72" s="2">
-        <v>117.55694444444444</v>
+        <v>117.55694</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -3594,10 +3594,10 @@
         <v>Kenawi Island</v>
       </c>
       <c r="C73" s="2">
-        <v>5.9883333333333333</v>
+        <v>5.9883300000000004</v>
       </c>
       <c r="D73" s="2">
-        <v>117.70194444444445</v>
+        <v>117.70193999999999</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -3608,10 +3608,10 @@
         <v>Kampung Sungai-Sungai</v>
       </c>
       <c r="C74" s="2">
-        <v>6.2508333333333335</v>
+        <v>6.2508299999999997</v>
       </c>
       <c r="D74" s="2">
-        <v>117.35111111111111</v>
+        <v>117.35111000000001</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3622,10 +3622,10 @@
         <v>Kampung Terusan</v>
       </c>
       <c r="C75" s="2">
-        <v>6.4258333333333333</v>
+        <v>6.4258300000000004</v>
       </c>
       <c r="D75" s="2">
-        <v>117.68722222222223</v>
+        <v>117.68722</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3636,10 +3636,10 @@
         <v>Selingan Island</v>
       </c>
       <c r="C76" s="2">
-        <v>6.1741666666666672</v>
+        <v>6.1741700000000002</v>
       </c>
       <c r="D76" s="2">
-        <v>118.06055555555555</v>
+        <v>118.06056</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3653,7 +3653,7 @@
         <v>6.5</v>
       </c>
       <c r="D77" s="2">
-        <v>117.91666666666667</v>
+        <v>117.91667</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3664,10 +3664,10 @@
         <v>South of Berhala Island</v>
       </c>
       <c r="C78" s="2">
-        <v>5.8641666666666667</v>
+        <v>5.8641699999999997</v>
       </c>
       <c r="D78" s="2">
-        <v>118.14833333333334</v>
+        <v>118.14833</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -3678,7 +3678,7 @@
         <v>Luang Manis</v>
       </c>
       <c r="C79" s="2">
-        <v>5.666666666666667</v>
+        <v>5.6666699999999999</v>
       </c>
       <c r="D79" s="2">
         <v>117.655</v>
@@ -3692,10 +3692,10 @@
         <v>Pamaguan Primary School</v>
       </c>
       <c r="C80" s="2">
-        <v>5.9575000000000005</v>
+        <v>5.9574999999999996</v>
       </c>
       <c r="D80" s="2">
-        <v>118.06444444444445</v>
+        <v>118.06444</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -3706,10 +3706,10 @@
         <v>Port Weld</v>
       </c>
       <c r="C81" s="2">
-        <v>4.8380555555555551</v>
+        <v>4.8380599999999996</v>
       </c>
       <c r="D81" s="2">
-        <v>100.62583333333333</v>
+        <v>100.62582999999999</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3720,10 +3720,10 @@
         <v>Tanjung Piandang</v>
       </c>
       <c r="C82" s="2">
-        <v>5.0880555555555551</v>
+        <v>5.0880599999999996</v>
       </c>
       <c r="D82" s="2">
-        <v>100.36055555555555</v>
+        <v>100.36056000000001</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3734,10 +3734,10 @@
         <v>South of Pulau Aman</v>
       </c>
       <c r="C83" s="2">
-        <v>5.2586111111111107</v>
+        <v>5.25861</v>
       </c>
       <c r="D83" s="2">
-        <v>100.38416666666667</v>
+        <v>100.38417</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3748,10 +3748,10 @@
         <v>Kedah Peak West</v>
       </c>
       <c r="C84" s="2">
-        <v>5.743611111111111</v>
+        <v>5.7436100000000003</v>
       </c>
       <c r="D84" s="2">
-        <v>100.35694444444444</v>
+        <v>100.35693999999999</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3765,7 +3765,7 @@
         <v>5.5774999999999997</v>
       </c>
       <c r="D85" s="2">
-        <v>100.33583333333333</v>
+        <v>100.33583</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -3776,10 +3776,10 @@
         <v>North of George Town</v>
       </c>
       <c r="C86" s="2">
-        <v>5.464722222222222</v>
+        <v>5.4647199999999998</v>
       </c>
       <c r="D86" s="2">
-        <v>100.30722222222222</v>
+        <v>100.30722</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -3804,10 +3804,10 @@
         <v>Pulau Sulug</v>
       </c>
       <c r="C88" s="2">
-        <v>5.9611111111111112</v>
+        <v>5.9611099999999997</v>
       </c>
       <c r="D88" s="2">
-        <v>115.99166666666667</v>
+        <v>115.99167</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -3821,7 +3821,7 @@
         <v>5.75</v>
       </c>
       <c r="D89" s="2">
-        <v>115.65833333333335</v>
+        <v>115.65833000000001</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3832,7 +3832,7 @@
         <v>Kuala Penyu</v>
       </c>
       <c r="C90" s="2">
-        <v>5.5666666666666664</v>
+        <v>5.5666700000000002</v>
       </c>
       <c r="D90" s="2">
         <v>115.6</v>
@@ -3846,10 +3846,10 @@
         <v>Bongawan</v>
       </c>
       <c r="C91" s="2">
-        <v>5.5388888888888888</v>
+        <v>5.5388900000000003</v>
       </c>
       <c r="D91" s="2">
-        <v>115.85777777777777</v>
+        <v>115.85778000000001</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -3863,7 +3863,7 @@
         <v>5.7</v>
       </c>
       <c r="D92" s="2">
-        <v>116.01666666666667</v>
+        <v>116.01667</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -3874,7 +3874,7 @@
         <v>East of Kawang</v>
       </c>
       <c r="C93" s="2">
-        <v>5.7666666666666666</v>
+        <v>5.7666700000000004</v>
       </c>
       <c r="D93" s="2">
         <v>116.05</v>
@@ -3888,10 +3888,10 @@
         <v>East of Kinarut Town</v>
       </c>
       <c r="C94" s="2">
-        <v>5.8183333333333334</v>
+        <v>5.8183299999999996</v>
       </c>
       <c r="D94" s="2">
-        <v>116.07194444444444</v>
+        <v>116.07194</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -3902,10 +3902,10 @@
         <v>Kepayan</v>
       </c>
       <c r="C95" s="2">
-        <v>5.9258333333333333</v>
+        <v>5.9258300000000004</v>
       </c>
       <c r="D95" s="2">
-        <v>116.05833333333334</v>
+        <v>116.05833</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -3916,10 +3916,10 @@
         <v>East of Inanam Town</v>
       </c>
       <c r="C96" s="2">
-        <v>5.9955555555555557</v>
+        <v>5.9955600000000002</v>
       </c>
       <c r="D96" s="2">
-        <v>116.15138888888889</v>
+        <v>116.15139000000001</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -3930,10 +3930,10 @@
         <v>East of Telipok</v>
       </c>
       <c r="C97" s="2">
-        <v>6.1083333333333334</v>
+        <v>6.1083299999999996</v>
       </c>
       <c r="D97" s="2">
-        <v>116.20833333333334</v>
+        <v>116.20833</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -3944,10 +3944,10 @@
         <v>Kampung Kiulu</v>
       </c>
       <c r="C98" s="2">
-        <v>6.0616666666666665</v>
+        <v>6.0616700000000003</v>
       </c>
       <c r="D98" s="2">
-        <v>116.28305555555555</v>
+        <v>116.28306000000001</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -3961,7 +3961,7 @@
         <v>6.0250000000000004</v>
       </c>
       <c r="D99" s="2">
-        <v>116.4538888888889</v>
+        <v>116.45389</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -3972,10 +3972,10 @@
         <v>Ranau</v>
       </c>
       <c r="C100" s="2">
-        <v>5.9583333333333339</v>
+        <v>5.9583300000000001</v>
       </c>
       <c r="D100" s="2">
-        <v>116.67500000000001</v>
+        <v>116.675</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -3986,10 +3986,10 @@
         <v>West of Hill 1040</v>
       </c>
       <c r="C101" s="2">
-        <v>6.1097222222222216</v>
+        <v>6.1097200000000003</v>
       </c>
       <c r="D101" s="2">
-        <v>116.07694444444444</v>
+        <v>116.07693999999999</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -4003,7 +4003,7 @@
         <v>6.16</v>
       </c>
       <c r="D102" s="2">
-        <v>116.14166666666668</v>
+        <v>116.14167</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -4014,10 +4014,10 @@
         <v>Kota Belud</v>
       </c>
       <c r="C103" s="2">
-        <v>6.3466666666666667</v>
+        <v>6.3466699999999996</v>
       </c>
       <c r="D103" s="2">
-        <v>116.39777777777779</v>
+        <v>116.39778</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -4028,10 +4028,10 @@
         <v>Terendak</v>
       </c>
       <c r="C104" s="2">
-        <v>2.2922222222222222</v>
+        <v>2.2922199999999999</v>
       </c>
       <c r="D104" s="2">
-        <v>102.0911111111111</v>
+        <v>102.09111</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -4042,7 +4042,7 @@
         <v>Rembia</v>
       </c>
       <c r="C105" s="2">
-        <v>2.2822222222222224</v>
+        <v>2.2822200000000001</v>
       </c>
       <c r="D105" s="2">
         <v>102.215</v>
@@ -4056,7 +4056,7 @@
         <v>Tampin</v>
       </c>
       <c r="C106" s="2">
-        <v>2.4705555555555558</v>
+        <v>2.4705599999999999</v>
       </c>
       <c r="D106" s="2">
         <v>102.23</v>
@@ -4073,7 +4073,7 @@
         <v>2.29</v>
       </c>
       <c r="D107" s="2">
-        <v>102.47777777777777</v>
+        <v>102.47778</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -4084,10 +4084,10 @@
         <v>Bt Beruang</v>
       </c>
       <c r="C108" s="2">
-        <v>2.2422222222222223</v>
+        <v>2.2422200000000001</v>
       </c>
       <c r="D108" s="2">
-        <v>102.30472222222222</v>
+        <v>102.30472</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -4098,10 +4098,10 @@
         <v>Umbai</v>
       </c>
       <c r="C109" s="2">
-        <v>2.1555555555555554</v>
+        <v>2.1555599999999999</v>
       </c>
       <c r="D109" s="2">
-        <v>102.34444444444443</v>
+        <v>102.34444000000001</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -4126,7 +4126,7 @@
         <v>Muar</v>
       </c>
       <c r="C111" s="2">
-        <v>2.0616666666666665</v>
+        <v>2.0616699999999999</v>
       </c>
       <c r="D111" s="2">
         <v>102.565</v>
@@ -4140,10 +4140,10 @@
         <v>Tangkak</v>
       </c>
       <c r="C112" s="2">
-        <v>2.2722222222222221</v>
+        <v>2.2722199999999999</v>
       </c>
       <c r="D112" s="2">
-        <v>102.54444444444444</v>
+        <v>102.54443999999999</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -4168,10 +4168,10 @@
         <v>Penarik</v>
       </c>
       <c r="C114">
-        <v>5.5958333333333332</v>
+        <v>5.5958300000000003</v>
       </c>
       <c r="D114">
-        <v>102.8261111111111</v>
+        <v>102.82611</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -4182,10 +4182,10 @@
         <v>Bandar Permaisuri</v>
       </c>
       <c r="C115">
-        <v>5.5113888888888889</v>
+        <v>5.5113899999999996</v>
       </c>
       <c r="D115">
-        <v>102.74555555555555</v>
+        <v>102.74556</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -4196,10 +4196,10 @@
         <v>Kampung Merang</v>
       </c>
       <c r="C116">
-        <v>5.5194444444444448</v>
+        <v>5.5194400000000003</v>
       </c>
       <c r="D116">
-        <v>102.95944444444444</v>
+        <v>102.95944</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -4210,10 +4210,10 @@
         <v>Batu Rakit</v>
       </c>
       <c r="C117">
-        <v>5.4444444444444446</v>
+        <v>5.4444400000000002</v>
       </c>
       <c r="D117">
-        <v>103.04861111111111</v>
+        <v>103.04861</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -4224,10 +4224,10 @@
         <v>Kampung Chenering</v>
       </c>
       <c r="C118">
-        <v>5.2716666666666665</v>
+        <v>5.2716700000000003</v>
       </c>
       <c r="D118">
-        <v>103.17638888888889</v>
+        <v>103.17639</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -4238,10 +4238,10 @@
         <v>Marang</v>
       </c>
       <c r="C119">
-        <v>5.1888888888888891</v>
+        <v>5.1888899999999998</v>
       </c>
       <c r="D119">
-        <v>103.22055555555556</v>
+        <v>103.22056000000001</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -4252,10 +4252,10 @@
         <v>Kuala Berang</v>
       </c>
       <c r="C120">
-        <v>5.0619444444444444</v>
+        <v>5.0619399999999999</v>
       </c>
       <c r="D120">
-        <v>103.00916666666667</v>
+        <v>103.00917</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -4266,10 +4266,10 @@
         <v>Tasik Kenyir</v>
       </c>
       <c r="C121">
-        <v>5.0836111111111109</v>
+        <v>5.0836100000000002</v>
       </c>
       <c r="D121">
-        <v>102.81138888888889</v>
+        <v>102.81139</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -4280,10 +4280,10 @@
         <v>Penerak</v>
       </c>
       <c r="C122">
-        <v>4.9683333333333337</v>
+        <v>4.9683299999999999</v>
       </c>
       <c r="D122">
-        <v>103.32055555555556</v>
+        <v>103.32056</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -4294,10 +4294,10 @@
         <v>Nenasi River Mouth</v>
       </c>
       <c r="C123">
-        <v>3.0736111111111115</v>
+        <v>3.07361</v>
       </c>
       <c r="D123">
-        <v>103.4388888888889</v>
+        <v>103.43889</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -4308,10 +4308,10 @@
         <v>Pekan Bridge</v>
       </c>
       <c r="C124">
-        <v>3.5055555555555555</v>
+        <v>3.50556</v>
       </c>
       <c r="D124">
-        <v>103.39111111111112</v>
+        <v>103.39111</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -4322,7 +4322,7 @@
         <v>Tower 188</v>
       </c>
       <c r="C125">
-        <v>3.8038888888888889</v>
+        <v>3.80389</v>
       </c>
       <c r="D125">
         <v>103.3275</v>
@@ -4336,10 +4336,10 @@
         <v>Juantan Port</v>
       </c>
       <c r="C126">
-        <v>3.9833333333333334</v>
+        <v>3.98333</v>
       </c>
       <c r="D126">
-        <v>103.41666666666667</v>
+        <v>103.41667</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -4350,10 +4350,10 @@
         <v>Kuala Kemaman</v>
       </c>
       <c r="C127">
-        <v>4.2361111111111116</v>
+        <v>4.23611</v>
       </c>
       <c r="D127">
-        <v>103.44861111111112</v>
+        <v>103.44861</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -4364,10 +4364,10 @@
         <v>Highway Y-Junction</v>
       </c>
       <c r="C128">
-        <v>3.5811111111111109</v>
+        <v>3.5811099999999998</v>
       </c>
       <c r="D128">
-        <v>102.76527777777778</v>
+        <v>102.76528</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -4378,10 +4378,10 @@
         <v>IIUM Gambang Complex</v>
       </c>
       <c r="C129">
-        <v>3.7233333333333336</v>
+        <v>3.7233299999999998</v>
       </c>
       <c r="D129">
-        <v>103.05861111111111</v>
+        <v>103.05861</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -4392,10 +4392,10 @@
         <v>Lepar Bridge</v>
       </c>
       <c r="C130">
-        <v>3.4916666666666667</v>
+        <v>3.4916700000000001</v>
       </c>
       <c r="D130">
-        <v>103.09555555555555</v>
+        <v>103.09556000000001</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -4406,7 +4406,7 @@
         <v>4-junction Flyover Kuantan-Segaman Highway</v>
       </c>
       <c r="C131">
-        <v>3.0722222222222224</v>
+        <v>3.0722200000000002</v>
       </c>
       <c r="D131">
         <v>103.07</v>
@@ -4420,10 +4420,10 @@
         <v>Football Field Sg Lembing</v>
       </c>
       <c r="C132">
-        <v>3.9152777777777779</v>
+        <v>3.9152800000000001</v>
       </c>
       <c r="D132">
-        <v>103.03388888888888</v>
+        <v>103.03389</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -4434,10 +4434,10 @@
         <v>Lundu</v>
       </c>
       <c r="C133">
-        <v>1.6774999999999998</v>
+        <v>1.6775</v>
       </c>
       <c r="D133">
-        <v>109.85361111111111</v>
+        <v>109.85361</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -4448,10 +4448,10 @@
         <v>Kampung Rambungan</v>
       </c>
       <c r="C134">
-        <v>1.6919444444444445</v>
+        <v>1.69194</v>
       </c>
       <c r="D134">
-        <v>110.12472222222222</v>
+        <v>110.12472</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -4462,10 +4462,10 @@
         <v>Kampung Stinggang</v>
       </c>
       <c r="C135">
-        <v>1.4813888888888891</v>
+        <v>1.48139</v>
       </c>
       <c r="D135">
-        <v>110.03833333333333</v>
+        <v>110.03833</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -4476,10 +4476,10 @@
         <v>Muara Tebas</v>
       </c>
       <c r="C136">
-        <v>1.6411111111111112</v>
+        <v>1.6411100000000001</v>
       </c>
       <c r="D136">
-        <v>110.48138888888889</v>
+        <v>110.48139</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -4490,10 +4490,10 @@
         <v>Abeam Semera</v>
       </c>
       <c r="C137">
-        <v>1.5522222222222222</v>
+        <v>1.5522199999999999</v>
       </c>
       <c r="D137">
-        <v>110.67027777777778</v>
+        <v>110.67028000000001</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -4504,10 +4504,10 @@
         <v>Tebedu</v>
       </c>
       <c r="C138">
-        <v>1.0166666666666666</v>
+        <v>1.01667</v>
       </c>
       <c r="D138">
-        <v>110.35749999999999</v>
+        <v>110.3575</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -4518,10 +4518,10 @@
         <v>Serian</v>
       </c>
       <c r="C139">
-        <v>1.1697222222222223</v>
+        <v>1.1697200000000001</v>
       </c>
       <c r="D139">
-        <v>110.56722222222221</v>
+        <v>110.56722000000001</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -4532,10 +4532,10 @@
         <v>Simunjan</v>
       </c>
       <c r="C140">
-        <v>1.3911111111111112</v>
+        <v>1.3911100000000001</v>
       </c>
       <c r="D140">
-        <v>110.74944444444445</v>
+        <v>110.74944000000001</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -4546,10 +4546,10 @@
         <v>Kampung Triso</v>
       </c>
       <c r="C141">
-        <v>1.5272222222222223</v>
+        <v>1.52722</v>
       </c>
       <c r="D141">
-        <v>111.00361111111111</v>
+        <v>111.00360999999999</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -4563,7 +4563,7 @@
         <v>1.4075</v>
       </c>
       <c r="D142">
-        <v>110.36333333333333</v>
+        <v>110.36333</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -4574,10 +4574,10 @@
         <v>Bukit Siol</v>
       </c>
       <c r="C143">
-        <v>1.5788888888888888</v>
+        <v>1.5788899999999999</v>
       </c>
       <c r="D143">
-        <v>110.35361111111111</v>
+        <v>110.35361</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -4588,10 +4588,10 @@
         <v>Abeam Narub</v>
       </c>
       <c r="C144">
-        <v>2.6433333333333331</v>
+        <v>2.6433300000000002</v>
       </c>
       <c r="D144">
-        <v>112.07666666666667</v>
+        <v>112.07666999999999</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -4602,10 +4602,10 @@
         <v>Nanga Tamin</v>
       </c>
       <c r="C145">
-        <v>2.5083333333333333</v>
+        <v>2.5083299999999999</v>
       </c>
       <c r="D145">
-        <v>112.07166666666666</v>
+        <v>112.07167</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -4616,10 +4616,10 @@
         <v>Lassa River</v>
       </c>
       <c r="C146">
-        <v>2.4683333333333333</v>
+        <v>2.4683299999999999</v>
       </c>
       <c r="D146">
-        <v>111.60833333333333</v>
+        <v>111.60833</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -4630,10 +4630,10 @@
         <v>Selangau</v>
       </c>
       <c r="C147">
-        <v>2.5233333333333334</v>
+        <v>2.5233300000000001</v>
       </c>
       <c r="D147">
-        <v>112.31833333333333</v>
+        <v>112.31833</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -4644,10 +4644,10 @@
         <v>Stapang</v>
       </c>
       <c r="C148">
-        <v>2.3983333333333334</v>
+        <v>2.3983300000000001</v>
       </c>
       <c r="D148">
-        <v>112.13166666666666</v>
+        <v>112.13167</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -4675,7 +4675,7 @@
         <v>2.19</v>
       </c>
       <c r="D150">
-        <v>111.93666666666667</v>
+        <v>111.93667000000001</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -4686,10 +4686,10 @@
         <v>Meruan</v>
       </c>
       <c r="C151">
-        <v>2.3016666666666663</v>
+        <v>2.3016700000000001</v>
       </c>
       <c r="D151">
-        <v>112.05666666666666</v>
+        <v>112.05667</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -4703,7 +4703,7 @@
         <v>2.0649999999999999</v>
       </c>
       <c r="D152">
-        <v>111.76666666666667</v>
+        <v>111.76667</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -4714,10 +4714,10 @@
         <v>Pakan Road</v>
       </c>
       <c r="C153">
-        <v>1.9816666666666667</v>
+        <v>1.98167</v>
       </c>
       <c r="D153">
-        <v>111.64833333333334</v>
+        <v>111.64833</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -4728,7 +4728,7 @@
         <v>Durin Town</v>
       </c>
       <c r="C154">
-        <v>2.1333333333333333</v>
+        <v>2.1333299999999999</v>
       </c>
       <c r="D154">
         <v>111.97</v>
@@ -4745,7 +4745,7 @@
         <v>2.0950000000000002</v>
       </c>
       <c r="D155">
-        <v>112.15166666666667</v>
+        <v>112.15167</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -4756,10 +4756,10 @@
         <v>Penarik</v>
       </c>
       <c r="C156">
-        <v>5.5952777777777776</v>
+        <v>5.5952799999999998</v>
       </c>
       <c r="D156">
-        <v>102.80666666666666</v>
+        <v>102.80667</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -4770,10 +4770,10 @@
         <v>Kampung Setiu Lama</v>
       </c>
       <c r="C157">
-        <v>5.6813888888888888</v>
+        <v>5.6813900000000004</v>
       </c>
       <c r="D157">
-        <v>102.71277777777777</v>
+        <v>102.71278</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -4787,7 +4787,7 @@
         <v>5.7374999999999998</v>
       </c>
       <c r="D158">
-        <v>102.65083333333334</v>
+        <v>102.65083</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -4798,10 +4798,10 @@
         <v>Pulau Ru</v>
       </c>
       <c r="C159">
-        <v>5.8308333333333335</v>
+        <v>5.8308299999999997</v>
       </c>
       <c r="D159">
-        <v>102.60638888888889</v>
+        <v>102.60639</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -4812,10 +4812,10 @@
         <v>Kampung Besut</v>
       </c>
       <c r="C160">
-        <v>5.8319444444444439</v>
+        <v>5.8319400000000003</v>
       </c>
       <c r="D160">
-        <v>102.54861111111111</v>
+        <v>102.54861</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -4826,7 +4826,7 @@
         <v>Kampung Tok Bali</v>
       </c>
       <c r="C161">
-        <v>5.8844444444444441</v>
+        <v>5.8844399999999997</v>
       </c>
       <c r="D161">
         <v>102.485</v>
@@ -4840,10 +4840,10 @@
         <v>Kampung Kandis</v>
       </c>
       <c r="C162">
-        <v>5.9480555555555554</v>
+        <v>5.9480599999999999</v>
       </c>
       <c r="D162">
-        <v>102.44277777777778</v>
+        <v>102.44278</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -4854,7 +4854,7 @@
         <v>Bachok</v>
       </c>
       <c r="C163">
-        <v>6.0649999999999995</v>
+        <v>6.0650000000000004</v>
       </c>
       <c r="D163">
         <v>102.39</v>
@@ -4868,10 +4868,10 @@
         <v>Kota Bharu Town</v>
       </c>
       <c r="C164">
-        <v>6.1319444444444438</v>
+        <v>6.1319400000000002</v>
       </c>
       <c r="D164">
-        <v>102.23194444444445</v>
+        <v>102.23193999999999</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -4882,10 +4882,10 @@
         <v>Kuala Krai</v>
       </c>
       <c r="C165">
-        <v>5.5991666666666662</v>
+        <v>5.59917</v>
       </c>
       <c r="D165">
-        <v>102.23666666666666</v>
+        <v>102.23667</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -4896,10 +4896,10 @@
         <v>Tanah Merah</v>
       </c>
       <c r="C166">
-        <v>5.7747222222222225</v>
+        <v>5.7747200000000003</v>
       </c>
       <c r="D166">
-        <v>102.12666666666667</v>
+        <v>102.12667</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -4910,10 +4910,10 @@
         <v>Bukit Melintang</v>
       </c>
       <c r="C167">
-        <v>5.7013888888888893</v>
+        <v>5.70139</v>
       </c>
       <c r="D167">
-        <v>101.72361111111111</v>
+        <v>101.72360999999999</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -4924,10 +4924,10 @@
         <v>Jeli</v>
       </c>
       <c r="C168">
-        <v>5.7013888888888893</v>
+        <v>5.70139</v>
       </c>
       <c r="D168">
-        <v>101.82805555555555</v>
+        <v>101.82805999999999</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -4952,10 +4952,10 @@
         <v>Pulau Timun</v>
       </c>
       <c r="C170">
-        <v>6.3130555555555556</v>
+        <v>6.3130600000000001</v>
       </c>
       <c r="D170">
-        <v>99.914722222222224</v>
+        <v>99.914720000000003</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -4966,10 +4966,10 @@
         <v>Abeam Pulau Tuba</v>
       </c>
       <c r="C171">
-        <v>6.2672222222222222</v>
+        <v>6.26722</v>
       </c>
       <c r="D171">
-        <v>99.888611111111118</v>
+        <v>99.88861</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -4994,10 +4994,10 @@
         <v>Kuala Perlis</v>
       </c>
       <c r="C173">
-        <v>6.3986111111111112</v>
+        <v>6.3986099999999997</v>
       </c>
       <c r="D173">
-        <v>100.1388888888889</v>
+        <v>100.13889</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -5011,7 +5011,7 @@
         <v>6.2374999999999998</v>
       </c>
       <c r="D174">
-        <v>100.24833333333333</v>
+        <v>100.24833</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -5036,10 +5036,10 @@
         <v>Simpang Empat</v>
       </c>
       <c r="C176">
-        <v>6.0241666666666669</v>
+        <v>6.0241699999999998</v>
       </c>
       <c r="D176">
-        <v>100.38194444444444</v>
+        <v>100.38194</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -5050,10 +5050,10 @@
         <v>Kota Sarang Semut</v>
       </c>
       <c r="C177">
-        <v>5.9744444444444449</v>
+        <v>5.9744400000000004</v>
       </c>
       <c r="D177">
-        <v>100.39972222222222</v>
+        <v>100.39972</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -5064,10 +5064,10 @@
         <v>Batu Hampar</v>
       </c>
       <c r="C178">
-        <v>4.5322222222222219</v>
+        <v>4.5322199999999997</v>
       </c>
       <c r="D178">
-        <v>100.71277777777777</v>
+        <v>100.71278</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -5078,10 +5078,10 @@
         <v>Parit</v>
       </c>
       <c r="C179">
-        <v>4.4830555555555556</v>
+        <v>4.48306</v>
       </c>
       <c r="D179">
-        <v>100.91083333333334</v>
+        <v>100.91083</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -5092,10 +5092,10 @@
         <v>Batu Gajah</v>
       </c>
       <c r="C180">
-        <v>4.469444444444445</v>
+        <v>4.4694399999999996</v>
       </c>
       <c r="D180">
-        <v>101.0436111111111</v>
+        <v>101.04361</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -5109,7 +5109,7 @@
         <v>4.46</v>
       </c>
       <c r="D181">
-        <v>101.16000000000001</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -5148,10 +5148,10 @@
         <v>Bidor</v>
       </c>
       <c r="C184">
-        <v>4.1133333333333333</v>
+        <v>4.1133300000000004</v>
       </c>
       <c r="D184">
-        <v>101.28583333333333</v>
+        <v>101.28583</v>
       </c>
     </row>
   </sheetData>
@@ -5173,22 +5173,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5197,19 +5197,19 @@
         <v>SGBESR</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D2" t="str" cm="1">
         <f t="array" ref="D2:D184">_xlfn.XLOOKUP('Source Data'!H1,'Source Data'!$F$1:$J$1,'Source Data'!$F$2:$J$184)</f>
         <v>Sungai Besar Stadium</v>
       </c>
       <c r="E2" s="5" cm="1">
-        <f t="array" ref="E2:E184">_xlfn.XLOOKUP('Source Data'!I1,'Source Data'!$F$1:$J$1,'Source Data'!$F$2:$J$184)</f>
-        <v>3.6744444444444442</v>
+        <f t="array" ref="E2:E184">ROUND(_xlfn.XLOOKUP('Source Data'!I1,'Source Data'!$F$1:$J$1,'Source Data'!$F$2:$J$184), 5)</f>
+        <v>3.6744400000000002</v>
       </c>
       <c r="F2" s="5" cm="1">
-        <f t="array" ref="F2:F184">_xlfn.XLOOKUP('Source Data'!J1,'Source Data'!$F$1:$J$1,'Source Data'!$F$2:$J$184)</f>
-        <v>100.98666666666666</v>
+        <f t="array" ref="F2:F184">ROUND(_xlfn.XLOOKUP('Source Data'!J1,'Source Data'!$F$1:$J$1,'Source Data'!$F$2:$J$184), 5)</f>
+        <v>100.98667</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5217,13 +5217,13 @@
         <v>KLSELA</v>
       </c>
       <c r="B3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D3" t="str">
         <v>Kuala Selangor Bridge</v>
       </c>
       <c r="E3" s="5">
-        <v>3.3405555555555555</v>
+        <v>3.34056</v>
       </c>
       <c r="F3" s="5">
         <v>101.2525</v>
@@ -5234,16 +5234,16 @@
         <v>KAPAR</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D4" t="str">
         <v>Kapar Junction</v>
       </c>
       <c r="E4" s="5">
-        <v>3.1361111111111111</v>
+        <v>3.13611</v>
       </c>
       <c r="F4" s="5">
-        <v>101.37583333333333</v>
+        <v>101.37582999999999</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5251,16 +5251,16 @@
         <v>PTKLNG</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D5" t="str">
         <v>Pulau Indah Bridge</v>
       </c>
       <c r="E5" s="5">
-        <v>3.0322222222222224</v>
+        <v>3.0322200000000001</v>
       </c>
       <c r="F5" s="5">
-        <v>101.3611111111111</v>
+        <v>101.36111</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5268,16 +5268,16 @@
         <v>MORIB</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D6" t="str">
         <v>Golf Course</v>
       </c>
       <c r="E6" s="5">
-        <v>2.7433333333333332</v>
+        <v>2.7433299999999998</v>
       </c>
       <c r="F6" s="5">
-        <v>101.44638888888889</v>
+        <v>101.44638999999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5285,16 +5285,16 @@
         <v>TJSEPT</v>
       </c>
       <c r="B7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D7" t="str">
         <v>Jetty Tanjung Sepat</v>
       </c>
       <c r="E7" s="5">
-        <v>2.6591666666666667</v>
+        <v>2.65917</v>
       </c>
       <c r="F7" s="5">
-        <v>101.55611111111111</v>
+        <v>101.55611</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5302,16 +5302,16 @@
         <v>TJTUAN</v>
       </c>
       <c r="B8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D8" t="str">
         <v>Lighthouse</v>
       </c>
       <c r="E8" s="5">
-        <v>2.4069444444444446</v>
+        <v>2.4069400000000001</v>
       </c>
       <c r="F8" s="5">
-        <v>101.85194444444444</v>
+        <v>101.85194</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5319,16 +5319,16 @@
         <v>SLMRVR</v>
       </c>
       <c r="B9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D9" t="str">
         <v>Slim River Hospital</v>
       </c>
       <c r="E9" s="5">
-        <v>3.8372222222222225</v>
+        <v>3.8372199999999999</v>
       </c>
       <c r="F9" s="5">
-        <v>101.40416666666667</v>
+        <v>101.40416999999999</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5336,7 +5336,7 @@
         <v>TJMALM</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D10" t="str">
         <v>Universiti Perguruan Sult</v>
@@ -5345,7 +5345,7 @@
         <v>3.6850000000000001</v>
       </c>
       <c r="F10" s="5">
-        <v>101.52388888888889</v>
+        <v>101.52388999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5353,16 +5353,16 @@
         <v>RAWANG</v>
       </c>
       <c r="B11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D11" t="str">
         <v>Lafarge plant</v>
       </c>
       <c r="E11" s="5">
-        <v>3.3091666666666666</v>
+        <v>3.3091699999999999</v>
       </c>
       <c r="F11" s="5">
-        <v>101.57111111111111</v>
+        <v>101.57111</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5370,16 +5370,16 @@
         <v>BATUCV</v>
       </c>
       <c r="B12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D12" t="str">
         <v>Hindu Temple</v>
       </c>
       <c r="E12" s="5">
-        <v>3.2375000000000003</v>
+        <v>3.2374999999999998</v>
       </c>
       <c r="F12" s="5">
-        <v>101.68388888888889</v>
+        <v>101.68389000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5387,16 +5387,16 @@
         <v>SGBESI</v>
       </c>
       <c r="B13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D13" t="str">
         <v>Smart Toll Plaza</v>
       </c>
       <c r="E13" s="5">
-        <v>3.108888888888889</v>
+        <v>3.1088900000000002</v>
       </c>
       <c r="F13" s="5">
-        <v>101.70222222222222</v>
+        <v>101.70222</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5404,16 +5404,16 @@
         <v>KAJANG</v>
       </c>
       <c r="B14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D14" t="str">
         <v>Stadium</v>
       </c>
       <c r="E14" s="5">
-        <v>2.9944444444444445</v>
+        <v>2.99444</v>
       </c>
       <c r="F14" s="5">
-        <v>101.78694444444444</v>
+        <v>101.78694</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5421,16 +5421,16 @@
         <v>SERMBN</v>
       </c>
       <c r="B15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D15" t="str">
         <v>Seremban Mosque</v>
       </c>
       <c r="E15" s="5">
-        <v>2.7219444444444445</v>
+        <v>2.72194</v>
       </c>
       <c r="F15" s="5">
-        <v>101.94222222222223</v>
+        <v>101.94222000000001</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5438,16 +5438,16 @@
         <v>BENTNG</v>
       </c>
       <c r="B16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D16" t="str">
         <v>Dataran Bentong</v>
       </c>
       <c r="E16" s="5">
-        <v>3.5291666666666668</v>
+        <v>3.5291700000000001</v>
       </c>
       <c r="F16" s="5">
-        <v>101.90472222222223</v>
+        <v>101.90472</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5455,16 +5455,16 @@
         <v>RANTAU</v>
       </c>
       <c r="B17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D17" t="str">
         <v>TNB Substation</v>
       </c>
       <c r="E17" s="5">
-        <v>2.5947222222222224</v>
+        <v>2.5947200000000001</v>
       </c>
       <c r="F17" s="5">
-        <v>101.96194444444444</v>
+        <v>101.96194</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5472,16 +5472,16 @@
         <v>KLKLWG</v>
       </c>
       <c r="B18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D18" t="str">
         <v>Jelebu District Council</v>
       </c>
       <c r="E18" s="5">
-        <v>2.9408333333333334</v>
+        <v>2.9408300000000001</v>
       </c>
       <c r="F18" s="5">
-        <v>102.06944444444444</v>
+        <v>102.06944</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5489,16 +5489,16 @@
         <v>PETJYA</v>
       </c>
       <c r="B19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D19" t="str">
         <v>Menara TM</v>
       </c>
       <c r="E19" s="5">
-        <v>3.1158333333333332</v>
+        <v>3.1158299999999999</v>
       </c>
       <c r="F19" s="5">
-        <v>101.66555555555556</v>
+        <v>101.66556</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5506,16 +5506,16 @@
         <v>BTLNJN</v>
       </c>
       <c r="B20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D20" t="str">
         <v>Tol Sungai Penchala</v>
       </c>
       <c r="E20" s="5">
-        <v>3.1774999999999998</v>
+        <v>3.1775000000000002</v>
       </c>
       <c r="F20" s="5">
-        <v>101.61944444444444</v>
+        <v>101.61944</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -5523,16 +5523,16 @@
         <v>PCKPRD</v>
       </c>
       <c r="B21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D21" t="str">
         <v>Puncak Perdana Interchang</v>
       </c>
       <c r="E21" s="5">
-        <v>3.1344444444444446</v>
+        <v>3.1344400000000001</v>
       </c>
       <c r="F21" s="5">
-        <v>101.49611111111111</v>
+        <v>101.49611</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -5540,16 +5540,16 @@
         <v>SHALAM</v>
       </c>
       <c r="B22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D22" t="str">
         <v>Sultan Salahudin Abdul Az</v>
       </c>
       <c r="E22" s="5">
-        <v>3.0788888888888892</v>
+        <v>3.0788899999999999</v>
       </c>
       <c r="F22" s="5">
-        <v>101.52055555555556</v>
+        <v>101.52056</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -5557,16 +5557,16 @@
         <v>KUANG</v>
       </c>
       <c r="B23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D23" t="str">
         <v>Guthrie – LATAR Expresswa</v>
       </c>
       <c r="E23" s="5">
-        <v>3.2694444444444444</v>
+        <v>3.2694399999999999</v>
       </c>
       <c r="F23" s="5">
-        <v>101.54583333333333</v>
+        <v>101.54583</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -5574,16 +5574,16 @@
         <v>NBGILA</v>
       </c>
       <c r="B24" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D24" t="str">
         <v>Met Weather Radar</v>
       </c>
       <c r="E24" s="5">
-        <v>3.1447222222222222</v>
+        <v>3.14472</v>
       </c>
       <c r="F24" s="5">
-        <v>101.55861111111111</v>
+        <v>101.55861</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -5591,16 +5591,16 @@
         <v>TITWGS</v>
       </c>
       <c r="B25" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D25" t="str">
         <v>Titiwangsa Lake</v>
       </c>
       <c r="E25" s="5">
-        <v>3.1774999999999998</v>
+        <v>3.1775000000000002</v>
       </c>
       <c r="F25" s="5">
-        <v>101.70444444444445</v>
+        <v>101.70444000000001</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -5608,16 +5608,16 @@
         <v>SGMBUT</v>
       </c>
       <c r="B26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D26" t="str">
         <v>DUKE Jalan Kuching Interc</v>
       </c>
       <c r="E26" s="5">
-        <v>3.1919444444444443</v>
+        <v>3.1919400000000002</v>
       </c>
       <c r="F26" s="5">
-        <v>101.66888888888889</v>
+        <v>101.66889</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -5625,13 +5625,13 @@
         <v>UTMMSQ</v>
       </c>
       <c r="B27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D27" t="str">
         <v>UTM Mosque</v>
       </c>
       <c r="E27" s="5">
-        <v>1.5591666666666668</v>
+        <v>1.5591699999999999</v>
       </c>
       <c r="F27" s="5">
         <v>103.6375</v>
@@ -5642,16 +5642,16 @@
         <v>BENUT</v>
       </c>
       <c r="B28" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D28" t="str">
         <v>Benut</v>
       </c>
       <c r="E28" s="5">
-        <v>1.6441666666666666</v>
+        <v>1.6441699999999999</v>
       </c>
       <c r="F28" s="5">
-        <v>103.25944444444444</v>
+        <v>103.25944</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -5659,7 +5659,7 @@
         <v>KULAI</v>
       </c>
       <c r="B29" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D29" t="str">
         <v>Kulai Tol Plaza</v>
@@ -5668,7 +5668,7 @@
         <v>1.65</v>
       </c>
       <c r="F29" s="5">
-        <v>103.55499999999999</v>
+        <v>103.55500000000001</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -5676,16 +5676,16 @@
         <v>EJBAIR</v>
       </c>
       <c r="B30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D30" t="str">
         <v>East of Johor Bahru Airfi</v>
       </c>
       <c r="E30" s="5">
-        <v>1.6680555555555554</v>
+        <v>1.6680600000000001</v>
       </c>
       <c r="F30" s="5">
-        <v>103.71638888888889</v>
+        <v>103.71639</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -5693,16 +5693,16 @@
         <v>KOTATG</v>
       </c>
       <c r="B31" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D31" t="str">
         <v>Kota Tinggi Bridge</v>
       </c>
       <c r="E31" s="5">
-        <v>1.7288888888888889</v>
+        <v>1.72889</v>
       </c>
       <c r="F31" s="5">
-        <v>103.90166666666667</v>
+        <v>103.90167</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -5710,16 +5710,16 @@
         <v>ETIRAM</v>
       </c>
       <c r="B32" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D32" t="str">
         <v>East of Kg Sg Tiram</v>
       </c>
       <c r="E32" s="5">
-        <v>1.5833333333333335</v>
+        <v>1.5833299999999999</v>
       </c>
       <c r="F32" s="5">
-        <v>103.91666666666667</v>
+        <v>103.91667</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -5727,13 +5727,13 @@
         <v>EASTJB</v>
       </c>
       <c r="B33" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D33" t="str">
         <v>East of Johor Bahru Town</v>
       </c>
       <c r="E33" s="5">
-        <v>1.5038888888888888</v>
+        <v>1.5038899999999999</v>
       </c>
       <c r="F33" s="5">
         <v>103.86499999999999</v>
@@ -5744,16 +5744,16 @@
         <v>FELDA</v>
       </c>
       <c r="B34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D34" t="str">
         <v>Felda Ulu Tebrau</v>
       </c>
       <c r="E34" s="5">
-        <v>1.6308333333333334</v>
+        <v>1.63083</v>
       </c>
       <c r="F34" s="5">
-        <v>103.75277777777778</v>
+        <v>103.75278</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -5761,16 +5761,16 @@
         <v>TEBMAL</v>
       </c>
       <c r="B35" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D35" t="str">
         <v>Tebrau City Mall</v>
       </c>
       <c r="E35" s="5">
-        <v>1.549722222222222</v>
+        <v>1.54972</v>
       </c>
       <c r="F35" s="5">
-        <v>103.79666666666667</v>
+        <v>103.79667000000001</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -5778,16 +5778,16 @@
         <v>SKGSEM</v>
       </c>
       <c r="B36" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D36" t="str">
-        <v>South Of Kg Semangar</v>
+        <v>South of Kg Semangar</v>
       </c>
       <c r="E36" s="5">
-        <v>1.7416666666666667</v>
+        <v>1.7416700000000001</v>
       </c>
       <c r="F36" s="5">
-        <v>103.78333333333333</v>
+        <v>103.78333000000001</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -5795,16 +5795,16 @@
         <v>SDLBSR</v>
       </c>
       <c r="B37" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D37" t="str">
         <v>Kampung Sedili Besar</v>
       </c>
       <c r="E37" s="5">
-        <v>1.9266666666666665</v>
+        <v>1.9266700000000001</v>
       </c>
       <c r="F37" s="5">
-        <v>104.11611111111111</v>
+        <v>104.11611000000001</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -5812,16 +5812,16 @@
         <v>SPGRNG</v>
       </c>
       <c r="B38" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D38" t="str">
         <v>Simpang Renggam Town</v>
       </c>
       <c r="E38" s="5">
-        <v>1.8277777777777777</v>
+        <v>1.82778</v>
       </c>
       <c r="F38" s="5">
-        <v>103.30944444444444</v>
+        <v>103.30944</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -5829,16 +5829,16 @@
         <v>AIRHTM</v>
       </c>
       <c r="B39" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D39" t="str">
         <v>Air Hitam</v>
       </c>
       <c r="E39" s="5">
-        <v>1.931111111111111</v>
+        <v>1.9311100000000001</v>
       </c>
       <c r="F39" s="5">
-        <v>103.17583333333334</v>
+        <v>103.17583</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -5846,16 +5846,16 @@
         <v>YONGPG</v>
       </c>
       <c r="B40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D40" t="str">
         <v>Yong Peng</v>
       </c>
       <c r="E40" s="5">
-        <v>2.0172222222222222</v>
+        <v>2.01722</v>
       </c>
       <c r="F40" s="5">
-        <v>103.06305555555555</v>
+        <v>103.06305999999999</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -5863,7 +5863,7 @@
         <v>PTXRAY</v>
       </c>
       <c r="B41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D41" t="str">
         <v>Point XRay</v>
@@ -5872,7 +5872,7 @@
         <v>1.4750000000000001</v>
       </c>
       <c r="F41" s="5">
-        <v>103.83166666666666</v>
+        <v>103.83167</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -5880,16 +5880,16 @@
         <v>TASSAN</v>
       </c>
       <c r="B42" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D42" t="str">
         <v>Tass Andrassy</v>
       </c>
       <c r="E42" s="5">
-        <v>4.3213888888888885</v>
+        <v>4.3213900000000001</v>
       </c>
       <c r="F42" s="5">
-        <v>118.02138888888889</v>
+        <v>118.02139</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -5897,16 +5897,16 @@
         <v>OLDAIR</v>
       </c>
       <c r="B43" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D43" t="str">
         <v>Old Airport</v>
       </c>
       <c r="E43" s="5">
-        <v>4.2669444444444444</v>
+        <v>4.26694</v>
       </c>
       <c r="F43" s="5">
-        <v>117.88666666666667</v>
+        <v>117.88667</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -5914,16 +5914,16 @@
         <v>SBTKIS</v>
       </c>
       <c r="B44" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D44" t="str">
         <v>Sebatik Island</v>
       </c>
       <c r="E44" s="5">
-        <v>4.2230555555555558</v>
+        <v>4.2230600000000003</v>
       </c>
       <c r="F44" s="5">
-        <v>117.78055555555555</v>
+        <v>117.78055999999999</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -5931,13 +5931,13 @@
         <v>KLBKN</v>
       </c>
       <c r="B45" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D45" t="str">
         <v>Kalabakan</v>
       </c>
       <c r="E45" s="5">
-        <v>4.3988888888888891</v>
+        <v>4.3988899999999997</v>
       </c>
       <c r="F45" s="5">
         <v>117.495</v>
@@ -5948,16 +5948,16 @@
         <v>BALUNG</v>
       </c>
       <c r="B46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D46" t="str">
         <v>Balung</v>
       </c>
       <c r="E46" s="5">
-        <v>4.3644444444444437</v>
+        <v>4.3644400000000001</v>
       </c>
       <c r="F46" s="5">
-        <v>118.12777777777777</v>
+        <v>118.12778</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -5965,16 +5965,16 @@
         <v>KWAHLL</v>
       </c>
       <c r="B47" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D47" t="str">
         <v>Kawa Hill</v>
       </c>
       <c r="E47" s="5">
-        <v>4.3938888888888892</v>
+        <v>4.3938899999999999</v>
       </c>
       <c r="F47" s="5">
-        <v>118.08694444444444</v>
+        <v>118.08694</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -5982,16 +5982,16 @@
         <v>MTPYRM</v>
       </c>
       <c r="B48" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D48" t="str">
         <v>Mt Pyramid</v>
       </c>
       <c r="E48" s="5">
-        <v>4.4733333333333336</v>
+        <v>4.4733299999999998</v>
       </c>
       <c r="F48" s="5">
-        <v>118.06916666666666</v>
+        <v>118.06917</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -5999,13 +5999,13 @@
         <v>BTRNG</v>
       </c>
       <c r="B49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D49" t="str">
         <v>Baturong</v>
       </c>
       <c r="E49" s="5">
-        <v>4.6994444444444445</v>
+        <v>4.6994400000000001</v>
       </c>
       <c r="F49" s="5">
         <v>118.0025</v>
@@ -6016,16 +6016,16 @@
         <v>DANUM</v>
       </c>
       <c r="B50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D50" t="str">
         <v>Danum</v>
       </c>
       <c r="E50" s="5">
-        <v>4.8519444444444444</v>
+        <v>4.8519399999999999</v>
       </c>
       <c r="F50" s="5">
-        <v>117.78638888888889</v>
+        <v>117.78639</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -6033,16 +6033,16 @@
         <v>JCT49K</v>
       </c>
       <c r="B51" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D51" t="str">
         <v>Junction (49KM)</v>
       </c>
       <c r="E51" s="5">
-        <v>4.4266666666666667</v>
+        <v>4.4266699999999997</v>
       </c>
       <c r="F51" s="5">
-        <v>118.17833333333334</v>
+        <v>118.17833</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -6050,16 +6050,16 @@
         <v>KGAMAN</v>
       </c>
       <c r="B52" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D52" t="str">
         <v>Kampung Aman</v>
       </c>
       <c r="E52" s="5">
-        <v>4.6036111111111104</v>
+        <v>4.6036099999999998</v>
       </c>
       <c r="F52" s="5">
-        <v>118.18972222222223</v>
+        <v>118.18971999999999</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -6067,16 +6067,16 @@
         <v>TJBATI</v>
       </c>
       <c r="B53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D53" t="str">
         <v>Tanjung Batai</v>
       </c>
       <c r="E53" s="5">
-        <v>4.8386111111111108</v>
+        <v>4.8386100000000001</v>
       </c>
       <c r="F53" s="5">
-        <v>118.16777777777779</v>
+        <v>118.16777999999999</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -6084,16 +6084,16 @@
         <v>SDLHLL</v>
       </c>
       <c r="B54" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D54" t="str">
         <v>Saddle Hill</v>
       </c>
       <c r="E54" s="5">
-        <v>4.2988888888888885</v>
+        <v>4.2988900000000001</v>
       </c>
       <c r="F54" s="5">
-        <v>118.18555555555555</v>
+        <v>118.18556</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -6101,16 +6101,16 @@
         <v>NAGOS</v>
       </c>
       <c r="B55" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D55" t="str">
         <v>Nagos</v>
       </c>
       <c r="E55" s="5">
-        <v>4.3477777777777771</v>
+        <v>4.3477800000000002</v>
       </c>
       <c r="F55" s="5">
-        <v>118.39305555555556</v>
+        <v>118.39306000000001</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -6118,16 +6118,16 @@
         <v>SMPRNA</v>
       </c>
       <c r="B56" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D56" t="str">
         <v>Semporna</v>
       </c>
       <c r="E56" s="5">
-        <v>4.4497222222222224</v>
+        <v>4.4497200000000001</v>
       </c>
       <c r="F56" s="5">
-        <v>118.59638888888888</v>
+        <v>118.59639</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -6135,16 +6135,16 @@
         <v>GAYAIS</v>
       </c>
       <c r="B57" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D57" t="str">
         <v>Gaya Island</v>
       </c>
       <c r="E57" s="5">
-        <v>4.6222222222222227</v>
+        <v>4.6222200000000004</v>
       </c>
       <c r="F57" s="5">
-        <v>118.74027777777778</v>
+        <v>118.74028</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -6152,16 +6152,16 @@
         <v>SPDNIS</v>
       </c>
       <c r="B58" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D58" t="str">
         <v>Sipadan Island</v>
       </c>
       <c r="E58" s="5">
-        <v>4.1405555555555562</v>
+        <v>4.1405599999999998</v>
       </c>
       <c r="F58" s="5">
-        <v>118.6438888888889</v>
+        <v>118.64389</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -6169,16 +6169,16 @@
         <v>BNDIND</v>
       </c>
       <c r="B59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D59" t="str">
         <v>Bandar Indah (Road Juncti</v>
       </c>
       <c r="E59" s="5">
-        <v>5.855833333333333</v>
+        <v>5.8558300000000001</v>
       </c>
       <c r="F59" s="5">
-        <v>118.07222222222222</v>
+        <v>118.07222</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -6186,16 +6186,16 @@
         <v>KPTBNK</v>
       </c>
       <c r="B60" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D60" t="str">
         <v>Kampong Tobanka</v>
       </c>
       <c r="E60" s="5">
-        <v>6.019166666666667</v>
+        <v>6.0191699999999999</v>
       </c>
       <c r="F60" s="5">
-        <v>118.03944444444444</v>
+        <v>118.03944</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -6203,16 +6203,16 @@
         <v>BAIIS</v>
       </c>
       <c r="B61" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D61" t="str">
         <v>Bai Island</v>
       </c>
       <c r="E61" s="5">
-        <v>5.7752777777777773</v>
+        <v>5.7752800000000004</v>
       </c>
       <c r="F61" s="5">
-        <v>118.10027777777778</v>
+        <v>118.10028</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -6220,16 +6220,16 @@
         <v>TJBDR</v>
       </c>
       <c r="B62" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D62" t="str">
         <v>Tanjung Bidadari</v>
       </c>
       <c r="E62" s="5">
-        <v>5.8244444444444445</v>
+        <v>5.8244400000000001</v>
       </c>
       <c r="F62" s="5">
-        <v>118.34916666666666</v>
+        <v>118.34917</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -6237,13 +6237,13 @@
         <v>KLKNBB</v>
       </c>
       <c r="B63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D63" t="str">
         <v>Kuala Kinabatangan Besar</v>
       </c>
       <c r="E63" s="5">
-        <v>5.642777777777777</v>
+        <v>5.6427800000000001</v>
       </c>
       <c r="F63" s="5">
         <v>118.6125</v>
@@ -6254,16 +6254,16 @@
         <v>KGBILT</v>
       </c>
       <c r="B64" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D64" t="str">
         <v>Kampung Bilit</v>
       </c>
       <c r="E64" s="5">
-        <v>5.4975000000000005</v>
+        <v>5.4974999999999996</v>
       </c>
       <c r="F64" s="5">
-        <v>118.20805555555556</v>
+        <v>118.20806</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -6271,16 +6271,16 @@
         <v>SGSEG</v>
       </c>
       <c r="B65" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D65" t="str">
         <v>Sungai Seguntor</v>
       </c>
       <c r="E65" s="5">
-        <v>5.8066666666666666</v>
+        <v>5.8066700000000004</v>
       </c>
       <c r="F65" s="5">
-        <v>117.99361111111111</v>
+        <v>117.99361</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -6288,13 +6288,13 @@
         <v>KTKNB</v>
       </c>
       <c r="B66" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D66" t="str">
         <v>Kota Kinabatangan</v>
       </c>
       <c r="E66" s="5">
-        <v>5.5888888888888886</v>
+        <v>5.5888900000000001</v>
       </c>
       <c r="F66" s="5">
         <v>117.845</v>
@@ -6305,16 +6305,16 @@
         <v>KGKLLK</v>
       </c>
       <c r="B67" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D67" t="str">
         <v>Kampung Kuala Lokan</v>
       </c>
       <c r="E67" s="5">
-        <v>5.4369444444444444</v>
+        <v>5.4369399999999999</v>
       </c>
       <c r="F67" s="5">
-        <v>117.74861111111112</v>
+        <v>117.74861</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -6322,16 +6322,16 @@
         <v>ML32JT</v>
       </c>
       <c r="B68" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D68" t="str">
         <v>Mile 32 Rd Junction</v>
       </c>
       <c r="E68" s="5">
-        <v>5.7577777777777781</v>
+        <v>5.7577800000000003</v>
       </c>
       <c r="F68" s="5">
-        <v>117.75861111111111</v>
+        <v>117.75861</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -6339,7 +6339,7 @@
         <v>TELPID</v>
       </c>
       <c r="B69" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D69" t="str">
         <v>Telupid</v>
@@ -6348,7 +6348,7 @@
         <v>5.6275000000000004</v>
       </c>
       <c r="F69" s="5">
-        <v>117.13055555555555</v>
+        <v>117.13056</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -6356,16 +6356,16 @@
         <v>KGGMGL</v>
       </c>
       <c r="B70" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D70" t="str">
         <v>Kampung GumGum Laut</v>
       </c>
       <c r="E70" s="5">
-        <v>5.969444444444445</v>
+        <v>5.9694399999999996</v>
       </c>
       <c r="F70" s="5">
-        <v>117.90972222222223</v>
+        <v>117.90971999999999</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -6373,16 +6373,16 @@
         <v>KGSMWG</v>
       </c>
       <c r="B71" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D71" t="str">
         <v>Kampung Semawang</v>
       </c>
       <c r="E71" s="5">
-        <v>5.9197222222222221</v>
+        <v>5.9197199999999999</v>
       </c>
       <c r="F71" s="5">
-        <v>117.76222222222222</v>
+        <v>117.76222</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -6390,7 +6390,7 @@
         <v>BLURAN</v>
       </c>
       <c r="B72" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D72" t="str">
         <v>Beluran</v>
@@ -6399,7 +6399,7 @@
         <v>5.8949999999999996</v>
       </c>
       <c r="F72" s="5">
-        <v>117.55694444444444</v>
+        <v>117.55694</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -6407,16 +6407,16 @@
         <v>KNWIIS</v>
       </c>
       <c r="B73" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D73" t="str">
         <v>Kenawi Island</v>
       </c>
       <c r="E73" s="5">
-        <v>5.9883333333333333</v>
+        <v>5.9883300000000004</v>
       </c>
       <c r="F73" s="5">
-        <v>117.70194444444445</v>
+        <v>117.70193999999999</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -6424,16 +6424,16 @@
         <v>KGSGSG</v>
       </c>
       <c r="B74" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D74" t="str">
         <v>Kampung Sungai-Sungai</v>
       </c>
       <c r="E74" s="5">
-        <v>6.2508333333333335</v>
+        <v>6.2508299999999997</v>
       </c>
       <c r="F74" s="5">
-        <v>117.35111111111111</v>
+        <v>117.35111000000001</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -6441,16 +6441,16 @@
         <v>KGTRSN</v>
       </c>
       <c r="B75" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D75" t="str">
         <v>Kampung Terusan</v>
       </c>
       <c r="E75" s="5">
-        <v>6.4258333333333333</v>
+        <v>6.4258300000000004</v>
       </c>
       <c r="F75" s="5">
-        <v>117.68722222222223</v>
+        <v>117.68722</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -6458,16 +6458,16 @@
         <v>SLNGIS</v>
       </c>
       <c r="B76" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D76" t="str">
         <v>Selingan Island</v>
       </c>
       <c r="E76" s="5">
-        <v>6.1741666666666672</v>
+        <v>6.1741700000000002</v>
       </c>
       <c r="F76" s="5">
-        <v>118.06055555555555</v>
+        <v>118.06056</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -6475,7 +6475,7 @@
         <v>LNKYIS</v>
       </c>
       <c r="B77" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D77" t="str">
         <v>Lankayan Island</v>
@@ -6484,7 +6484,7 @@
         <v>6.5</v>
       </c>
       <c r="F77" s="5">
-        <v>117.91666666666667</v>
+        <v>117.91667</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -6492,16 +6492,16 @@
         <v>SBRHIS</v>
       </c>
       <c r="B78" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D78" t="str">
         <v>South of Berhala Island</v>
       </c>
       <c r="E78" s="5">
-        <v>5.8641666666666667</v>
+        <v>5.8641699999999997</v>
       </c>
       <c r="F78" s="5">
-        <v>118.14833333333334</v>
+        <v>118.14833</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -6509,13 +6509,13 @@
         <v>LNGMNS</v>
       </c>
       <c r="B79" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D79" t="str">
         <v>Luang Manis</v>
       </c>
       <c r="E79" s="5">
-        <v>5.666666666666667</v>
+        <v>5.6666699999999999</v>
       </c>
       <c r="F79" s="5">
         <v>117.655</v>
@@ -6526,16 +6526,16 @@
         <v>PMGSCH</v>
       </c>
       <c r="B80" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D80" t="str">
         <v>Pamaguan Primary School</v>
       </c>
       <c r="E80" s="5">
-        <v>5.9575000000000005</v>
+        <v>5.9574999999999996</v>
       </c>
       <c r="F80" s="5">
-        <v>118.06444444444445</v>
+        <v>118.06444</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -6543,16 +6543,16 @@
         <v>PRTWLD</v>
       </c>
       <c r="B81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D81" t="str">
         <v>Port Weld</v>
       </c>
       <c r="E81" s="5">
-        <v>4.8380555555555551</v>
+        <v>4.8380599999999996</v>
       </c>
       <c r="F81" s="5">
-        <v>100.62583333333333</v>
+        <v>100.62582999999999</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -6560,16 +6560,16 @@
         <v>TJPDNG</v>
       </c>
       <c r="B82" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D82" t="str">
         <v>Tanjung Piandang</v>
       </c>
       <c r="E82" s="5">
-        <v>5.0880555555555551</v>
+        <v>5.0880599999999996</v>
       </c>
       <c r="F82" s="5">
-        <v>100.36055555555555</v>
+        <v>100.36056000000001</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -6577,16 +6577,16 @@
         <v>PAMAN</v>
       </c>
       <c r="B83" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D83" t="str">
         <v>South of Pulau Aman</v>
       </c>
       <c r="E83" s="5">
-        <v>5.2586111111111107</v>
+        <v>5.25861</v>
       </c>
       <c r="F83" s="5">
-        <v>100.38416666666667</v>
+        <v>100.38417</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -6594,16 +6594,16 @@
         <v>KDHPKW</v>
       </c>
       <c r="B84" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D84" t="str">
         <v>Kedah Peak West</v>
       </c>
       <c r="E84" s="5">
-        <v>5.743611111111111</v>
+        <v>5.7436100000000003</v>
       </c>
       <c r="F84" s="5">
-        <v>100.35694444444444</v>
+        <v>100.35693999999999</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -6611,7 +6611,7 @@
         <v>KLMUDA</v>
       </c>
       <c r="B85" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D85" t="str">
         <v>Kuala Sungai Muda</v>
@@ -6620,7 +6620,7 @@
         <v>5.5774999999999997</v>
       </c>
       <c r="F85" s="5">
-        <v>100.33583333333333</v>
+        <v>100.33583</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -6628,16 +6628,16 @@
         <v>GRGTWN</v>
       </c>
       <c r="B86" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D86" t="str">
         <v>North of George Town</v>
       </c>
       <c r="E86" s="5">
-        <v>5.464722222222222</v>
+        <v>5.4647199999999998</v>
       </c>
       <c r="F86" s="5">
-        <v>100.30722222222222</v>
+        <v>100.30722</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -6645,7 +6645,7 @@
         <v>PLGAYA</v>
       </c>
       <c r="B87" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D87" t="str">
         <v>West of Pulau Gaya</v>
@@ -6662,16 +6662,16 @@
         <v>PLSULG</v>
       </c>
       <c r="B88" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D88" t="str">
         <v>Pulau Sulug</v>
       </c>
       <c r="E88" s="5">
-        <v>5.9611111111111112</v>
+        <v>5.9611099999999997</v>
       </c>
       <c r="F88" s="5">
-        <v>115.99166666666667</v>
+        <v>115.99167</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -6679,7 +6679,7 @@
         <v>PLTIGA</v>
       </c>
       <c r="B89" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D89" t="str">
         <v>Pulau Tiga</v>
@@ -6688,7 +6688,7 @@
         <v>5.75</v>
       </c>
       <c r="F89" s="5">
-        <v>115.65833333333335</v>
+        <v>115.65833000000001</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -6696,13 +6696,13 @@
         <v>KLPNYU</v>
       </c>
       <c r="B90" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D90" t="str">
         <v>Kuala Penyu</v>
       </c>
       <c r="E90" s="5">
-        <v>5.5666666666666664</v>
+        <v>5.5666700000000002</v>
       </c>
       <c r="F90" s="5">
         <v>115.6</v>
@@ -6713,16 +6713,16 @@
         <v>BNGWN</v>
       </c>
       <c r="B91" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D91" t="str">
         <v>Bongawan</v>
       </c>
       <c r="E91" s="5">
-        <v>5.5388888888888888</v>
+        <v>5.5388900000000003</v>
       </c>
       <c r="F91" s="5">
-        <v>115.85777777777777</v>
+        <v>115.85778000000001</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -6730,7 +6730,7 @@
         <v>EPAPAR</v>
       </c>
       <c r="B92" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D92" t="str">
         <v>East of Papar</v>
@@ -6739,7 +6739,7 @@
         <v>5.7</v>
       </c>
       <c r="F92" s="5">
-        <v>116.01666666666667</v>
+        <v>116.01667</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -6747,13 +6747,13 @@
         <v>EKAWNG</v>
       </c>
       <c r="B93" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D93" t="str">
         <v>East of Kawang</v>
       </c>
       <c r="E93" s="5">
-        <v>5.7666666666666666</v>
+        <v>5.7666700000000004</v>
       </c>
       <c r="F93" s="5">
         <v>116.05</v>
@@ -6764,16 +6764,16 @@
         <v>EKNRTT</v>
       </c>
       <c r="B94" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D94" t="str">
         <v>East of Kinarut Town</v>
       </c>
       <c r="E94" s="5">
-        <v>5.8183333333333334</v>
+        <v>5.8183299999999996</v>
       </c>
       <c r="F94" s="5">
-        <v>116.07194444444444</v>
+        <v>116.07194</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -6781,16 +6781,16 @@
         <v>KPYAN</v>
       </c>
       <c r="B95" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D95" t="str">
         <v>Kepayan</v>
       </c>
       <c r="E95" s="5">
-        <v>5.9258333333333333</v>
+        <v>5.9258300000000004</v>
       </c>
       <c r="F95" s="5">
-        <v>116.05833333333334</v>
+        <v>116.05833</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -6798,16 +6798,16 @@
         <v>EINMNT</v>
       </c>
       <c r="B96" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D96" t="str">
         <v>East of Inanam Town</v>
       </c>
       <c r="E96" s="5">
-        <v>5.9955555555555557</v>
+        <v>5.9955600000000002</v>
       </c>
       <c r="F96" s="5">
-        <v>116.15138888888889</v>
+        <v>116.15139000000001</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -6815,16 +6815,16 @@
         <v>ETLPOK</v>
       </c>
       <c r="B97" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D97" t="str">
         <v>East of Telipok</v>
       </c>
       <c r="E97" s="5">
-        <v>6.1083333333333334</v>
+        <v>6.1083299999999996</v>
       </c>
       <c r="F97" s="5">
-        <v>116.20833333333334</v>
+        <v>116.20833</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -6832,16 +6832,16 @@
         <v>KGKULU</v>
       </c>
       <c r="B98" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D98" t="str">
         <v>Kampung Kiulu</v>
       </c>
       <c r="E98" s="5">
-        <v>6.0616666666666665</v>
+        <v>6.0616700000000003</v>
       </c>
       <c r="F98" s="5">
-        <v>116.28305555555555</v>
+        <v>116.28306000000001</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -6849,7 +6849,7 @@
         <v>KGBLBK</v>
       </c>
       <c r="B99" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D99" t="str">
         <v>Kampung Balabakan</v>
@@ -6858,7 +6858,7 @@
         <v>6.0250000000000004</v>
       </c>
       <c r="F99" s="5">
-        <v>116.4538888888889</v>
+        <v>116.45389</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -6866,16 +6866,16 @@
         <v>RANAU</v>
       </c>
       <c r="B100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D100" t="str">
         <v>Ranau</v>
       </c>
       <c r="E100" s="5">
-        <v>5.9583333333333339</v>
+        <v>5.9583300000000001</v>
       </c>
       <c r="F100" s="5">
-        <v>116.67500000000001</v>
+        <v>116.675</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -6883,16 +6883,16 @@
         <v>WH1040</v>
       </c>
       <c r="B101" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D101" t="str">
         <v>West of Hill 1040</v>
       </c>
       <c r="E101" s="5">
-        <v>6.1097222222222216</v>
+        <v>6.1097200000000003</v>
       </c>
       <c r="F101" s="5">
-        <v>116.07694444444444</v>
+        <v>116.07693999999999</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -6900,7 +6900,7 @@
         <v>TJDLT</v>
       </c>
       <c r="B102" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D102" t="str">
         <v>Tanjung Dalit</v>
@@ -6909,7 +6909,7 @@
         <v>6.16</v>
       </c>
       <c r="F102" s="5">
-        <v>116.14166666666668</v>
+        <v>116.14167</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -6917,16 +6917,16 @@
         <v>KTBLUD</v>
       </c>
       <c r="B103" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D103" t="str">
         <v>Kota Belud</v>
       </c>
       <c r="E103" s="5">
-        <v>6.3466666666666667</v>
+        <v>6.3466699999999996</v>
       </c>
       <c r="F103" s="5">
-        <v>116.39777777777779</v>
+        <v>116.39778</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -6934,16 +6934,16 @@
         <v>TRNDAK</v>
       </c>
       <c r="B104" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D104" t="str">
         <v>Terendak</v>
       </c>
       <c r="E104" s="5">
-        <v>2.2922222222222222</v>
+        <v>2.2922199999999999</v>
       </c>
       <c r="F104" s="5">
-        <v>102.0911111111111</v>
+        <v>102.09111</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -6951,13 +6951,13 @@
         <v>REMBIA</v>
       </c>
       <c r="B105" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D105" t="str">
         <v>Rembia</v>
       </c>
       <c r="E105" s="5">
-        <v>2.2822222222222224</v>
+        <v>2.2822200000000001</v>
       </c>
       <c r="F105" s="5">
         <v>102.215</v>
@@ -6968,13 +6968,13 @@
         <v>TAMPIN</v>
       </c>
       <c r="B106" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D106" t="str">
         <v>Tampin</v>
       </c>
       <c r="E106" s="5">
-        <v>2.4705555555555558</v>
+        <v>2.4705599999999999</v>
       </c>
       <c r="F106" s="5">
         <v>102.23</v>
@@ -6985,7 +6985,7 @@
         <v>CHNCHN</v>
       </c>
       <c r="B107" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D107" t="str">
         <v>Chin Chin</v>
@@ -6994,7 +6994,7 @@
         <v>2.29</v>
       </c>
       <c r="F107" s="5">
-        <v>102.47777777777777</v>
+        <v>102.47778</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -7002,16 +7002,16 @@
         <v>BTBERU</v>
       </c>
       <c r="B108" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D108" t="str">
         <v>Bt Beruang</v>
       </c>
       <c r="E108" s="5">
-        <v>2.2422222222222223</v>
+        <v>2.2422200000000001</v>
       </c>
       <c r="F108" s="5">
-        <v>102.30472222222222</v>
+        <v>102.30472</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -7019,16 +7019,16 @@
         <v>UMBAI</v>
       </c>
       <c r="B109" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D109" t="str">
         <v>Umbai</v>
       </c>
       <c r="E109" s="5">
-        <v>2.1555555555555554</v>
+        <v>2.1555599999999999</v>
       </c>
       <c r="F109" s="5">
-        <v>102.34444444444443</v>
+        <v>102.34444000000001</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -7036,7 +7036,7 @@
         <v>MALCTY</v>
       </c>
       <c r="B110" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D110" t="str">
         <v>Malacca City</v>
@@ -7053,13 +7053,13 @@
         <v>MUAR</v>
       </c>
       <c r="B111" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D111" t="str">
         <v>Muar</v>
       </c>
       <c r="E111" s="5">
-        <v>2.0616666666666665</v>
+        <v>2.0616699999999999</v>
       </c>
       <c r="F111" s="5">
         <v>102.565</v>
@@ -7070,16 +7070,16 @@
         <v>TANKAK</v>
       </c>
       <c r="B112" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D112" t="str">
         <v>Tangkak</v>
       </c>
       <c r="E112" s="5">
-        <v>2.2722222222222221</v>
+        <v>2.2722199999999999</v>
       </c>
       <c r="F112" s="5">
-        <v>102.54444444444444</v>
+        <v>102.54443999999999</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -7087,7 +7087,7 @@
         <v>PAGOH</v>
       </c>
       <c r="B113" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D113" t="str">
         <v>Pagoh</v>
@@ -7104,16 +7104,16 @@
         <v>PENRIK</v>
       </c>
       <c r="B114" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D114" t="str">
         <v>Penarik</v>
       </c>
       <c r="E114" s="5">
-        <v>5.5958333333333332</v>
+        <v>5.5958300000000003</v>
       </c>
       <c r="F114" s="5">
-        <v>102.8261111111111</v>
+        <v>102.82611</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -7121,16 +7121,16 @@
         <v>BDRPER</v>
       </c>
       <c r="B115" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D115" t="str">
         <v>Bandar Permaisuri</v>
       </c>
       <c r="E115" s="5">
-        <v>5.5113888888888889</v>
+        <v>5.5113899999999996</v>
       </c>
       <c r="F115" s="5">
-        <v>102.74555555555555</v>
+        <v>102.74556</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -7138,16 +7138,16 @@
         <v>KGMRNG</v>
       </c>
       <c r="B116" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D116" t="str">
         <v>Kampung Merang</v>
       </c>
       <c r="E116" s="5">
-        <v>5.5194444444444448</v>
+        <v>5.5194400000000003</v>
       </c>
       <c r="F116" s="5">
-        <v>102.95944444444444</v>
+        <v>102.95944</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -7155,16 +7155,16 @@
         <v>BATURK</v>
       </c>
       <c r="B117" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D117" t="str">
         <v>Batu Rakit</v>
       </c>
       <c r="E117" s="5">
-        <v>5.4444444444444446</v>
+        <v>5.4444400000000002</v>
       </c>
       <c r="F117" s="5">
-        <v>103.04861111111111</v>
+        <v>103.04861</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -7172,16 +7172,16 @@
         <v>PGCNRG</v>
       </c>
       <c r="B118" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D118" t="str">
         <v>Kampung Chenering</v>
       </c>
       <c r="E118" s="5">
-        <v>5.2716666666666665</v>
+        <v>5.2716700000000003</v>
       </c>
       <c r="F118" s="5">
-        <v>103.17638888888889</v>
+        <v>103.17639</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -7189,16 +7189,16 @@
         <v>MARANG</v>
       </c>
       <c r="B119" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D119" t="str">
         <v>Marang</v>
       </c>
       <c r="E119" s="5">
-        <v>5.1888888888888891</v>
+        <v>5.1888899999999998</v>
       </c>
       <c r="F119" s="5">
-        <v>103.22055555555556</v>
+        <v>103.22056000000001</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -7206,16 +7206,16 @@
         <v>KLBRNG</v>
       </c>
       <c r="B120" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D120" t="str">
         <v>Kuala Berang</v>
       </c>
       <c r="E120" s="5">
-        <v>5.0619444444444444</v>
+        <v>5.0619399999999999</v>
       </c>
       <c r="F120" s="5">
-        <v>103.00916666666667</v>
+        <v>103.00917</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -7223,16 +7223,16 @@
         <v>TSKKEN</v>
       </c>
       <c r="B121" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D121" t="str">
         <v>Tasik Kenyir</v>
       </c>
       <c r="E121" s="5">
-        <v>5.0836111111111109</v>
+        <v>5.0836100000000002</v>
       </c>
       <c r="F121" s="5">
-        <v>102.81138888888889</v>
+        <v>102.81139</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -7240,16 +7240,16 @@
         <v>PENERK</v>
       </c>
       <c r="B122" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D122" t="str">
         <v>Penerak</v>
       </c>
       <c r="E122" s="5">
-        <v>4.9683333333333337</v>
+        <v>4.9683299999999999</v>
       </c>
       <c r="F122" s="5">
-        <v>103.32055555555556</v>
+        <v>103.32056</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -7257,16 +7257,16 @@
         <v>NENASI</v>
       </c>
       <c r="B123" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D123" t="str">
         <v>Nenasi River Mouth</v>
       </c>
       <c r="E123" s="5">
-        <v>3.0736111111111115</v>
+        <v>3.07361</v>
       </c>
       <c r="F123" s="5">
-        <v>103.4388888888889</v>
+        <v>103.43889</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -7274,16 +7274,16 @@
         <v>PEKAN</v>
       </c>
       <c r="B124" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D124" t="str">
         <v>Pekan Bridge</v>
       </c>
       <c r="E124" s="5">
-        <v>3.5055555555555555</v>
+        <v>3.50556</v>
       </c>
       <c r="F124" s="5">
-        <v>103.39111111111112</v>
+        <v>103.39111</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -7291,13 +7291,13 @@
         <v>KUANTW</v>
       </c>
       <c r="B125" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D125" t="str">
         <v>Tower 188</v>
       </c>
       <c r="E125" s="5">
-        <v>3.8038888888888889</v>
+        <v>3.80389</v>
       </c>
       <c r="F125" s="5">
         <v>103.3275</v>
@@ -7308,16 +7308,16 @@
         <v>TJGELG</v>
       </c>
       <c r="B126" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D126" t="str">
         <v>Juantan Port</v>
       </c>
       <c r="E126" s="5">
-        <v>3.9833333333333334</v>
+        <v>3.98333</v>
       </c>
       <c r="F126" s="5">
-        <v>103.41666666666667</v>
+        <v>103.41667</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -7325,16 +7325,16 @@
         <v>CUKAI</v>
       </c>
       <c r="B127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D127" t="str">
         <v>Kuala Kemaman</v>
       </c>
       <c r="E127" s="5">
-        <v>4.2361111111111116</v>
+        <v>4.23611</v>
       </c>
       <c r="F127" s="5">
-        <v>103.44861111111112</v>
+        <v>103.44861</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -7342,16 +7342,16 @@
         <v>MARAN</v>
       </c>
       <c r="B128" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D128" t="str">
         <v>Highway Y-Junction</v>
       </c>
       <c r="E128" s="5">
-        <v>3.5811111111111109</v>
+        <v>3.5811099999999998</v>
       </c>
       <c r="F128" s="5">
-        <v>102.76527777777778</v>
+        <v>102.76528</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -7359,16 +7359,16 @@
         <v>GAMBNG</v>
       </c>
       <c r="B129" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D129" t="str">
         <v>IIUM Gambang Complex</v>
       </c>
       <c r="E129" s="5">
-        <v>3.7233333333333336</v>
+        <v>3.7233299999999998</v>
       </c>
       <c r="F129" s="5">
-        <v>103.05861111111111</v>
+        <v>103.05861</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -7376,16 +7376,16 @@
         <v>LEPAR</v>
       </c>
       <c r="B130" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D130" t="str">
         <v>Lepar Bridge</v>
       </c>
       <c r="E130" s="5">
-        <v>3.4916666666666667</v>
+        <v>3.4916700000000001</v>
       </c>
       <c r="F130" s="5">
-        <v>103.09555555555555</v>
+        <v>103.09556000000001</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -7393,13 +7393,13 @@
         <v>MUADZM</v>
       </c>
       <c r="B131" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D131" t="str">
         <v>4-junction Flyover Kuanta</v>
       </c>
       <c r="E131" s="5">
-        <v>3.0722222222222224</v>
+        <v>3.0722200000000002</v>
       </c>
       <c r="F131" s="5">
         <v>103.07</v>
@@ -7410,16 +7410,16 @@
         <v>SGLEMB</v>
       </c>
       <c r="B132" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D132" t="str">
         <v>Football Field Sg Lembing</v>
       </c>
       <c r="E132" s="5">
-        <v>3.9152777777777779</v>
+        <v>3.9152800000000001</v>
       </c>
       <c r="F132" s="5">
-        <v>103.03388888888888</v>
+        <v>103.03389</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -7427,16 +7427,16 @@
         <v>LUNDU</v>
       </c>
       <c r="B133" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D133" t="str">
         <v>Lundu</v>
       </c>
       <c r="E133" s="5">
-        <v>1.6774999999999998</v>
+        <v>1.6775</v>
       </c>
       <c r="F133" s="5">
-        <v>109.85361111111111</v>
+        <v>109.85361</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -7444,16 +7444,16 @@
         <v>KGRMBG</v>
       </c>
       <c r="B134" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D134" t="str">
         <v>Kampung Rambungan</v>
       </c>
       <c r="E134" s="5">
-        <v>1.6919444444444445</v>
+        <v>1.69194</v>
       </c>
       <c r="F134" s="5">
-        <v>110.12472222222222</v>
+        <v>110.12472</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -7461,16 +7461,16 @@
         <v>KGSTNG</v>
       </c>
       <c r="B135" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D135" t="str">
         <v>Kampung Stinggang</v>
       </c>
       <c r="E135" s="5">
-        <v>1.4813888888888891</v>
+        <v>1.48139</v>
       </c>
       <c r="F135" s="5">
-        <v>110.03833333333333</v>
+        <v>110.03833</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -7478,16 +7478,16 @@
         <v>MUARTB</v>
       </c>
       <c r="B136" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D136" t="str">
         <v>Muara Tebas</v>
       </c>
       <c r="E136" s="5">
-        <v>1.6411111111111112</v>
+        <v>1.6411100000000001</v>
       </c>
       <c r="F136" s="5">
-        <v>110.48138888888889</v>
+        <v>110.48139</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -7495,16 +7495,16 @@
         <v>ABMSEM</v>
       </c>
       <c r="B137" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D137" t="str">
         <v>Abeam Semera</v>
       </c>
       <c r="E137" s="5">
-        <v>1.5522222222222222</v>
+        <v>1.5522199999999999</v>
       </c>
       <c r="F137" s="5">
-        <v>110.67027777777778</v>
+        <v>110.67028000000001</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -7512,16 +7512,16 @@
         <v>TEBEDU</v>
       </c>
       <c r="B138" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D138" t="str">
         <v>Tebedu</v>
       </c>
       <c r="E138" s="5">
-        <v>1.0166666666666666</v>
+        <v>1.01667</v>
       </c>
       <c r="F138" s="5">
-        <v>110.35749999999999</v>
+        <v>110.3575</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -7529,16 +7529,16 @@
         <v>SERIAN</v>
       </c>
       <c r="B139" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D139" t="str">
         <v>Serian</v>
       </c>
       <c r="E139" s="5">
-        <v>1.1697222222222223</v>
+        <v>1.1697200000000001</v>
       </c>
       <c r="F139" s="5">
-        <v>110.56722222222221</v>
+        <v>110.56722000000001</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -7546,16 +7546,16 @@
         <v>SIMUNJ</v>
       </c>
       <c r="B140" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D140" t="str">
         <v>Simunjan</v>
       </c>
       <c r="E140" s="5">
-        <v>1.3911111111111112</v>
+        <v>1.3911100000000001</v>
       </c>
       <c r="F140" s="5">
-        <v>110.74944444444445</v>
+        <v>110.74944000000001</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -7563,16 +7563,16 @@
         <v>KGTRSO</v>
       </c>
       <c r="B141" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D141" t="str">
         <v>Kampung Triso</v>
       </c>
       <c r="E141" s="5">
-        <v>1.5272222222222223</v>
+        <v>1.52722</v>
       </c>
       <c r="F141" s="5">
-        <v>111.00361111111111</v>
+        <v>111.00360999999999</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -7580,7 +7580,7 @@
         <v>KGKUAP</v>
       </c>
       <c r="B142" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D142" t="str">
         <v>Kampung Kuap</v>
@@ -7589,7 +7589,7 @@
         <v>1.4075</v>
       </c>
       <c r="F142" s="5">
-        <v>110.36333333333333</v>
+        <v>110.36333</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -7597,16 +7597,16 @@
         <v>BTSIOL</v>
       </c>
       <c r="B143" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D143" t="str">
         <v>Bukit Siol</v>
       </c>
       <c r="E143" s="5">
-        <v>1.5788888888888888</v>
+        <v>1.5788899999999999</v>
       </c>
       <c r="F143" s="5">
-        <v>110.35361111111111</v>
+        <v>110.35361</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -7614,16 +7614,16 @@
         <v>ABMNRB</v>
       </c>
       <c r="B144" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D144" t="str">
         <v>Abeam Narub</v>
       </c>
       <c r="E144" s="5">
-        <v>2.6433333333333331</v>
+        <v>2.6433300000000002</v>
       </c>
       <c r="F144" s="5">
-        <v>112.07666666666667</v>
+        <v>112.07666999999999</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -7631,16 +7631,16 @@
         <v>NGATMN</v>
       </c>
       <c r="B145" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D145" t="str">
         <v>Nanga Tamin</v>
       </c>
       <c r="E145" s="5">
-        <v>2.5083333333333333</v>
+        <v>2.5083299999999999</v>
       </c>
       <c r="F145" s="5">
-        <v>112.07166666666666</v>
+        <v>112.07167</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -7648,16 +7648,16 @@
         <v>LASSAR</v>
       </c>
       <c r="B146" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D146" t="str">
         <v>Lassa River</v>
       </c>
       <c r="E146" s="5">
-        <v>2.4683333333333333</v>
+        <v>2.4683299999999999</v>
       </c>
       <c r="F146" s="5">
-        <v>111.60833333333333</v>
+        <v>111.60833</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -7665,16 +7665,16 @@
         <v>SLNGAU</v>
       </c>
       <c r="B147" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D147" t="str">
         <v>Selangau</v>
       </c>
       <c r="E147" s="5">
-        <v>2.5233333333333334</v>
+        <v>2.5233300000000001</v>
       </c>
       <c r="F147" s="5">
-        <v>112.31833333333333</v>
+        <v>112.31833</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -7682,16 +7682,16 @@
         <v>STAPNG</v>
       </c>
       <c r="B148" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D148" t="str">
         <v>Stapang</v>
       </c>
       <c r="E148" s="5">
-        <v>2.3983333333333334</v>
+        <v>2.3983300000000001</v>
       </c>
       <c r="F148" s="5">
-        <v>112.13166666666666</v>
+        <v>112.13167</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -7699,7 +7699,7 @@
         <v>TRVRJT</v>
       </c>
       <c r="B149" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D149" t="str">
         <v>T River Junction</v>
@@ -7716,7 +7716,7 @@
         <v>PDUDNG</v>
       </c>
       <c r="B150" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D150" t="str">
         <v>Pulau Dudong</v>
@@ -7725,7 +7725,7 @@
         <v>2.19</v>
       </c>
       <c r="F150" s="5">
-        <v>111.93666666666667</v>
+        <v>111.93667000000001</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -7733,16 +7733,16 @@
         <v>MERUAN</v>
       </c>
       <c r="B151" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D151" t="str">
         <v>Meruan</v>
       </c>
       <c r="E151" s="5">
-        <v>2.3016666666666663</v>
+        <v>2.3016700000000001</v>
       </c>
       <c r="F151" s="5">
-        <v>112.05666666666666</v>
+        <v>112.05667</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -7750,7 +7750,7 @@
         <v>LENG</v>
       </c>
       <c r="B152" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D152" t="str">
         <v>Leng</v>
@@ -7759,7 +7759,7 @@
         <v>2.0649999999999999</v>
       </c>
       <c r="F152" s="5">
-        <v>111.76666666666667</v>
+        <v>111.76667</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -7767,16 +7767,16 @@
         <v>PAKAN</v>
       </c>
       <c r="B153" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D153" t="str">
         <v>Pakan Road</v>
       </c>
       <c r="E153" s="5">
-        <v>1.9816666666666667</v>
+        <v>1.98167</v>
       </c>
       <c r="F153" s="5">
-        <v>111.64833333333334</v>
+        <v>111.64833</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -7784,13 +7784,13 @@
         <v>DURIN</v>
       </c>
       <c r="B154" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D154" t="str">
         <v>Durin Town</v>
       </c>
       <c r="E154" s="5">
-        <v>2.1333333333333333</v>
+        <v>2.1333299999999999</v>
       </c>
       <c r="F154" s="5">
         <v>111.97</v>
@@ -7801,7 +7801,7 @@
         <v>KANOWT</v>
       </c>
       <c r="B155" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D155" t="str">
         <v>Kanowit</v>
@@ -7810,7 +7810,7 @@
         <v>2.0950000000000002</v>
       </c>
       <c r="F155" s="5">
-        <v>112.15166666666667</v>
+        <v>112.15167</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -7818,16 +7818,16 @@
         <v>PENARK</v>
       </c>
       <c r="B156" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D156" t="str">
         <v>Penarik</v>
       </c>
       <c r="E156" s="5">
-        <v>5.5952777777777776</v>
+        <v>5.5952799999999998</v>
       </c>
       <c r="F156" s="5">
-        <v>102.80666666666666</v>
+        <v>102.80667</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -7835,16 +7835,16 @@
         <v>KGSETI</v>
       </c>
       <c r="B157" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D157" t="str">
         <v>Kampung Setiu Lama</v>
       </c>
       <c r="E157" s="5">
-        <v>5.6813888888888888</v>
+        <v>5.6813900000000004</v>
       </c>
       <c r="F157" s="5">
-        <v>102.71277777777777</v>
+        <v>102.71278</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -7852,7 +7852,7 @@
         <v>BETLTG</v>
       </c>
       <c r="B158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D158" t="str">
         <v>Beting Lintang</v>
@@ -7861,7 +7861,7 @@
         <v>5.7374999999999998</v>
       </c>
       <c r="F158" s="5">
-        <v>102.65083333333334</v>
+        <v>102.65083</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -7869,16 +7869,16 @@
         <v>PRU</v>
       </c>
       <c r="B159" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D159" t="str">
         <v>Pulau Ru</v>
       </c>
       <c r="E159" s="5">
-        <v>5.8308333333333335</v>
+        <v>5.8308299999999997</v>
       </c>
       <c r="F159" s="5">
-        <v>102.60638888888889</v>
+        <v>102.60639</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -7886,16 +7886,16 @@
         <v>KGBSUT</v>
       </c>
       <c r="B160" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D160" t="str">
         <v>Kampung Besut</v>
       </c>
       <c r="E160" s="5">
-        <v>5.8319444444444439</v>
+        <v>5.8319400000000003</v>
       </c>
       <c r="F160" s="5">
-        <v>102.54861111111111</v>
+        <v>102.54861</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -7903,13 +7903,13 @@
         <v>KGTOKB</v>
       </c>
       <c r="B161" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D161" t="str">
         <v>Kampung Tok Bali</v>
       </c>
       <c r="E161" s="5">
-        <v>5.8844444444444441</v>
+        <v>5.8844399999999997</v>
       </c>
       <c r="F161" s="5">
         <v>102.485</v>
@@ -7920,16 +7920,16 @@
         <v>KGKNGS</v>
       </c>
       <c r="B162" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D162" t="str">
         <v>Kampung Kandis</v>
       </c>
       <c r="E162" s="5">
-        <v>5.9480555555555554</v>
+        <v>5.9480599999999999</v>
       </c>
       <c r="F162" s="5">
-        <v>102.44277777777778</v>
+        <v>102.44278</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -7937,13 +7937,13 @@
         <v>BACHOK</v>
       </c>
       <c r="B163" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D163" t="str">
         <v>Bachok</v>
       </c>
       <c r="E163" s="5">
-        <v>6.0649999999999995</v>
+        <v>6.0650000000000004</v>
       </c>
       <c r="F163" s="5">
         <v>102.39</v>
@@ -7954,16 +7954,16 @@
         <v>KTBHTW</v>
       </c>
       <c r="B164" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D164" t="str">
         <v>Kota Bharu Town</v>
       </c>
       <c r="E164" s="5">
-        <v>6.1319444444444438</v>
+        <v>6.1319400000000002</v>
       </c>
       <c r="F164" s="5">
-        <v>102.23194444444445</v>
+        <v>102.23193999999999</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -7971,16 +7971,16 @@
         <v>KLKRAI</v>
       </c>
       <c r="B165" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D165" t="str">
         <v>Kuala Krai</v>
       </c>
       <c r="E165" s="5">
-        <v>5.5991666666666662</v>
+        <v>5.59917</v>
       </c>
       <c r="F165" s="5">
-        <v>102.23666666666666</v>
+        <v>102.23667</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -7988,16 +7988,16 @@
         <v>TANAMR</v>
       </c>
       <c r="B166" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D166" t="str">
         <v>Tanah Merah</v>
       </c>
       <c r="E166" s="5">
-        <v>5.7747222222222225</v>
+        <v>5.7747200000000003</v>
       </c>
       <c r="F166" s="5">
-        <v>102.12666666666667</v>
+        <v>102.12667</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -8005,16 +8005,16 @@
         <v>BTMLTG</v>
       </c>
       <c r="B167" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D167" t="str">
         <v>Bukit Melintang</v>
       </c>
       <c r="E167" s="5">
-        <v>5.7013888888888893</v>
+        <v>5.70139</v>
       </c>
       <c r="F167" s="5">
-        <v>101.72361111111111</v>
+        <v>101.72360999999999</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -8022,16 +8022,16 @@
         <v>JELI</v>
       </c>
       <c r="B168" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D168" t="str">
         <v>Jeli</v>
       </c>
       <c r="E168" s="5">
-        <v>5.7013888888888893</v>
+        <v>5.70139</v>
       </c>
       <c r="F168" s="5">
-        <v>101.82805555555555</v>
+        <v>101.82805999999999</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -8039,7 +8039,7 @@
         <v>KUAH</v>
       </c>
       <c r="B169" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D169" t="str">
         <v>Kuah</v>
@@ -8056,16 +8056,16 @@
         <v>PTIMUN</v>
       </c>
       <c r="B170" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D170" t="str">
         <v>Pulau Timun</v>
       </c>
       <c r="E170" s="5">
-        <v>6.3130555555555556</v>
+        <v>6.3130600000000001</v>
       </c>
       <c r="F170" s="5">
-        <v>99.914722222222224</v>
+        <v>99.914720000000003</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -8073,16 +8073,16 @@
         <v>ABMTBA</v>
       </c>
       <c r="B171" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D171" t="str">
         <v>Abeam Pulau Tuba</v>
       </c>
       <c r="E171" s="5">
-        <v>6.2672222222222222</v>
+        <v>6.26722</v>
       </c>
       <c r="F171" s="5">
-        <v>99.888611111111118</v>
+        <v>99.88861</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -8090,7 +8090,7 @@
         <v>PPAYA</v>
       </c>
       <c r="B172" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D172" t="str">
         <v>Pulau Paya</v>
@@ -8107,16 +8107,16 @@
         <v>KLPRLS</v>
       </c>
       <c r="B173" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D173" t="str">
         <v>Kuala Perlis</v>
       </c>
       <c r="E173" s="5">
-        <v>6.3986111111111112</v>
+        <v>6.3986099999999997</v>
       </c>
       <c r="F173" s="5">
-        <v>100.1388888888889</v>
+        <v>100.13889</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -8124,7 +8124,7 @@
         <v>AYRHTM</v>
       </c>
       <c r="B174" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D174" t="str">
         <v>Ayer Hitam</v>
@@ -8133,7 +8133,7 @@
         <v>6.2374999999999998</v>
       </c>
       <c r="F174" s="5">
-        <v>100.24833333333333</v>
+        <v>100.24833</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -8141,7 +8141,7 @@
         <v>KLKDAH</v>
       </c>
       <c r="B175" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D175" t="str">
         <v>Kuala Kedah</v>
@@ -8158,16 +8158,16 @@
         <v>SPGEMP</v>
       </c>
       <c r="B176" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D176" t="str">
         <v>Simpang Empat</v>
       </c>
       <c r="E176" s="5">
-        <v>6.0241666666666669</v>
+        <v>6.0241699999999998</v>
       </c>
       <c r="F176" s="5">
-        <v>100.38194444444444</v>
+        <v>100.38194</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -8175,16 +8175,16 @@
         <v>KTSASE</v>
       </c>
       <c r="B177" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D177" t="str">
         <v>Kota Sarang Semut</v>
       </c>
       <c r="E177" s="5">
-        <v>5.9744444444444449</v>
+        <v>5.9744400000000004</v>
       </c>
       <c r="F177" s="5">
-        <v>100.39972222222222</v>
+        <v>100.39972</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -8192,16 +8192,16 @@
         <v>BTHMPR</v>
       </c>
       <c r="B178" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D178" t="str">
         <v>Batu Hampar</v>
       </c>
       <c r="E178">
-        <v>4.5322222222222219</v>
+        <v>4.5322199999999997</v>
       </c>
       <c r="F178">
-        <v>100.71277777777777</v>
+        <v>100.71278</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -8209,16 +8209,16 @@
         <v>PARIT</v>
       </c>
       <c r="B179" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D179" t="str">
         <v>Parit</v>
       </c>
       <c r="E179">
-        <v>4.4830555555555556</v>
+        <v>4.48306</v>
       </c>
       <c r="F179">
-        <v>100.91083333333334</v>
+        <v>100.91083</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -8226,16 +8226,16 @@
         <v>BTGJAH</v>
       </c>
       <c r="B180" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D180" t="str">
         <v>Batu Gajah</v>
       </c>
       <c r="E180">
-        <v>4.469444444444445</v>
+        <v>4.4694399999999996</v>
       </c>
       <c r="F180">
-        <v>101.0436111111111</v>
+        <v>101.04361</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -8243,7 +8243,7 @@
         <v>GOPENG</v>
       </c>
       <c r="B181" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D181" t="str">
         <v>Gopeng</v>
@@ -8252,7 +8252,7 @@
         <v>4.46</v>
       </c>
       <c r="F181">
-        <v>101.16000000000001</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -8260,7 +8260,7 @@
         <v>KAMPAR</v>
       </c>
       <c r="B182" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D182" t="str">
         <v>Kampar</v>
@@ -8277,7 +8277,7 @@
         <v>TLINTN</v>
       </c>
       <c r="B183" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D183" t="str">
         <v>Teluk Intan</v>
@@ -8294,16 +8294,16 @@
         <v>BIDOR</v>
       </c>
       <c r="B184" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D184" t="str">
         <v>Bidor</v>
       </c>
       <c r="E184">
-        <v>4.1133333333333333</v>
+        <v>4.1133300000000004</v>
       </c>
       <c r="F184">
-        <v>101.28583333333333</v>
+        <v>101.28583</v>
       </c>
     </row>
   </sheetData>
@@ -8335,19 +8335,19 @@
         <v>245</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>268</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>223</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>218</v>
@@ -8375,7 +8375,7 @@
         <v>SG_BESAR</v>
       </c>
       <c r="F2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G2" t="str">
         <f t="shared" ref="G2:G33" si="1">B2</f>
@@ -8413,7 +8413,7 @@
         <v>KUALA_SELANGOR</v>
       </c>
       <c r="F3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" si="1"/>
@@ -8451,7 +8451,7 @@
         <v>KAPAR</v>
       </c>
       <c r="F4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="1"/>
@@ -8489,7 +8489,7 @@
         <v>PORT_KLANG</v>
       </c>
       <c r="F5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="1"/>
@@ -8527,7 +8527,7 @@
         <v>MORIB</v>
       </c>
       <c r="F6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="1"/>
@@ -8565,7 +8565,7 @@
         <v>TJ_SEPAT</v>
       </c>
       <c r="F7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="1"/>
@@ -8603,7 +8603,7 @@
         <v>TJ_TUAN_(CAPE_RACHARDO)</v>
       </c>
       <c r="F8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" si="1"/>
@@ -8641,7 +8641,7 @@
         <v>SLIM_RIVER</v>
       </c>
       <c r="F9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="1"/>
@@ -8679,7 +8679,7 @@
         <v>TJ_MALIM</v>
       </c>
       <c r="F10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="1"/>
@@ -8717,7 +8717,7 @@
         <v>RAWANG</v>
       </c>
       <c r="F11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" si="1"/>
@@ -8755,7 +8755,7 @@
         <v>BATU_CAVES</v>
       </c>
       <c r="F12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="1"/>
@@ -8793,7 +8793,7 @@
         <v>SG_BESI</v>
       </c>
       <c r="F13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
@@ -8831,7 +8831,7 @@
         <v>KAJANG</v>
       </c>
       <c r="F14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="1"/>
@@ -8869,7 +8869,7 @@
         <v>SEREMBAN</v>
       </c>
       <c r="F15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="1"/>
@@ -8907,7 +8907,7 @@
         <v>BENTONG</v>
       </c>
       <c r="F16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" si="1"/>
@@ -8945,7 +8945,7 @@
         <v>RANTAU</v>
       </c>
       <c r="F17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="1"/>
@@ -8983,7 +8983,7 @@
         <v>KUALA_KELAWANG</v>
       </c>
       <c r="F18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="1"/>
@@ -9021,7 +9021,7 @@
         <v>PETALING_JAYA</v>
       </c>
       <c r="F19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="1"/>
@@ -9059,7 +9059,7 @@
         <v>BT_LANJAN</v>
       </c>
       <c r="F20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="1"/>
@@ -9097,7 +9097,7 @@
         <v>PUNCAK_PERDANA</v>
       </c>
       <c r="F21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="1"/>
@@ -9135,7 +9135,7 @@
         <v>SHAH_ALAM</v>
       </c>
       <c r="F22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="1"/>
@@ -9173,7 +9173,7 @@
         <v>KUANG</v>
       </c>
       <c r="F23" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="1"/>
@@ -9211,7 +9211,7 @@
         <v>NIBONG_GILA</v>
       </c>
       <c r="F24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="1"/>
@@ -9249,7 +9249,7 @@
         <v>TITIWANGSA</v>
       </c>
       <c r="F25" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="1"/>
@@ -9287,7 +9287,7 @@
         <v>SEGAMBUT</v>
       </c>
       <c r="F26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" si="1"/>
@@ -9325,7 +9325,7 @@
         <v>UTM_MOSQUE</v>
       </c>
       <c r="F27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="1"/>
@@ -9363,7 +9363,7 @@
         <v>BENUT</v>
       </c>
       <c r="F28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="1"/>
@@ -9401,7 +9401,7 @@
         <v>KULAI_TOL_PLAZA</v>
       </c>
       <c r="F29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G29" t="str">
         <f t="shared" si="1"/>
@@ -9439,7 +9439,7 @@
         <v>EAST_JOHOR_BAHRU_AIRFIELD</v>
       </c>
       <c r="F30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="1"/>
@@ -9477,7 +9477,7 @@
         <v>KOTA_TINGGI_BRIDGE</v>
       </c>
       <c r="F31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="1"/>
@@ -9515,7 +9515,7 @@
         <v>EAST_KG_SG_TIRAM</v>
       </c>
       <c r="F32" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="1"/>
@@ -9553,7 +9553,7 @@
         <v>EAST_JOHOR_BAHRU_TOWN</v>
       </c>
       <c r="F33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
@@ -9591,7 +9591,7 @@
         <v>FELDA_ULU_TEBRAU</v>
       </c>
       <c r="F34" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" ref="G34:G65" si="6">B34</f>
@@ -9629,7 +9629,7 @@
         <v>TEBRAU_CITY_MALL</v>
       </c>
       <c r="F35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="6"/>
@@ -9650,10 +9650,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>271</v>
+        <v>623</v>
       </c>
       <c r="B36" t="s">
-        <v>271</v>
+        <v>623</v>
       </c>
       <c r="C36" t="s">
         <v>67</v>
@@ -9667,15 +9667,15 @@
         <v>SOUTH_KG_SEMANGAR</v>
       </c>
       <c r="F36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="6"/>
-        <v>South Of Kg Semangar</v>
+        <v>South of Kg Semangar</v>
       </c>
       <c r="H36" t="str">
         <f t="shared" si="4"/>
-        <v>South Of Kg Semangar</v>
+        <v>South of Kg Semangar</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="7"/>
@@ -9705,7 +9705,7 @@
         <v>KG_SEDILI_BESAR</v>
       </c>
       <c r="F37" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="6"/>
@@ -9743,7 +9743,7 @@
         <v>SIMPANG_RENGGAM_TOWN</v>
       </c>
       <c r="F38" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G38" t="str">
         <f t="shared" si="6"/>
@@ -9781,7 +9781,7 @@
         <v>AIR_HITAM</v>
       </c>
       <c r="F39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="6"/>
@@ -9819,7 +9819,7 @@
         <v>YONG_PENG</v>
       </c>
       <c r="F40" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="6"/>
@@ -9857,7 +9857,7 @@
         <v>POINT_XRAY</v>
       </c>
       <c r="F41" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G41" t="str">
         <f t="shared" si="6"/>
@@ -9895,7 +9895,7 @@
         <v>TASS_ANDRASSY</v>
       </c>
       <c r="F42" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="6"/>
@@ -9933,7 +9933,7 @@
         <v>OLD_AIRPORT</v>
       </c>
       <c r="F43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="6"/>
@@ -9971,7 +9971,7 @@
         <v>SEBATIK_IS</v>
       </c>
       <c r="F44" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G44" t="str">
         <f t="shared" si="6"/>
@@ -10009,7 +10009,7 @@
         <v>KALABAKAN</v>
       </c>
       <c r="F45" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G45" t="str">
         <f t="shared" si="6"/>
@@ -10047,7 +10047,7 @@
         <v>BALUNG</v>
       </c>
       <c r="F46" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G46" t="str">
         <f t="shared" si="6"/>
@@ -10085,7 +10085,7 @@
         <v>KAWA_HILL</v>
       </c>
       <c r="F47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G47" t="str">
         <f t="shared" si="6"/>
@@ -10106,10 +10106,10 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C48" t="s">
         <v>95</v>
@@ -10123,7 +10123,7 @@
         <v>MT_PYRAMID</v>
       </c>
       <c r="F48" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G48" t="str">
         <f t="shared" si="6"/>
@@ -10161,7 +10161,7 @@
         <v>BATURONG</v>
       </c>
       <c r="F49" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G49" t="str">
         <f t="shared" si="6"/>
@@ -10199,7 +10199,7 @@
         <v>DANUM</v>
       </c>
       <c r="F50" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G50" t="str">
         <f t="shared" si="6"/>
@@ -10237,7 +10237,7 @@
         <v>JUNCTION_(49KM)</v>
       </c>
       <c r="F51" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G51" t="str">
         <f t="shared" si="6"/>
@@ -10275,7 +10275,7 @@
         <v>KG_AMAN</v>
       </c>
       <c r="F52" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G52" t="str">
         <f t="shared" si="6"/>
@@ -10313,7 +10313,7 @@
         <v>TJ_BATAI</v>
       </c>
       <c r="F53" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G53" t="str">
         <f t="shared" si="6"/>
@@ -10351,7 +10351,7 @@
         <v>SADDLE_HILL</v>
       </c>
       <c r="F54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G54" t="str">
         <f t="shared" si="6"/>
@@ -10389,7 +10389,7 @@
         <v>NAGOS</v>
       </c>
       <c r="F55" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G55" t="str">
         <f t="shared" si="6"/>
@@ -10427,7 +10427,7 @@
         <v>SEMPORNA</v>
       </c>
       <c r="F56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G56" t="str">
         <f t="shared" si="6"/>
@@ -10465,7 +10465,7 @@
         <v>GAYA_IS</v>
       </c>
       <c r="F57" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G57" t="str">
         <f t="shared" si="6"/>
@@ -10503,7 +10503,7 @@
         <v>SIPADAN_IS</v>
       </c>
       <c r="F58" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G58" t="str">
         <f t="shared" si="6"/>
@@ -10541,7 +10541,7 @@
         <v>BANDAR_INDAH_(ROAD_JUNCTION)</v>
       </c>
       <c r="F59" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G59" t="str">
         <f t="shared" si="6"/>
@@ -10579,7 +10579,7 @@
         <v>KAMPONG_TOBANKA</v>
       </c>
       <c r="F60" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G60" t="str">
         <f t="shared" si="6"/>
@@ -10617,7 +10617,7 @@
         <v>BAI_IS</v>
       </c>
       <c r="F61" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G61" t="str">
         <f t="shared" si="6"/>
@@ -10655,7 +10655,7 @@
         <v>TJ_BIDADARI</v>
       </c>
       <c r="F62" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G62" t="str">
         <f t="shared" si="6"/>
@@ -10693,7 +10693,7 @@
         <v>KUALA_KINABATANGAN_BESAR</v>
       </c>
       <c r="F63" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G63" t="str">
         <f t="shared" si="6"/>
@@ -10731,7 +10731,7 @@
         <v>KG_BILIT</v>
       </c>
       <c r="F64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G64" t="str">
         <f t="shared" si="6"/>
@@ -10769,7 +10769,7 @@
         <v>SG_SEGUNTOR</v>
       </c>
       <c r="F65" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G65" t="str">
         <f t="shared" si="6"/>
@@ -10807,7 +10807,7 @@
         <v>KOTA_KINABATANGAN</v>
       </c>
       <c r="F66" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G66" t="str">
         <f t="shared" ref="G66:G97" si="9">B66</f>
@@ -10845,7 +10845,7 @@
         <v>KG_KUALA_LOKAN</v>
       </c>
       <c r="F67" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G67" t="str">
         <f t="shared" si="9"/>
@@ -10883,7 +10883,7 @@
         <v>MILE_32_RD_JUNCTION</v>
       </c>
       <c r="F68" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G68" t="str">
         <f t="shared" si="9"/>
@@ -10921,7 +10921,7 @@
         <v>TELUPID</v>
       </c>
       <c r="F69" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G69" t="str">
         <f t="shared" si="9"/>
@@ -10942,10 +10942,10 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C70" t="s">
         <v>137</v>
@@ -10959,7 +10959,7 @@
         <v>KG_GUMGUM_LAUT</v>
       </c>
       <c r="F70" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G70" t="str">
         <f t="shared" si="9"/>
@@ -10997,7 +10997,7 @@
         <v>KG_SEMAWANG</v>
       </c>
       <c r="F71" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="9"/>
@@ -11035,7 +11035,7 @@
         <v>BELURAN</v>
       </c>
       <c r="F72" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G72" t="str">
         <f t="shared" si="9"/>
@@ -11073,7 +11073,7 @@
         <v>KENAWI_IS</v>
       </c>
       <c r="F73" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G73" t="str">
         <f t="shared" si="9"/>
@@ -11111,7 +11111,7 @@
         <v>KG_SG-SG</v>
       </c>
       <c r="F74" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G74" t="str">
         <f t="shared" si="9"/>
@@ -11149,7 +11149,7 @@
         <v>KG_TERUSAN</v>
       </c>
       <c r="F75" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G75" t="str">
         <f t="shared" si="9"/>
@@ -11187,7 +11187,7 @@
         <v>SELINGAN_IS</v>
       </c>
       <c r="F76" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G76" t="str">
         <f t="shared" si="9"/>
@@ -11225,7 +11225,7 @@
         <v>LANKAYAN_IS</v>
       </c>
       <c r="F77" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G77" t="str">
         <f t="shared" si="9"/>
@@ -11263,7 +11263,7 @@
         <v>SOUTH_BERHALA_IS</v>
       </c>
       <c r="F78" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G78" t="str">
         <f t="shared" si="9"/>
@@ -11301,7 +11301,7 @@
         <v>LUANG_MANIS</v>
       </c>
       <c r="F79" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G79" t="str">
         <f t="shared" si="9"/>
@@ -11339,7 +11339,7 @@
         <v>PAMAGUAN_PRIMARY_SCHOOL</v>
       </c>
       <c r="F80" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G80" t="str">
         <f t="shared" si="9"/>
@@ -11377,7 +11377,7 @@
         <v>PORT_WELD</v>
       </c>
       <c r="F81" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G81" t="str">
         <f t="shared" si="9"/>
@@ -11415,7 +11415,7 @@
         <v>TJ_PIANDANG</v>
       </c>
       <c r="F82" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G82" t="str">
         <f t="shared" si="9"/>
@@ -11453,7 +11453,7 @@
         <v>SOUTH_P_AMAN</v>
       </c>
       <c r="F83" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G83" t="str">
         <f t="shared" si="9"/>
@@ -11491,7 +11491,7 @@
         <v>KEDAH_PEAK_WEST</v>
       </c>
       <c r="F84" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G84" t="str">
         <f t="shared" si="9"/>
@@ -11529,7 +11529,7 @@
         <v>KUALA_SG_MUDA</v>
       </c>
       <c r="F85" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G85" t="str">
         <f t="shared" si="9"/>
@@ -11567,7 +11567,7 @@
         <v>NORTH_GEORGE_TOWN</v>
       </c>
       <c r="F86" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G86" t="str">
         <f t="shared" si="9"/>
@@ -11605,7 +11605,7 @@
         <v>WEST_P_GAYA</v>
       </c>
       <c r="F87" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G87" t="str">
         <f t="shared" si="9"/>
@@ -11643,7 +11643,7 @@
         <v>P_SULUG</v>
       </c>
       <c r="F88" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G88" t="str">
         <f t="shared" si="9"/>
@@ -11681,7 +11681,7 @@
         <v>P_TIGA</v>
       </c>
       <c r="F89" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G89" t="str">
         <f t="shared" si="9"/>
@@ -11719,7 +11719,7 @@
         <v>KUALA_PENYU</v>
       </c>
       <c r="F90" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G90" t="str">
         <f t="shared" si="9"/>
@@ -11757,7 +11757,7 @@
         <v>BONGAWAN</v>
       </c>
       <c r="F91" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G91" t="str">
         <f t="shared" si="9"/>
@@ -11795,7 +11795,7 @@
         <v>EAST_PAPAR</v>
       </c>
       <c r="F92" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G92" t="str">
         <f t="shared" si="9"/>
@@ -11833,7 +11833,7 @@
         <v>EAST_KAWANG</v>
       </c>
       <c r="F93" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G93" t="str">
         <f t="shared" si="9"/>
@@ -11871,7 +11871,7 @@
         <v>EAST_KINARUT_TOWN</v>
       </c>
       <c r="F94" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G94" t="str">
         <f t="shared" si="9"/>
@@ -11909,7 +11909,7 @@
         <v>KEPAYAN</v>
       </c>
       <c r="F95" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G95" t="str">
         <f t="shared" si="9"/>
@@ -11947,7 +11947,7 @@
         <v>EAST_INANAM_TOWN</v>
       </c>
       <c r="F96" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G96" t="str">
         <f t="shared" si="9"/>
@@ -11985,7 +11985,7 @@
         <v>EAST_TELIPOK</v>
       </c>
       <c r="F97" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G97" t="str">
         <f t="shared" si="9"/>
@@ -12023,7 +12023,7 @@
         <v>KG_KIULU</v>
       </c>
       <c r="F98" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G98" t="str">
         <f t="shared" ref="G98:G129" si="14">B98</f>
@@ -12061,7 +12061,7 @@
         <v>KG_BALABAKAN</v>
       </c>
       <c r="F99" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G99" t="str">
         <f t="shared" si="14"/>
@@ -12099,7 +12099,7 @@
         <v>RANAU</v>
       </c>
       <c r="F100" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G100" t="str">
         <f t="shared" si="14"/>
@@ -12137,7 +12137,7 @@
         <v>WEST_HILL_1040</v>
       </c>
       <c r="F101" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G101" t="str">
         <f t="shared" si="14"/>
@@ -12175,7 +12175,7 @@
         <v>TJ_DALIT</v>
       </c>
       <c r="F102" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G102" t="str">
         <f t="shared" si="14"/>
@@ -12213,7 +12213,7 @@
         <v>KOTA_BELUD</v>
       </c>
       <c r="F103" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G103" t="str">
         <f t="shared" si="14"/>
@@ -12251,7 +12251,7 @@
         <v>TERENDAK</v>
       </c>
       <c r="F104" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G104" t="str">
         <f t="shared" si="14"/>
@@ -12289,7 +12289,7 @@
         <v>REMBIA</v>
       </c>
       <c r="F105" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G105" t="str">
         <f t="shared" si="14"/>
@@ -12327,7 +12327,7 @@
         <v>TAMPIN</v>
       </c>
       <c r="F106" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G106" t="str">
         <f t="shared" si="14"/>
@@ -12365,7 +12365,7 @@
         <v>CHIN_CHIN</v>
       </c>
       <c r="F107" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G107" t="str">
         <f t="shared" si="14"/>
@@ -12403,7 +12403,7 @@
         <v>BT_BERUANG</v>
       </c>
       <c r="F108" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G108" t="str">
         <f t="shared" si="14"/>
@@ -12441,7 +12441,7 @@
         <v>UMBAI</v>
       </c>
       <c r="F109" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G109" t="str">
         <f t="shared" si="14"/>
@@ -12479,7 +12479,7 @@
         <v>MALACCA_CITY</v>
       </c>
       <c r="F110" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G110" t="str">
         <f t="shared" si="14"/>
@@ -12517,7 +12517,7 @@
         <v>MUAR</v>
       </c>
       <c r="F111" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G111" t="str">
         <f t="shared" si="14"/>
@@ -12555,7 +12555,7 @@
         <v>TANGKAK</v>
       </c>
       <c r="F112" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G112" t="str">
         <f t="shared" si="14"/>
@@ -12593,7 +12593,7 @@
         <v>PAGOH</v>
       </c>
       <c r="F113" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G113" t="str">
         <f t="shared" si="14"/>
@@ -12614,13 +12614,13 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>399</v>
+      </c>
+      <c r="B114" t="s">
+        <v>399</v>
+      </c>
+      <c r="C114" t="s">
         <v>400</v>
-      </c>
-      <c r="B114" t="s">
-        <v>400</v>
-      </c>
-      <c r="C114" t="s">
-        <v>401</v>
       </c>
       <c r="D114" t="str">
         <f t="shared" si="13"/>
@@ -12631,7 +12631,7 @@
         <v>PENARIK</v>
       </c>
       <c r="F114" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G114" t="str">
         <f t="shared" si="14"/>
@@ -12652,13 +12652,13 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>401</v>
+      </c>
+      <c r="B115" t="s">
+        <v>401</v>
+      </c>
+      <c r="C115" t="s">
         <v>402</v>
-      </c>
-      <c r="B115" t="s">
-        <v>402</v>
-      </c>
-      <c r="C115" t="s">
-        <v>403</v>
       </c>
       <c r="D115" t="str">
         <f t="shared" si="13"/>
@@ -12669,7 +12669,7 @@
         <v>BANDAR_PERMAISURI</v>
       </c>
       <c r="F115" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G115" t="str">
         <f t="shared" si="14"/>
@@ -12690,13 +12690,13 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>403</v>
+      </c>
+      <c r="B116" t="s">
+        <v>403</v>
+      </c>
+      <c r="C116" t="s">
         <v>404</v>
-      </c>
-      <c r="B116" t="s">
-        <v>404</v>
-      </c>
-      <c r="C116" t="s">
-        <v>405</v>
       </c>
       <c r="D116" t="str">
         <f t="shared" si="13"/>
@@ -12707,7 +12707,7 @@
         <v>KG_MERANG</v>
       </c>
       <c r="F116" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G116" t="str">
         <f t="shared" si="14"/>
@@ -12728,13 +12728,13 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>405</v>
+      </c>
+      <c r="B117" t="s">
+        <v>405</v>
+      </c>
+      <c r="C117" t="s">
         <v>406</v>
-      </c>
-      <c r="B117" t="s">
-        <v>406</v>
-      </c>
-      <c r="C117" t="s">
-        <v>407</v>
       </c>
       <c r="D117" t="str">
         <f t="shared" si="13"/>
@@ -12745,7 +12745,7 @@
         <v>BATU_RAKIT</v>
       </c>
       <c r="F117" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G117" t="str">
         <f t="shared" si="14"/>
@@ -12766,13 +12766,13 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>407</v>
+      </c>
+      <c r="B118" t="s">
+        <v>407</v>
+      </c>
+      <c r="C118" t="s">
         <v>408</v>
-      </c>
-      <c r="B118" t="s">
-        <v>408</v>
-      </c>
-      <c r="C118" t="s">
-        <v>409</v>
       </c>
       <c r="D118" t="str">
         <f t="shared" si="13"/>
@@ -12783,7 +12783,7 @@
         <v>KG_CHENERING</v>
       </c>
       <c r="F118" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G118" t="str">
         <f t="shared" si="14"/>
@@ -12804,13 +12804,13 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>409</v>
+      </c>
+      <c r="B119" t="s">
+        <v>409</v>
+      </c>
+      <c r="C119" t="s">
         <v>410</v>
-      </c>
-      <c r="B119" t="s">
-        <v>410</v>
-      </c>
-      <c r="C119" t="s">
-        <v>411</v>
       </c>
       <c r="D119" t="str">
         <f t="shared" si="13"/>
@@ -12821,7 +12821,7 @@
         <v>MARANG</v>
       </c>
       <c r="F119" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G119" t="str">
         <f t="shared" si="14"/>
@@ -12842,13 +12842,13 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>411</v>
+      </c>
+      <c r="B120" t="s">
+        <v>411</v>
+      </c>
+      <c r="C120" t="s">
         <v>412</v>
-      </c>
-      <c r="B120" t="s">
-        <v>412</v>
-      </c>
-      <c r="C120" t="s">
-        <v>413</v>
       </c>
       <c r="D120" t="str">
         <f t="shared" si="13"/>
@@ -12859,7 +12859,7 @@
         <v>KUALA_BERANG</v>
       </c>
       <c r="F120" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G120" t="str">
         <f t="shared" si="14"/>
@@ -12880,13 +12880,13 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>413</v>
+      </c>
+      <c r="B121" t="s">
+        <v>413</v>
+      </c>
+      <c r="C121" t="s">
         <v>414</v>
-      </c>
-      <c r="B121" t="s">
-        <v>414</v>
-      </c>
-      <c r="C121" t="s">
-        <v>415</v>
       </c>
       <c r="D121" t="str">
         <f t="shared" si="13"/>
@@ -12897,7 +12897,7 @@
         <v>TASIK_KENYIR</v>
       </c>
       <c r="F121" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G121" t="str">
         <f t="shared" si="14"/>
@@ -12918,13 +12918,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>415</v>
+      </c>
+      <c r="B122" t="s">
+        <v>415</v>
+      </c>
+      <c r="C122" t="s">
         <v>416</v>
-      </c>
-      <c r="B122" t="s">
-        <v>416</v>
-      </c>
-      <c r="C122" t="s">
-        <v>417</v>
       </c>
       <c r="D122" t="str">
         <f t="shared" si="13"/>
@@ -12935,7 +12935,7 @@
         <v>PENERAK</v>
       </c>
       <c r="F122" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G122" t="str">
         <f t="shared" si="14"/>
@@ -12956,13 +12956,13 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B123" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C123" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D123" t="str">
         <f t="shared" si="13"/>
@@ -12973,7 +12973,7 @@
         <v>NENASI</v>
       </c>
       <c r="F123" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G123" t="str">
         <f t="shared" si="14"/>
@@ -12994,13 +12994,13 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B124" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C124" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D124" t="str">
         <f t="shared" si="13"/>
@@ -13011,7 +13011,7 @@
         <v>PEKAN</v>
       </c>
       <c r="F124" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G124" t="str">
         <f t="shared" si="14"/>
@@ -13032,13 +13032,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B125" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C125" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D125" t="str">
         <f t="shared" si="13"/>
@@ -13049,7 +13049,7 @@
         <v>KUANTAN_TOWN</v>
       </c>
       <c r="F125" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G125" t="str">
         <f t="shared" si="14"/>
@@ -13070,13 +13070,13 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B126" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C126" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D126" t="str">
         <f t="shared" si="13"/>
@@ -13087,7 +13087,7 @@
         <v>TJ_GELANG</v>
       </c>
       <c r="F126" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G126" t="str">
         <f t="shared" si="14"/>
@@ -13108,13 +13108,13 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B127" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C127" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D127" t="str">
         <f t="shared" si="13"/>
@@ -13125,7 +13125,7 @@
         <v>CHUKAI</v>
       </c>
       <c r="F127" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G127" t="str">
         <f t="shared" si="14"/>
@@ -13146,13 +13146,13 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B128" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C128" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D128" t="str">
         <f t="shared" si="13"/>
@@ -13163,7 +13163,7 @@
         <v>MARAN</v>
       </c>
       <c r="F128" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G128" t="str">
         <f t="shared" si="14"/>
@@ -13184,13 +13184,13 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B129" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C129" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D129" t="str">
         <f t="shared" si="13"/>
@@ -13201,7 +13201,7 @@
         <v>GAMBANG</v>
       </c>
       <c r="F129" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G129" t="str">
         <f t="shared" si="14"/>
@@ -13222,13 +13222,13 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B130" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C130" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D130" t="str">
         <f t="shared" si="13"/>
@@ -13239,7 +13239,7 @@
         <v>LEPAR</v>
       </c>
       <c r="F130" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G130" t="str">
         <f t="shared" ref="G130:G161" si="17">B130</f>
@@ -13260,13 +13260,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B131" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C131" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D131" t="str">
         <f t="shared" si="13"/>
@@ -13277,7 +13277,7 @@
         <v>MUADZAM</v>
       </c>
       <c r="F131" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G131" t="str">
         <f t="shared" si="17"/>
@@ -13298,13 +13298,13 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B132" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C132" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D132" t="str">
         <f t="shared" si="13"/>
@@ -13315,7 +13315,7 @@
         <v>SG_LEMBING</v>
       </c>
       <c r="F132" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G132" t="str">
         <f t="shared" si="17"/>
@@ -13336,13 +13336,13 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>467</v>
+      </c>
+      <c r="B133" t="s">
+        <v>467</v>
+      </c>
+      <c r="C133" t="s">
         <v>468</v>
-      </c>
-      <c r="B133" t="s">
-        <v>468</v>
-      </c>
-      <c r="C133" t="s">
-        <v>469</v>
       </c>
       <c r="D133" t="str">
         <f t="shared" si="13"/>
@@ -13353,7 +13353,7 @@
         <v>LUNDU</v>
       </c>
       <c r="F133" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G133" t="str">
         <f t="shared" si="17"/>
@@ -13374,13 +13374,13 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>469</v>
+      </c>
+      <c r="B134" t="s">
+        <v>469</v>
+      </c>
+      <c r="C134" t="s">
         <v>470</v>
-      </c>
-      <c r="B134" t="s">
-        <v>470</v>
-      </c>
-      <c r="C134" t="s">
-        <v>471</v>
       </c>
       <c r="D134" t="str">
         <f t="shared" si="13"/>
@@ -13391,7 +13391,7 @@
         <v>KG_RAMBUNGAN</v>
       </c>
       <c r="F134" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G134" t="str">
         <f t="shared" si="17"/>
@@ -13412,13 +13412,13 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>471</v>
+      </c>
+      <c r="B135" t="s">
+        <v>471</v>
+      </c>
+      <c r="C135" t="s">
         <v>472</v>
-      </c>
-      <c r="B135" t="s">
-        <v>472</v>
-      </c>
-      <c r="C135" t="s">
-        <v>473</v>
       </c>
       <c r="D135" t="str">
         <f t="shared" si="13"/>
@@ -13429,7 +13429,7 @@
         <v>KG_STINGGANG</v>
       </c>
       <c r="F135" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G135" t="str">
         <f t="shared" si="17"/>
@@ -13450,13 +13450,13 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>473</v>
+      </c>
+      <c r="B136" t="s">
+        <v>473</v>
+      </c>
+      <c r="C136" t="s">
         <v>474</v>
-      </c>
-      <c r="B136" t="s">
-        <v>474</v>
-      </c>
-      <c r="C136" t="s">
-        <v>475</v>
       </c>
       <c r="D136" t="str">
         <f t="shared" si="13"/>
@@ -13467,7 +13467,7 @@
         <v>MUARA_TEBAS</v>
       </c>
       <c r="F136" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G136" t="str">
         <f t="shared" si="17"/>
@@ -13488,13 +13488,13 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B137" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C137" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D137" t="str">
         <f t="shared" si="13"/>
@@ -13505,7 +13505,7 @@
         <v>ABM_SEMERA</v>
       </c>
       <c r="F137" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G137" t="str">
         <f t="shared" si="17"/>
@@ -13526,13 +13526,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>476</v>
+      </c>
+      <c r="B138" t="s">
+        <v>476</v>
+      </c>
+      <c r="C138" t="s">
         <v>477</v>
-      </c>
-      <c r="B138" t="s">
-        <v>477</v>
-      </c>
-      <c r="C138" t="s">
-        <v>478</v>
       </c>
       <c r="D138" t="str">
         <f t="shared" si="13"/>
@@ -13543,7 +13543,7 @@
         <v>TEBEDU</v>
       </c>
       <c r="F138" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G138" t="str">
         <f t="shared" si="17"/>
@@ -13564,13 +13564,13 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>478</v>
+      </c>
+      <c r="B139" t="s">
+        <v>478</v>
+      </c>
+      <c r="C139" t="s">
         <v>479</v>
-      </c>
-      <c r="B139" t="s">
-        <v>479</v>
-      </c>
-      <c r="C139" t="s">
-        <v>480</v>
       </c>
       <c r="D139" t="str">
         <f t="shared" si="13"/>
@@ -13581,7 +13581,7 @@
         <v>SERIAN</v>
       </c>
       <c r="F139" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G139" t="str">
         <f t="shared" si="17"/>
@@ -13602,13 +13602,13 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>480</v>
+      </c>
+      <c r="B140" t="s">
+        <v>480</v>
+      </c>
+      <c r="C140" t="s">
         <v>481</v>
-      </c>
-      <c r="B140" t="s">
-        <v>481</v>
-      </c>
-      <c r="C140" t="s">
-        <v>482</v>
       </c>
       <c r="D140" t="str">
         <f t="shared" si="13"/>
@@ -13619,7 +13619,7 @@
         <v>SIMUNJAN</v>
       </c>
       <c r="F140" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G140" t="str">
         <f t="shared" si="17"/>
@@ -13640,13 +13640,13 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>482</v>
+      </c>
+      <c r="B141" t="s">
+        <v>482</v>
+      </c>
+      <c r="C141" t="s">
         <v>483</v>
-      </c>
-      <c r="B141" t="s">
-        <v>483</v>
-      </c>
-      <c r="C141" t="s">
-        <v>484</v>
       </c>
       <c r="D141" t="str">
         <f t="shared" si="13"/>
@@ -13657,7 +13657,7 @@
         <v>KG_TRISO</v>
       </c>
       <c r="F141" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G141" t="str">
         <f t="shared" si="17"/>
@@ -13678,13 +13678,13 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>492</v>
+      </c>
+      <c r="B142" t="s">
+        <v>492</v>
+      </c>
+      <c r="C142" t="s">
         <v>493</v>
-      </c>
-      <c r="B142" t="s">
-        <v>493</v>
-      </c>
-      <c r="C142" t="s">
-        <v>494</v>
       </c>
       <c r="D142" t="str">
         <f t="shared" si="13"/>
@@ -13695,7 +13695,7 @@
         <v>KG_KUAP</v>
       </c>
       <c r="F142" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G142" t="str">
         <f t="shared" si="17"/>
@@ -13716,13 +13716,13 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>494</v>
+      </c>
+      <c r="B143" t="s">
+        <v>494</v>
+      </c>
+      <c r="C143" t="s">
         <v>495</v>
-      </c>
-      <c r="B143" t="s">
-        <v>495</v>
-      </c>
-      <c r="C143" t="s">
-        <v>496</v>
       </c>
       <c r="D143" t="str">
         <f t="shared" si="13"/>
@@ -13733,7 +13733,7 @@
         <v>BT_SIOL</v>
       </c>
       <c r="F143" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G143" t="str">
         <f t="shared" si="17"/>
@@ -13754,13 +13754,13 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B144" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C144" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D144" t="str">
         <f t="shared" si="13"/>
@@ -13771,7 +13771,7 @@
         <v>ABM_NARUB</v>
       </c>
       <c r="F144" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G144" t="str">
         <f t="shared" si="17"/>
@@ -13792,13 +13792,13 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>499</v>
+      </c>
+      <c r="B145" t="s">
+        <v>499</v>
+      </c>
+      <c r="C145" t="s">
         <v>500</v>
-      </c>
-      <c r="B145" t="s">
-        <v>500</v>
-      </c>
-      <c r="C145" t="s">
-        <v>501</v>
       </c>
       <c r="D145" t="str">
         <f t="shared" si="13"/>
@@ -13809,7 +13809,7 @@
         <v>NANGA_TAMIN</v>
       </c>
       <c r="F145" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G145" t="str">
         <f t="shared" si="17"/>
@@ -13830,13 +13830,13 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>501</v>
+      </c>
+      <c r="B146" t="s">
+        <v>501</v>
+      </c>
+      <c r="C146" t="s">
         <v>502</v>
-      </c>
-      <c r="B146" t="s">
-        <v>502</v>
-      </c>
-      <c r="C146" t="s">
-        <v>503</v>
       </c>
       <c r="D146" t="str">
         <f t="shared" si="13"/>
@@ -13847,7 +13847,7 @@
         <v>LASSA_RIVER</v>
       </c>
       <c r="F146" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G146" t="str">
         <f t="shared" si="17"/>
@@ -13868,13 +13868,13 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B147" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C147" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D147" t="str">
         <f t="shared" si="13"/>
@@ -13885,7 +13885,7 @@
         <v>SELANGAU</v>
       </c>
       <c r="F147" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G147" t="str">
         <f t="shared" si="17"/>
@@ -13906,13 +13906,13 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>504</v>
+      </c>
+      <c r="B148" t="s">
+        <v>504</v>
+      </c>
+      <c r="C148" t="s">
         <v>505</v>
-      </c>
-      <c r="B148" t="s">
-        <v>505</v>
-      </c>
-      <c r="C148" t="s">
-        <v>506</v>
       </c>
       <c r="D148" t="str">
         <f t="shared" si="13"/>
@@ -13923,7 +13923,7 @@
         <v>STAPANG</v>
       </c>
       <c r="F148" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G148" t="str">
         <f t="shared" si="17"/>
@@ -13944,13 +13944,13 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>506</v>
+      </c>
+      <c r="B149" t="s">
+        <v>506</v>
+      </c>
+      <c r="C149" t="s">
         <v>507</v>
-      </c>
-      <c r="B149" t="s">
-        <v>507</v>
-      </c>
-      <c r="C149" t="s">
-        <v>508</v>
       </c>
       <c r="D149" t="str">
         <f t="shared" si="13"/>
@@ -13961,7 +13961,7 @@
         <v>T_RIVER_JUNCTION</v>
       </c>
       <c r="F149" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G149" t="str">
         <f t="shared" si="17"/>
@@ -13982,13 +13982,13 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>509</v>
+      </c>
+      <c r="B150" t="s">
+        <v>509</v>
+      </c>
+      <c r="C150" t="s">
         <v>510</v>
-      </c>
-      <c r="B150" t="s">
-        <v>510</v>
-      </c>
-      <c r="C150" t="s">
-        <v>511</v>
       </c>
       <c r="D150" t="str">
         <f t="shared" si="13"/>
@@ -13999,7 +13999,7 @@
         <v>P_DUDONG</v>
       </c>
       <c r="F150" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G150" t="str">
         <f t="shared" si="17"/>
@@ -14020,13 +14020,13 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>511</v>
+      </c>
+      <c r="B151" t="s">
+        <v>511</v>
+      </c>
+      <c r="C151" t="s">
         <v>512</v>
-      </c>
-      <c r="B151" t="s">
-        <v>512</v>
-      </c>
-      <c r="C151" t="s">
-        <v>513</v>
       </c>
       <c r="D151" t="str">
         <f t="shared" si="13"/>
@@ -14037,7 +14037,7 @@
         <v>MERUAN</v>
       </c>
       <c r="F151" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G151" t="str">
         <f t="shared" si="17"/>
@@ -14058,13 +14058,13 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>513</v>
+      </c>
+      <c r="B152" t="s">
+        <v>513</v>
+      </c>
+      <c r="C152" t="s">
         <v>514</v>
-      </c>
-      <c r="B152" t="s">
-        <v>514</v>
-      </c>
-      <c r="C152" t="s">
-        <v>515</v>
       </c>
       <c r="D152" t="str">
         <f t="shared" si="13"/>
@@ -14075,7 +14075,7 @@
         <v>LENG</v>
       </c>
       <c r="F152" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G152" t="str">
         <f t="shared" si="17"/>
@@ -14096,13 +14096,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>515</v>
+      </c>
+      <c r="B153" t="s">
+        <v>515</v>
+      </c>
+      <c r="C153" t="s">
         <v>516</v>
-      </c>
-      <c r="B153" t="s">
-        <v>516</v>
-      </c>
-      <c r="C153" t="s">
-        <v>517</v>
       </c>
       <c r="D153" t="str">
         <f t="shared" si="13"/>
@@ -14113,7 +14113,7 @@
         <v>PAKAN_ROAD</v>
       </c>
       <c r="F153" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G153" t="str">
         <f t="shared" si="17"/>
@@ -14134,13 +14134,13 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>517</v>
+      </c>
+      <c r="B154" t="s">
+        <v>517</v>
+      </c>
+      <c r="C154" t="s">
         <v>518</v>
-      </c>
-      <c r="B154" t="s">
-        <v>518</v>
-      </c>
-      <c r="C154" t="s">
-        <v>519</v>
       </c>
       <c r="D154" t="str">
         <f t="shared" si="13"/>
@@ -14151,7 +14151,7 @@
         <v>DURIN_TOWN</v>
       </c>
       <c r="F154" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G154" t="str">
         <f t="shared" si="17"/>
@@ -14172,13 +14172,13 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>519</v>
+      </c>
+      <c r="B155" t="s">
+        <v>519</v>
+      </c>
+      <c r="C155" t="s">
         <v>520</v>
-      </c>
-      <c r="B155" t="s">
-        <v>520</v>
-      </c>
-      <c r="C155" t="s">
-        <v>521</v>
       </c>
       <c r="D155" t="str">
         <f t="shared" si="13"/>
@@ -14189,7 +14189,7 @@
         <v>KANOWIT</v>
       </c>
       <c r="F155" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G155" t="str">
         <f t="shared" si="17"/>
@@ -14210,13 +14210,13 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B156" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C156" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D156" t="str">
         <f t="shared" si="13"/>
@@ -14227,7 +14227,7 @@
         <v>PENARIK</v>
       </c>
       <c r="F156" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G156" t="str">
         <f t="shared" si="17"/>
@@ -14248,13 +14248,13 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>522</v>
+      </c>
+      <c r="B157" t="s">
+        <v>522</v>
+      </c>
+      <c r="C157" t="s">
         <v>523</v>
-      </c>
-      <c r="B157" t="s">
-        <v>523</v>
-      </c>
-      <c r="C157" t="s">
-        <v>524</v>
       </c>
       <c r="D157" t="str">
         <f t="shared" ref="D157:D184" si="23">SUBSTITUTE(UPPER(A157), " ", "_")</f>
@@ -14265,7 +14265,7 @@
         <v>KG_SETIU_LAMA</v>
       </c>
       <c r="F157" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G157" t="str">
         <f t="shared" si="17"/>
@@ -14286,13 +14286,13 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>524</v>
+      </c>
+      <c r="B158" t="s">
+        <v>524</v>
+      </c>
+      <c r="C158" t="s">
         <v>525</v>
-      </c>
-      <c r="B158" t="s">
-        <v>525</v>
-      </c>
-      <c r="C158" t="s">
-        <v>526</v>
       </c>
       <c r="D158" t="str">
         <f t="shared" si="23"/>
@@ -14303,7 +14303,7 @@
         <v>BETING_LINTANG</v>
       </c>
       <c r="F158" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G158" t="str">
         <f t="shared" si="17"/>
@@ -14324,13 +14324,13 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B159" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C159" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D159" t="str">
         <f t="shared" si="23"/>
@@ -14341,7 +14341,7 @@
         <v>P_RU</v>
       </c>
       <c r="F159" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G159" t="str">
         <f t="shared" si="17"/>
@@ -14362,13 +14362,13 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>528</v>
+      </c>
+      <c r="B160" t="s">
+        <v>528</v>
+      </c>
+      <c r="C160" t="s">
         <v>529</v>
-      </c>
-      <c r="B160" t="s">
-        <v>529</v>
-      </c>
-      <c r="C160" t="s">
-        <v>530</v>
       </c>
       <c r="D160" t="str">
         <f t="shared" si="23"/>
@@ -14379,7 +14379,7 @@
         <v>KG_BESUT</v>
       </c>
       <c r="F160" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G160" t="str">
         <f t="shared" si="17"/>
@@ -14400,13 +14400,13 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>530</v>
+      </c>
+      <c r="B161" t="s">
+        <v>530</v>
+      </c>
+      <c r="C161" t="s">
         <v>531</v>
-      </c>
-      <c r="B161" t="s">
-        <v>531</v>
-      </c>
-      <c r="C161" t="s">
-        <v>532</v>
       </c>
       <c r="D161" t="str">
         <f t="shared" si="23"/>
@@ -14417,7 +14417,7 @@
         <v>KG_TOK_BALI</v>
       </c>
       <c r="F161" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G161" t="str">
         <f t="shared" si="17"/>
@@ -14438,13 +14438,13 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>532</v>
+      </c>
+      <c r="B162" t="s">
+        <v>532</v>
+      </c>
+      <c r="C162" t="s">
         <v>533</v>
-      </c>
-      <c r="B162" t="s">
-        <v>533</v>
-      </c>
-      <c r="C162" t="s">
-        <v>534</v>
       </c>
       <c r="D162" t="str">
         <f t="shared" si="23"/>
@@ -14455,7 +14455,7 @@
         <v>KG_KANDIS</v>
       </c>
       <c r="F162" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G162" t="str">
         <f t="shared" ref="G162:G168" si="24">B162</f>
@@ -14476,13 +14476,13 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>534</v>
+      </c>
+      <c r="B163" t="s">
+        <v>534</v>
+      </c>
+      <c r="C163" t="s">
         <v>535</v>
-      </c>
-      <c r="B163" t="s">
-        <v>535</v>
-      </c>
-      <c r="C163" t="s">
-        <v>536</v>
       </c>
       <c r="D163" t="str">
         <f t="shared" si="23"/>
@@ -14493,7 +14493,7 @@
         <v>BACHOK</v>
       </c>
       <c r="F163" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G163" t="str">
         <f t="shared" si="24"/>
@@ -14514,13 +14514,13 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>536</v>
+      </c>
+      <c r="B164" t="s">
+        <v>536</v>
+      </c>
+      <c r="C164" t="s">
         <v>537</v>
-      </c>
-      <c r="B164" t="s">
-        <v>537</v>
-      </c>
-      <c r="C164" t="s">
-        <v>538</v>
       </c>
       <c r="D164" t="str">
         <f t="shared" si="23"/>
@@ -14531,7 +14531,7 @@
         <v>KOTA_BHARU_TOWN</v>
       </c>
       <c r="F164" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G164" t="str">
         <f t="shared" si="24"/>
@@ -14552,13 +14552,13 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>538</v>
+      </c>
+      <c r="B165" t="s">
+        <v>538</v>
+      </c>
+      <c r="C165" t="s">
         <v>539</v>
-      </c>
-      <c r="B165" t="s">
-        <v>539</v>
-      </c>
-      <c r="C165" t="s">
-        <v>540</v>
       </c>
       <c r="D165" t="str">
         <f t="shared" si="23"/>
@@ -14569,7 +14569,7 @@
         <v>KUALA_KRAI</v>
       </c>
       <c r="F165" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G165" t="str">
         <f t="shared" si="24"/>
@@ -14590,13 +14590,13 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>540</v>
+      </c>
+      <c r="B166" t="s">
+        <v>540</v>
+      </c>
+      <c r="C166" t="s">
         <v>541</v>
-      </c>
-      <c r="B166" t="s">
-        <v>541</v>
-      </c>
-      <c r="C166" t="s">
-        <v>542</v>
       </c>
       <c r="D166" t="str">
         <f t="shared" si="23"/>
@@ -14607,7 +14607,7 @@
         <v>TANAH_MERAH</v>
       </c>
       <c r="F166" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G166" t="str">
         <f t="shared" si="24"/>
@@ -14628,13 +14628,13 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>542</v>
+      </c>
+      <c r="B167" t="s">
+        <v>542</v>
+      </c>
+      <c r="C167" t="s">
         <v>543</v>
-      </c>
-      <c r="B167" t="s">
-        <v>543</v>
-      </c>
-      <c r="C167" t="s">
-        <v>544</v>
       </c>
       <c r="D167" t="str">
         <f t="shared" si="23"/>
@@ -14645,7 +14645,7 @@
         <v>BT_MELINTANG</v>
       </c>
       <c r="F167" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G167" t="str">
         <f t="shared" si="24"/>
@@ -14666,13 +14666,13 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>544</v>
+      </c>
+      <c r="B168" t="s">
+        <v>544</v>
+      </c>
+      <c r="C168" t="s">
         <v>545</v>
-      </c>
-      <c r="B168" t="s">
-        <v>545</v>
-      </c>
-      <c r="C168" t="s">
-        <v>546</v>
       </c>
       <c r="D168" t="str">
         <f t="shared" si="23"/>
@@ -14683,7 +14683,7 @@
         <v>JELI</v>
       </c>
       <c r="F168" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G168" t="str">
         <f t="shared" si="24"/>
@@ -14704,13 +14704,13 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B169" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C169" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D169" t="str">
         <f t="shared" si="23"/>
@@ -14721,7 +14721,7 @@
         <v>KUAH</v>
       </c>
       <c r="F169" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G169" t="str">
         <f t="shared" ref="G169:G177" si="27">B169</f>
@@ -14740,13 +14740,13 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B170" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C170" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D170" t="str">
         <f t="shared" si="23"/>
@@ -14757,7 +14757,7 @@
         <v>P_TIMUN</v>
       </c>
       <c r="F170" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G170" t="str">
         <f t="shared" si="27"/>
@@ -14778,13 +14778,13 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B171" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C171" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D171" t="str">
         <f t="shared" si="23"/>
@@ -14795,7 +14795,7 @@
         <v>ABM_P_TUBA</v>
       </c>
       <c r="F171" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G171" t="str">
         <f t="shared" si="27"/>
@@ -14816,13 +14816,13 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B172" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C172" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D172" t="str">
         <f t="shared" si="23"/>
@@ -14833,7 +14833,7 @@
         <v>P_PAYA</v>
       </c>
       <c r="F172" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G172" t="str">
         <f t="shared" si="27"/>
@@ -14852,13 +14852,13 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B173" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C173" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D173" t="str">
         <f t="shared" si="23"/>
@@ -14869,7 +14869,7 @@
         <v>KUALA_PERLIS</v>
       </c>
       <c r="F173" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G173" t="str">
         <f t="shared" si="27"/>
@@ -14890,13 +14890,13 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B174" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C174" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D174" t="str">
         <f t="shared" si="23"/>
@@ -14907,7 +14907,7 @@
         <v>AYER_HITAM</v>
       </c>
       <c r="F174" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G174" t="str">
         <f t="shared" si="27"/>
@@ -14928,13 +14928,13 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B175" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C175" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D175" t="str">
         <f t="shared" si="23"/>
@@ -14945,7 +14945,7 @@
         <v>KUALA_KEDAH</v>
       </c>
       <c r="F175" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G175" t="str">
         <f t="shared" si="27"/>
@@ -14964,13 +14964,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B176" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C176" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D176" t="str">
         <f t="shared" si="23"/>
@@ -14981,7 +14981,7 @@
         <v>SIMPANG_EMPAT</v>
       </c>
       <c r="F176" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G176" t="str">
         <f t="shared" si="27"/>
@@ -15002,13 +15002,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B177" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C177" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D177" t="str">
         <f t="shared" si="23"/>
@@ -15019,7 +15019,7 @@
         <v>KOTA_SARANG_SEMUT</v>
       </c>
       <c r="F177" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G177" t="str">
         <f t="shared" si="27"/>
@@ -15040,13 +15040,13 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B178" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C178" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D178" t="str">
         <f t="shared" si="23"/>
@@ -15057,7 +15057,7 @@
         <v>BATU_HAMPAR</v>
       </c>
       <c r="F178" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G178" t="str">
         <f t="shared" ref="G178:G184" si="31">B178</f>
@@ -15078,13 +15078,13 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B179" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C179" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D179" t="str">
         <f t="shared" si="23"/>
@@ -15095,7 +15095,7 @@
         <v>PARIT</v>
       </c>
       <c r="F179" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G179" t="str">
         <f t="shared" si="31"/>
@@ -15116,13 +15116,13 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B180" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C180" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D180" t="str">
         <f t="shared" si="23"/>
@@ -15133,7 +15133,7 @@
         <v>BATU_GAJAH</v>
       </c>
       <c r="F180" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G180" t="str">
         <f t="shared" si="31"/>
@@ -15154,13 +15154,13 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B181" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C181" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D181" t="str">
         <f t="shared" si="23"/>
@@ -15171,7 +15171,7 @@
         <v>GOPENG</v>
       </c>
       <c r="F181" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G181" t="str">
         <f t="shared" si="31"/>
@@ -15192,13 +15192,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B182" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C182" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D182" t="str">
         <f t="shared" si="23"/>
@@ -15209,7 +15209,7 @@
         <v>KAMPAR</v>
       </c>
       <c r="F182" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G182" t="str">
         <f t="shared" si="31"/>
@@ -15228,13 +15228,13 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B183" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C183" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D183" t="str">
         <f t="shared" si="23"/>
@@ -15245,7 +15245,7 @@
         <v>TELUK_INTAN</v>
       </c>
       <c r="F183" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G183" t="str">
         <f t="shared" si="31"/>
@@ -15264,13 +15264,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B184" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C184" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D184" t="str">
         <f t="shared" si="23"/>
@@ -15281,7 +15281,7 @@
         <v>BIDOR</v>
       </c>
       <c r="F184" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G184" t="str">
         <f t="shared" si="31"/>
@@ -15341,10 +15341,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" t="s">
         <v>272</v>
-      </c>
-      <c r="B4" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -15389,18 +15389,18 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>576</v>
+      </c>
+      <c r="B10" t="s">
         <v>577</v>
-      </c>
-      <c r="B10" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B11" t="s">
         <v>318</v>
-      </c>
-      <c r="B11" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">

--- a/data/MY/Waypoints.xlsx
+++ b/data/MY/Waypoints.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Projects\VFR Waypoints\data\MY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC703721-8D5B-441C-A275-D7E7E36A93C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2D7DB8-3732-408C-BD78-B9D354EE6DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3915" yWindow="975" windowWidth="25470" windowHeight="20235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="975" windowWidth="25470" windowHeight="20235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Google My Maps Output" sheetId="3" r:id="rId1"/>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -439,9 +439,6 @@
     <t>Kuang</t>
   </si>
   <si>
-    <t>Guthrie – LATAR Expressway Kuang Exit</t>
-  </si>
-  <si>
     <t>Nibong Gila</t>
   </si>
   <si>
@@ -2180,6 +2177,9 @@
   </si>
   <si>
     <t>South of Kg Semangar</t>
+  </si>
+  <si>
+    <t>Guthrie - LATAR Expressway Kuang Exit</t>
   </si>
 </sst>
 </file>
@@ -2576,16 +2576,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2891,7 +2891,7 @@
         <v>KUANG</v>
       </c>
       <c r="B23" t="str">
-        <v>Guthrie – LATAR Expressway Kuang Exit</v>
+        <v>Guthrie - LATAR Expressway Kuang Exit</v>
       </c>
       <c r="C23" s="2">
         <v>3.2694399999999999</v>
@@ -5173,22 +5173,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5197,7 +5197,7 @@
         <v>SGBESR</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D2" t="str" cm="1">
         <f t="array" ref="D2:D184">_xlfn.XLOOKUP('Source Data'!H1,'Source Data'!$F$1:$J$1,'Source Data'!$F$2:$J$184)</f>
@@ -5217,7 +5217,7 @@
         <v>KLSELA</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D3" t="str">
         <v>Kuala Selangor Bridge</v>
@@ -5234,7 +5234,7 @@
         <v>KAPAR</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D4" t="str">
         <v>Kapar Junction</v>
@@ -5251,7 +5251,7 @@
         <v>PTKLNG</v>
       </c>
       <c r="B5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D5" t="str">
         <v>Pulau Indah Bridge</v>
@@ -5268,7 +5268,7 @@
         <v>MORIB</v>
       </c>
       <c r="B6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D6" t="str">
         <v>Golf Course</v>
@@ -5285,7 +5285,7 @@
         <v>TJSEPT</v>
       </c>
       <c r="B7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D7" t="str">
         <v>Jetty Tanjung Sepat</v>
@@ -5302,7 +5302,7 @@
         <v>TJTUAN</v>
       </c>
       <c r="B8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D8" t="str">
         <v>Lighthouse</v>
@@ -5319,7 +5319,7 @@
         <v>SLMRVR</v>
       </c>
       <c r="B9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D9" t="str">
         <v>Slim River Hospital</v>
@@ -5336,7 +5336,7 @@
         <v>TJMALM</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D10" t="str">
         <v>Universiti Perguruan Sult</v>
@@ -5353,7 +5353,7 @@
         <v>RAWANG</v>
       </c>
       <c r="B11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D11" t="str">
         <v>Lafarge plant</v>
@@ -5370,7 +5370,7 @@
         <v>BATUCV</v>
       </c>
       <c r="B12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D12" t="str">
         <v>Hindu Temple</v>
@@ -5387,7 +5387,7 @@
         <v>SGBESI</v>
       </c>
       <c r="B13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D13" t="str">
         <v>Smart Toll Plaza</v>
@@ -5404,7 +5404,7 @@
         <v>KAJANG</v>
       </c>
       <c r="B14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D14" t="str">
         <v>Stadium</v>
@@ -5421,7 +5421,7 @@
         <v>SERMBN</v>
       </c>
       <c r="B15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D15" t="str">
         <v>Seremban Mosque</v>
@@ -5438,7 +5438,7 @@
         <v>BENTNG</v>
       </c>
       <c r="B16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D16" t="str">
         <v>Dataran Bentong</v>
@@ -5455,7 +5455,7 @@
         <v>RANTAU</v>
       </c>
       <c r="B17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D17" t="str">
         <v>TNB Substation</v>
@@ -5472,7 +5472,7 @@
         <v>KLKLWG</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D18" t="str">
         <v>Jelebu District Council</v>
@@ -5489,7 +5489,7 @@
         <v>PETJYA</v>
       </c>
       <c r="B19" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D19" t="str">
         <v>Menara TM</v>
@@ -5506,7 +5506,7 @@
         <v>BTLNJN</v>
       </c>
       <c r="B20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D20" t="str">
         <v>Tol Sungai Penchala</v>
@@ -5523,7 +5523,7 @@
         <v>PCKPRD</v>
       </c>
       <c r="B21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D21" t="str">
         <v>Puncak Perdana Interchang</v>
@@ -5540,7 +5540,7 @@
         <v>SHALAM</v>
       </c>
       <c r="B22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D22" t="str">
         <v>Sultan Salahudin Abdul Az</v>
@@ -5557,10 +5557,10 @@
         <v>KUANG</v>
       </c>
       <c r="B23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D23" t="str">
-        <v>Guthrie – LATAR Expresswa</v>
+        <v>Guthrie - LATAR Expresswa</v>
       </c>
       <c r="E23" s="5">
         <v>3.2694399999999999</v>
@@ -5574,7 +5574,7 @@
         <v>NBGILA</v>
       </c>
       <c r="B24" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D24" t="str">
         <v>Met Weather Radar</v>
@@ -5591,7 +5591,7 @@
         <v>TITWGS</v>
       </c>
       <c r="B25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D25" t="str">
         <v>Titiwangsa Lake</v>
@@ -5608,7 +5608,7 @@
         <v>SGMBUT</v>
       </c>
       <c r="B26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D26" t="str">
         <v>DUKE Jalan Kuching Interc</v>
@@ -5625,7 +5625,7 @@
         <v>UTMMSQ</v>
       </c>
       <c r="B27" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D27" t="str">
         <v>UTM Mosque</v>
@@ -5642,7 +5642,7 @@
         <v>BENUT</v>
       </c>
       <c r="B28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D28" t="str">
         <v>Benut</v>
@@ -5659,7 +5659,7 @@
         <v>KULAI</v>
       </c>
       <c r="B29" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D29" t="str">
         <v>Kulai Tol Plaza</v>
@@ -5676,7 +5676,7 @@
         <v>EJBAIR</v>
       </c>
       <c r="B30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D30" t="str">
         <v>East of Johor Bahru Airfi</v>
@@ -5693,7 +5693,7 @@
         <v>KOTATG</v>
       </c>
       <c r="B31" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D31" t="str">
         <v>Kota Tinggi Bridge</v>
@@ -5710,7 +5710,7 @@
         <v>ETIRAM</v>
       </c>
       <c r="B32" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D32" t="str">
         <v>East of Kg Sg Tiram</v>
@@ -5727,7 +5727,7 @@
         <v>EASTJB</v>
       </c>
       <c r="B33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D33" t="str">
         <v>East of Johor Bahru Town</v>
@@ -5744,7 +5744,7 @@
         <v>FELDA</v>
       </c>
       <c r="B34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D34" t="str">
         <v>Felda Ulu Tebrau</v>
@@ -5761,7 +5761,7 @@
         <v>TEBMAL</v>
       </c>
       <c r="B35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D35" t="str">
         <v>Tebrau City Mall</v>
@@ -5778,7 +5778,7 @@
         <v>SKGSEM</v>
       </c>
       <c r="B36" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D36" t="str">
         <v>South of Kg Semangar</v>
@@ -5795,7 +5795,7 @@
         <v>SDLBSR</v>
       </c>
       <c r="B37" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D37" t="str">
         <v>Kampung Sedili Besar</v>
@@ -5812,7 +5812,7 @@
         <v>SPGRNG</v>
       </c>
       <c r="B38" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D38" t="str">
         <v>Simpang Renggam Town</v>
@@ -5829,7 +5829,7 @@
         <v>AIRHTM</v>
       </c>
       <c r="B39" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D39" t="str">
         <v>Air Hitam</v>
@@ -5846,7 +5846,7 @@
         <v>YONGPG</v>
       </c>
       <c r="B40" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D40" t="str">
         <v>Yong Peng</v>
@@ -5863,7 +5863,7 @@
         <v>PTXRAY</v>
       </c>
       <c r="B41" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D41" t="str">
         <v>Point XRay</v>
@@ -5880,7 +5880,7 @@
         <v>TASSAN</v>
       </c>
       <c r="B42" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D42" t="str">
         <v>Tass Andrassy</v>
@@ -5897,7 +5897,7 @@
         <v>OLDAIR</v>
       </c>
       <c r="B43" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D43" t="str">
         <v>Old Airport</v>
@@ -5914,7 +5914,7 @@
         <v>SBTKIS</v>
       </c>
       <c r="B44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D44" t="str">
         <v>Sebatik Island</v>
@@ -5931,7 +5931,7 @@
         <v>KLBKN</v>
       </c>
       <c r="B45" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D45" t="str">
         <v>Kalabakan</v>
@@ -5948,7 +5948,7 @@
         <v>BALUNG</v>
       </c>
       <c r="B46" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D46" t="str">
         <v>Balung</v>
@@ -5965,7 +5965,7 @@
         <v>KWAHLL</v>
       </c>
       <c r="B47" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D47" t="str">
         <v>Kawa Hill</v>
@@ -5982,7 +5982,7 @@
         <v>MTPYRM</v>
       </c>
       <c r="B48" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D48" t="str">
         <v>Mt Pyramid</v>
@@ -5999,7 +5999,7 @@
         <v>BTRNG</v>
       </c>
       <c r="B49" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D49" t="str">
         <v>Baturong</v>
@@ -6016,7 +6016,7 @@
         <v>DANUM</v>
       </c>
       <c r="B50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D50" t="str">
         <v>Danum</v>
@@ -6033,7 +6033,7 @@
         <v>JCT49K</v>
       </c>
       <c r="B51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D51" t="str">
         <v>Junction (49KM)</v>
@@ -6050,7 +6050,7 @@
         <v>KGAMAN</v>
       </c>
       <c r="B52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D52" t="str">
         <v>Kampung Aman</v>
@@ -6067,7 +6067,7 @@
         <v>TJBATI</v>
       </c>
       <c r="B53" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D53" t="str">
         <v>Tanjung Batai</v>
@@ -6084,7 +6084,7 @@
         <v>SDLHLL</v>
       </c>
       <c r="B54" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D54" t="str">
         <v>Saddle Hill</v>
@@ -6101,7 +6101,7 @@
         <v>NAGOS</v>
       </c>
       <c r="B55" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D55" t="str">
         <v>Nagos</v>
@@ -6118,7 +6118,7 @@
         <v>SMPRNA</v>
       </c>
       <c r="B56" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D56" t="str">
         <v>Semporna</v>
@@ -6135,7 +6135,7 @@
         <v>GAYAIS</v>
       </c>
       <c r="B57" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D57" t="str">
         <v>Gaya Island</v>
@@ -6152,7 +6152,7 @@
         <v>SPDNIS</v>
       </c>
       <c r="B58" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D58" t="str">
         <v>Sipadan Island</v>
@@ -6169,7 +6169,7 @@
         <v>BNDIND</v>
       </c>
       <c r="B59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D59" t="str">
         <v>Bandar Indah (Road Juncti</v>
@@ -6186,7 +6186,7 @@
         <v>KPTBNK</v>
       </c>
       <c r="B60" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D60" t="str">
         <v>Kampong Tobanka</v>
@@ -6203,7 +6203,7 @@
         <v>BAIIS</v>
       </c>
       <c r="B61" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D61" t="str">
         <v>Bai Island</v>
@@ -6220,7 +6220,7 @@
         <v>TJBDR</v>
       </c>
       <c r="B62" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D62" t="str">
         <v>Tanjung Bidadari</v>
@@ -6237,7 +6237,7 @@
         <v>KLKNBB</v>
       </c>
       <c r="B63" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D63" t="str">
         <v>Kuala Kinabatangan Besar</v>
@@ -6254,7 +6254,7 @@
         <v>KGBILT</v>
       </c>
       <c r="B64" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D64" t="str">
         <v>Kampung Bilit</v>
@@ -6271,7 +6271,7 @@
         <v>SGSEG</v>
       </c>
       <c r="B65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D65" t="str">
         <v>Sungai Seguntor</v>
@@ -6288,7 +6288,7 @@
         <v>KTKNB</v>
       </c>
       <c r="B66" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D66" t="str">
         <v>Kota Kinabatangan</v>
@@ -6305,7 +6305,7 @@
         <v>KGKLLK</v>
       </c>
       <c r="B67" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D67" t="str">
         <v>Kampung Kuala Lokan</v>
@@ -6322,7 +6322,7 @@
         <v>ML32JT</v>
       </c>
       <c r="B68" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D68" t="str">
         <v>Mile 32 Rd Junction</v>
@@ -6339,7 +6339,7 @@
         <v>TELPID</v>
       </c>
       <c r="B69" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D69" t="str">
         <v>Telupid</v>
@@ -6356,7 +6356,7 @@
         <v>KGGMGL</v>
       </c>
       <c r="B70" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D70" t="str">
         <v>Kampung GumGum Laut</v>
@@ -6373,7 +6373,7 @@
         <v>KGSMWG</v>
       </c>
       <c r="B71" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D71" t="str">
         <v>Kampung Semawang</v>
@@ -6390,7 +6390,7 @@
         <v>BLURAN</v>
       </c>
       <c r="B72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D72" t="str">
         <v>Beluran</v>
@@ -6407,7 +6407,7 @@
         <v>KNWIIS</v>
       </c>
       <c r="B73" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D73" t="str">
         <v>Kenawi Island</v>
@@ -6424,7 +6424,7 @@
         <v>KGSGSG</v>
       </c>
       <c r="B74" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D74" t="str">
         <v>Kampung Sungai-Sungai</v>
@@ -6441,7 +6441,7 @@
         <v>KGTRSN</v>
       </c>
       <c r="B75" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D75" t="str">
         <v>Kampung Terusan</v>
@@ -6458,7 +6458,7 @@
         <v>SLNGIS</v>
       </c>
       <c r="B76" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D76" t="str">
         <v>Selingan Island</v>
@@ -6475,7 +6475,7 @@
         <v>LNKYIS</v>
       </c>
       <c r="B77" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D77" t="str">
         <v>Lankayan Island</v>
@@ -6492,7 +6492,7 @@
         <v>SBRHIS</v>
       </c>
       <c r="B78" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D78" t="str">
         <v>South of Berhala Island</v>
@@ -6509,7 +6509,7 @@
         <v>LNGMNS</v>
       </c>
       <c r="B79" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D79" t="str">
         <v>Luang Manis</v>
@@ -6526,7 +6526,7 @@
         <v>PMGSCH</v>
       </c>
       <c r="B80" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D80" t="str">
         <v>Pamaguan Primary School</v>
@@ -6543,7 +6543,7 @@
         <v>PRTWLD</v>
       </c>
       <c r="B81" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D81" t="str">
         <v>Port Weld</v>
@@ -6560,7 +6560,7 @@
         <v>TJPDNG</v>
       </c>
       <c r="B82" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D82" t="str">
         <v>Tanjung Piandang</v>
@@ -6577,7 +6577,7 @@
         <v>PAMAN</v>
       </c>
       <c r="B83" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D83" t="str">
         <v>South of Pulau Aman</v>
@@ -6594,7 +6594,7 @@
         <v>KDHPKW</v>
       </c>
       <c r="B84" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D84" t="str">
         <v>Kedah Peak West</v>
@@ -6611,7 +6611,7 @@
         <v>KLMUDA</v>
       </c>
       <c r="B85" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D85" t="str">
         <v>Kuala Sungai Muda</v>
@@ -6628,7 +6628,7 @@
         <v>GRGTWN</v>
       </c>
       <c r="B86" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D86" t="str">
         <v>North of George Town</v>
@@ -6645,7 +6645,7 @@
         <v>PLGAYA</v>
       </c>
       <c r="B87" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D87" t="str">
         <v>West of Pulau Gaya</v>
@@ -6662,7 +6662,7 @@
         <v>PLSULG</v>
       </c>
       <c r="B88" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D88" t="str">
         <v>Pulau Sulug</v>
@@ -6679,7 +6679,7 @@
         <v>PLTIGA</v>
       </c>
       <c r="B89" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D89" t="str">
         <v>Pulau Tiga</v>
@@ -6696,7 +6696,7 @@
         <v>KLPNYU</v>
       </c>
       <c r="B90" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D90" t="str">
         <v>Kuala Penyu</v>
@@ -6713,7 +6713,7 @@
         <v>BNGWN</v>
       </c>
       <c r="B91" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D91" t="str">
         <v>Bongawan</v>
@@ -6730,7 +6730,7 @@
         <v>EPAPAR</v>
       </c>
       <c r="B92" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D92" t="str">
         <v>East of Papar</v>
@@ -6747,7 +6747,7 @@
         <v>EKAWNG</v>
       </c>
       <c r="B93" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D93" t="str">
         <v>East of Kawang</v>
@@ -6764,7 +6764,7 @@
         <v>EKNRTT</v>
       </c>
       <c r="B94" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D94" t="str">
         <v>East of Kinarut Town</v>
@@ -6781,7 +6781,7 @@
         <v>KPYAN</v>
       </c>
       <c r="B95" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D95" t="str">
         <v>Kepayan</v>
@@ -6798,7 +6798,7 @@
         <v>EINMNT</v>
       </c>
       <c r="B96" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D96" t="str">
         <v>East of Inanam Town</v>
@@ -6815,7 +6815,7 @@
         <v>ETLPOK</v>
       </c>
       <c r="B97" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D97" t="str">
         <v>East of Telipok</v>
@@ -6832,7 +6832,7 @@
         <v>KGKULU</v>
       </c>
       <c r="B98" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D98" t="str">
         <v>Kampung Kiulu</v>
@@ -6849,7 +6849,7 @@
         <v>KGBLBK</v>
       </c>
       <c r="B99" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D99" t="str">
         <v>Kampung Balabakan</v>
@@ -6866,7 +6866,7 @@
         <v>RANAU</v>
       </c>
       <c r="B100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D100" t="str">
         <v>Ranau</v>
@@ -6883,7 +6883,7 @@
         <v>WH1040</v>
       </c>
       <c r="B101" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D101" t="str">
         <v>West of Hill 1040</v>
@@ -6900,7 +6900,7 @@
         <v>TJDLT</v>
       </c>
       <c r="B102" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D102" t="str">
         <v>Tanjung Dalit</v>
@@ -6917,7 +6917,7 @@
         <v>KTBLUD</v>
       </c>
       <c r="B103" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D103" t="str">
         <v>Kota Belud</v>
@@ -6934,7 +6934,7 @@
         <v>TRNDAK</v>
       </c>
       <c r="B104" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D104" t="str">
         <v>Terendak</v>
@@ -6951,7 +6951,7 @@
         <v>REMBIA</v>
       </c>
       <c r="B105" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D105" t="str">
         <v>Rembia</v>
@@ -6968,7 +6968,7 @@
         <v>TAMPIN</v>
       </c>
       <c r="B106" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D106" t="str">
         <v>Tampin</v>
@@ -6985,7 +6985,7 @@
         <v>CHNCHN</v>
       </c>
       <c r="B107" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D107" t="str">
         <v>Chin Chin</v>
@@ -7002,7 +7002,7 @@
         <v>BTBERU</v>
       </c>
       <c r="B108" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D108" t="str">
         <v>Bt Beruang</v>
@@ -7019,7 +7019,7 @@
         <v>UMBAI</v>
       </c>
       <c r="B109" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D109" t="str">
         <v>Umbai</v>
@@ -7036,7 +7036,7 @@
         <v>MALCTY</v>
       </c>
       <c r="B110" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D110" t="str">
         <v>Malacca City</v>
@@ -7053,7 +7053,7 @@
         <v>MUAR</v>
       </c>
       <c r="B111" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D111" t="str">
         <v>Muar</v>
@@ -7070,7 +7070,7 @@
         <v>TANKAK</v>
       </c>
       <c r="B112" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D112" t="str">
         <v>Tangkak</v>
@@ -7087,7 +7087,7 @@
         <v>PAGOH</v>
       </c>
       <c r="B113" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D113" t="str">
         <v>Pagoh</v>
@@ -7104,7 +7104,7 @@
         <v>PENRIK</v>
       </c>
       <c r="B114" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D114" t="str">
         <v>Penarik</v>
@@ -7121,7 +7121,7 @@
         <v>BDRPER</v>
       </c>
       <c r="B115" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D115" t="str">
         <v>Bandar Permaisuri</v>
@@ -7138,7 +7138,7 @@
         <v>KGMRNG</v>
       </c>
       <c r="B116" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D116" t="str">
         <v>Kampung Merang</v>
@@ -7155,7 +7155,7 @@
         <v>BATURK</v>
       </c>
       <c r="B117" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D117" t="str">
         <v>Batu Rakit</v>
@@ -7172,7 +7172,7 @@
         <v>PGCNRG</v>
       </c>
       <c r="B118" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D118" t="str">
         <v>Kampung Chenering</v>
@@ -7189,7 +7189,7 @@
         <v>MARANG</v>
       </c>
       <c r="B119" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D119" t="str">
         <v>Marang</v>
@@ -7206,7 +7206,7 @@
         <v>KLBRNG</v>
       </c>
       <c r="B120" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D120" t="str">
         <v>Kuala Berang</v>
@@ -7223,7 +7223,7 @@
         <v>TSKKEN</v>
       </c>
       <c r="B121" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D121" t="str">
         <v>Tasik Kenyir</v>
@@ -7240,7 +7240,7 @@
         <v>PENERK</v>
       </c>
       <c r="B122" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D122" t="str">
         <v>Penerak</v>
@@ -7257,7 +7257,7 @@
         <v>NENASI</v>
       </c>
       <c r="B123" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D123" t="str">
         <v>Nenasi River Mouth</v>
@@ -7274,7 +7274,7 @@
         <v>PEKAN</v>
       </c>
       <c r="B124" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D124" t="str">
         <v>Pekan Bridge</v>
@@ -7291,7 +7291,7 @@
         <v>KUANTW</v>
       </c>
       <c r="B125" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D125" t="str">
         <v>Tower 188</v>
@@ -7308,7 +7308,7 @@
         <v>TJGELG</v>
       </c>
       <c r="B126" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D126" t="str">
         <v>Juantan Port</v>
@@ -7325,7 +7325,7 @@
         <v>CUKAI</v>
       </c>
       <c r="B127" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D127" t="str">
         <v>Kuala Kemaman</v>
@@ -7342,7 +7342,7 @@
         <v>MARAN</v>
       </c>
       <c r="B128" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D128" t="str">
         <v>Highway Y-Junction</v>
@@ -7359,7 +7359,7 @@
         <v>GAMBNG</v>
       </c>
       <c r="B129" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D129" t="str">
         <v>IIUM Gambang Complex</v>
@@ -7376,7 +7376,7 @@
         <v>LEPAR</v>
       </c>
       <c r="B130" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D130" t="str">
         <v>Lepar Bridge</v>
@@ -7393,7 +7393,7 @@
         <v>MUADZM</v>
       </c>
       <c r="B131" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D131" t="str">
         <v>4-junction Flyover Kuanta</v>
@@ -7410,7 +7410,7 @@
         <v>SGLEMB</v>
       </c>
       <c r="B132" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D132" t="str">
         <v>Football Field Sg Lembing</v>
@@ -7427,7 +7427,7 @@
         <v>LUNDU</v>
       </c>
       <c r="B133" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D133" t="str">
         <v>Lundu</v>
@@ -7444,7 +7444,7 @@
         <v>KGRMBG</v>
       </c>
       <c r="B134" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D134" t="str">
         <v>Kampung Rambungan</v>
@@ -7461,7 +7461,7 @@
         <v>KGSTNG</v>
       </c>
       <c r="B135" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D135" t="str">
         <v>Kampung Stinggang</v>
@@ -7478,7 +7478,7 @@
         <v>MUARTB</v>
       </c>
       <c r="B136" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D136" t="str">
         <v>Muara Tebas</v>
@@ -7495,7 +7495,7 @@
         <v>ABMSEM</v>
       </c>
       <c r="B137" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D137" t="str">
         <v>Abeam Semera</v>
@@ -7512,7 +7512,7 @@
         <v>TEBEDU</v>
       </c>
       <c r="B138" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D138" t="str">
         <v>Tebedu</v>
@@ -7529,7 +7529,7 @@
         <v>SERIAN</v>
       </c>
       <c r="B139" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D139" t="str">
         <v>Serian</v>
@@ -7546,7 +7546,7 @@
         <v>SIMUNJ</v>
       </c>
       <c r="B140" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D140" t="str">
         <v>Simunjan</v>
@@ -7563,7 +7563,7 @@
         <v>KGTRSO</v>
       </c>
       <c r="B141" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D141" t="str">
         <v>Kampung Triso</v>
@@ -7580,7 +7580,7 @@
         <v>KGKUAP</v>
       </c>
       <c r="B142" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D142" t="str">
         <v>Kampung Kuap</v>
@@ -7597,7 +7597,7 @@
         <v>BTSIOL</v>
       </c>
       <c r="B143" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D143" t="str">
         <v>Bukit Siol</v>
@@ -7614,7 +7614,7 @@
         <v>ABMNRB</v>
       </c>
       <c r="B144" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D144" t="str">
         <v>Abeam Narub</v>
@@ -7631,7 +7631,7 @@
         <v>NGATMN</v>
       </c>
       <c r="B145" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D145" t="str">
         <v>Nanga Tamin</v>
@@ -7648,7 +7648,7 @@
         <v>LASSAR</v>
       </c>
       <c r="B146" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D146" t="str">
         <v>Lassa River</v>
@@ -7665,7 +7665,7 @@
         <v>SLNGAU</v>
       </c>
       <c r="B147" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D147" t="str">
         <v>Selangau</v>
@@ -7682,7 +7682,7 @@
         <v>STAPNG</v>
       </c>
       <c r="B148" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D148" t="str">
         <v>Stapang</v>
@@ -7699,7 +7699,7 @@
         <v>TRVRJT</v>
       </c>
       <c r="B149" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D149" t="str">
         <v>T River Junction</v>
@@ -7716,7 +7716,7 @@
         <v>PDUDNG</v>
       </c>
       <c r="B150" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D150" t="str">
         <v>Pulau Dudong</v>
@@ -7733,7 +7733,7 @@
         <v>MERUAN</v>
       </c>
       <c r="B151" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D151" t="str">
         <v>Meruan</v>
@@ -7750,7 +7750,7 @@
         <v>LENG</v>
       </c>
       <c r="B152" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D152" t="str">
         <v>Leng</v>
@@ -7767,7 +7767,7 @@
         <v>PAKAN</v>
       </c>
       <c r="B153" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D153" t="str">
         <v>Pakan Road</v>
@@ -7784,7 +7784,7 @@
         <v>DURIN</v>
       </c>
       <c r="B154" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D154" t="str">
         <v>Durin Town</v>
@@ -7801,7 +7801,7 @@
         <v>KANOWT</v>
       </c>
       <c r="B155" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D155" t="str">
         <v>Kanowit</v>
@@ -7818,7 +7818,7 @@
         <v>PENARK</v>
       </c>
       <c r="B156" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D156" t="str">
         <v>Penarik</v>
@@ -7835,7 +7835,7 @@
         <v>KGSETI</v>
       </c>
       <c r="B157" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D157" t="str">
         <v>Kampung Setiu Lama</v>
@@ -7852,7 +7852,7 @@
         <v>BETLTG</v>
       </c>
       <c r="B158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D158" t="str">
         <v>Beting Lintang</v>
@@ -7869,7 +7869,7 @@
         <v>PRU</v>
       </c>
       <c r="B159" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D159" t="str">
         <v>Pulau Ru</v>
@@ -7886,7 +7886,7 @@
         <v>KGBSUT</v>
       </c>
       <c r="B160" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D160" t="str">
         <v>Kampung Besut</v>
@@ -7903,7 +7903,7 @@
         <v>KGTOKB</v>
       </c>
       <c r="B161" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D161" t="str">
         <v>Kampung Tok Bali</v>
@@ -7920,7 +7920,7 @@
         <v>KGKNGS</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D162" t="str">
         <v>Kampung Kandis</v>
@@ -7937,7 +7937,7 @@
         <v>BACHOK</v>
       </c>
       <c r="B163" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D163" t="str">
         <v>Bachok</v>
@@ -7954,7 +7954,7 @@
         <v>KTBHTW</v>
       </c>
       <c r="B164" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D164" t="str">
         <v>Kota Bharu Town</v>
@@ -7971,7 +7971,7 @@
         <v>KLKRAI</v>
       </c>
       <c r="B165" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D165" t="str">
         <v>Kuala Krai</v>
@@ -7988,7 +7988,7 @@
         <v>TANAMR</v>
       </c>
       <c r="B166" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D166" t="str">
         <v>Tanah Merah</v>
@@ -8005,7 +8005,7 @@
         <v>BTMLTG</v>
       </c>
       <c r="B167" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D167" t="str">
         <v>Bukit Melintang</v>
@@ -8022,7 +8022,7 @@
         <v>JELI</v>
       </c>
       <c r="B168" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D168" t="str">
         <v>Jeli</v>
@@ -8039,7 +8039,7 @@
         <v>KUAH</v>
       </c>
       <c r="B169" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D169" t="str">
         <v>Kuah</v>
@@ -8056,7 +8056,7 @@
         <v>PTIMUN</v>
       </c>
       <c r="B170" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D170" t="str">
         <v>Pulau Timun</v>
@@ -8073,7 +8073,7 @@
         <v>ABMTBA</v>
       </c>
       <c r="B171" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D171" t="str">
         <v>Abeam Pulau Tuba</v>
@@ -8090,7 +8090,7 @@
         <v>PPAYA</v>
       </c>
       <c r="B172" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D172" t="str">
         <v>Pulau Paya</v>
@@ -8107,7 +8107,7 @@
         <v>KLPRLS</v>
       </c>
       <c r="B173" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D173" t="str">
         <v>Kuala Perlis</v>
@@ -8124,7 +8124,7 @@
         <v>AYRHTM</v>
       </c>
       <c r="B174" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D174" t="str">
         <v>Ayer Hitam</v>
@@ -8141,7 +8141,7 @@
         <v>KLKDAH</v>
       </c>
       <c r="B175" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D175" t="str">
         <v>Kuala Kedah</v>
@@ -8158,7 +8158,7 @@
         <v>SPGEMP</v>
       </c>
       <c r="B176" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D176" t="str">
         <v>Simpang Empat</v>
@@ -8175,7 +8175,7 @@
         <v>KTSASE</v>
       </c>
       <c r="B177" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D177" t="str">
         <v>Kota Sarang Semut</v>
@@ -8192,7 +8192,7 @@
         <v>BTHMPR</v>
       </c>
       <c r="B178" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D178" t="str">
         <v>Batu Hampar</v>
@@ -8209,7 +8209,7 @@
         <v>PARIT</v>
       </c>
       <c r="B179" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D179" t="str">
         <v>Parit</v>
@@ -8226,7 +8226,7 @@
         <v>BTGJAH</v>
       </c>
       <c r="B180" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D180" t="str">
         <v>Batu Gajah</v>
@@ -8243,7 +8243,7 @@
         <v>GOPENG</v>
       </c>
       <c r="B181" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D181" t="str">
         <v>Gopeng</v>
@@ -8260,7 +8260,7 @@
         <v>KAMPAR</v>
       </c>
       <c r="B182" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D182" t="str">
         <v>Kampar</v>
@@ -8277,7 +8277,7 @@
         <v>TLINTN</v>
       </c>
       <c r="B183" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D183" t="str">
         <v>Teluk Intan</v>
@@ -8294,7 +8294,7 @@
         <v>BIDOR</v>
       </c>
       <c r="B184" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D184" t="str">
         <v>Bidor</v>
@@ -8326,34 +8326,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="D1" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>283</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -8364,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D2" t="str">
         <f t="shared" ref="D2:D26" si="0">SUBSTITUTE(UPPER(A2), " ", "_")</f>
@@ -8375,7 +8375,7 @@
         <v>SG_BESAR</v>
       </c>
       <c r="F2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G2" t="str">
         <f t="shared" ref="G2:G33" si="1">B2</f>
@@ -8402,7 +8402,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D3" t="str">
         <f t="shared" si="0"/>
@@ -8413,7 +8413,7 @@
         <v>KUALA_SELANGOR</v>
       </c>
       <c r="F3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" si="1"/>
@@ -8440,7 +8440,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D4" t="str">
         <f t="shared" si="0"/>
@@ -8451,7 +8451,7 @@
         <v>KAPAR</v>
       </c>
       <c r="F4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="1"/>
@@ -8478,7 +8478,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
@@ -8489,7 +8489,7 @@
         <v>PORT_KLANG</v>
       </c>
       <c r="F5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="1"/>
@@ -8516,7 +8516,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
@@ -8527,7 +8527,7 @@
         <v>MORIB</v>
       </c>
       <c r="F6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="1"/>
@@ -8554,7 +8554,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
@@ -8565,7 +8565,7 @@
         <v>TJ_SEPAT</v>
       </c>
       <c r="F7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="1"/>
@@ -8592,7 +8592,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
@@ -8603,7 +8603,7 @@
         <v>TJ_TUAN_(CAPE_RACHARDO)</v>
       </c>
       <c r="F8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" si="1"/>
@@ -8630,7 +8630,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
@@ -8641,7 +8641,7 @@
         <v>SLIM_RIVER</v>
       </c>
       <c r="F9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="1"/>
@@ -8668,7 +8668,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
@@ -8679,7 +8679,7 @@
         <v>TJ_MALIM</v>
       </c>
       <c r="F10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="1"/>
@@ -8706,7 +8706,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D11" t="str">
         <f t="shared" si="0"/>
@@ -8717,7 +8717,7 @@
         <v>RAWANG</v>
       </c>
       <c r="F11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" si="1"/>
@@ -8744,7 +8744,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D12" t="str">
         <f t="shared" si="0"/>
@@ -8755,7 +8755,7 @@
         <v>BATU_CAVES</v>
       </c>
       <c r="F12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="1"/>
@@ -8782,7 +8782,7 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D13" t="str">
         <f t="shared" si="0"/>
@@ -8793,7 +8793,7 @@
         <v>SG_BESI</v>
       </c>
       <c r="F13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
@@ -8820,7 +8820,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
@@ -8831,7 +8831,7 @@
         <v>KAJANG</v>
       </c>
       <c r="F14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="1"/>
@@ -8858,7 +8858,7 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
@@ -8869,7 +8869,7 @@
         <v>SEREMBAN</v>
       </c>
       <c r="F15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="1"/>
@@ -8896,7 +8896,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
@@ -8907,7 +8907,7 @@
         <v>BENTONG</v>
       </c>
       <c r="F16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" si="1"/>
@@ -8934,7 +8934,7 @@
         <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
@@ -8945,7 +8945,7 @@
         <v>RANTAU</v>
       </c>
       <c r="F17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="1"/>
@@ -8972,7 +8972,7 @@
         <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
@@ -8983,7 +8983,7 @@
         <v>KUALA_KELAWANG</v>
       </c>
       <c r="F18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="1"/>
@@ -9010,7 +9010,7 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D19" t="str">
         <f t="shared" si="0"/>
@@ -9021,7 +9021,7 @@
         <v>PETALING_JAYA</v>
       </c>
       <c r="F19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="1"/>
@@ -9048,7 +9048,7 @@
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D20" t="str">
         <f t="shared" si="0"/>
@@ -9059,7 +9059,7 @@
         <v>BT_LANJAN</v>
       </c>
       <c r="F20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="1"/>
@@ -9086,7 +9086,7 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D21" t="str">
         <f t="shared" si="0"/>
@@ -9097,7 +9097,7 @@
         <v>PUNCAK_PERDANA</v>
       </c>
       <c r="F21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="1"/>
@@ -9124,7 +9124,7 @@
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D22" t="str">
         <f t="shared" si="0"/>
@@ -9135,7 +9135,7 @@
         <v>SHAH_ALAM</v>
       </c>
       <c r="F22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="1"/>
@@ -9159,10 +9159,10 @@
         <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>623</v>
       </c>
       <c r="C23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D23" t="str">
         <f t="shared" si="0"/>
@@ -9173,15 +9173,15 @@
         <v>KUANG</v>
       </c>
       <c r="F23" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="1"/>
-        <v>Guthrie – LATAR Expressway Kuang Exit</v>
+        <v>Guthrie - LATAR Expressway Kuang Exit</v>
       </c>
       <c r="H23" t="str">
         <f t="shared" si="4"/>
-        <v>Guthrie – LATAR Expresswa</v>
+        <v>Guthrie - LATAR Expresswa</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
@@ -9194,13 +9194,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
         <v>44</v>
       </c>
-      <c r="B24" t="s">
-        <v>45</v>
-      </c>
       <c r="C24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D24" t="str">
         <f t="shared" si="0"/>
@@ -9211,7 +9211,7 @@
         <v>NIBONG_GILA</v>
       </c>
       <c r="F24" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="1"/>
@@ -9232,13 +9232,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
         <v>46</v>
       </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
       <c r="C25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D25" t="str">
         <f t="shared" si="0"/>
@@ -9249,7 +9249,7 @@
         <v>TITIWANGSA</v>
       </c>
       <c r="F25" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="1"/>
@@ -9270,13 +9270,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
         <v>48</v>
       </c>
-      <c r="B26" t="s">
-        <v>49</v>
-      </c>
       <c r="C26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D26" t="str">
         <f t="shared" si="0"/>
@@ -9287,7 +9287,7 @@
         <v>SEGAMBUT</v>
       </c>
       <c r="F26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" si="1"/>
@@ -9308,13 +9308,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
         <v>50</v>
-      </c>
-      <c r="B27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" t="s">
-        <v>51</v>
       </c>
       <c r="D27" t="str">
         <f>SUBSTITUTE(UPPER(A27), " ", "_")</f>
@@ -9325,7 +9325,7 @@
         <v>UTM_MOSQUE</v>
       </c>
       <c r="F27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="1"/>
@@ -9346,13 +9346,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
         <v>52</v>
-      </c>
-      <c r="B28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" t="s">
-        <v>53</v>
       </c>
       <c r="D28" t="str">
         <f t="shared" ref="D28:D91" si="5">SUBSTITUTE(UPPER(A28), " ", "_")</f>
@@ -9363,7 +9363,7 @@
         <v>BENUT</v>
       </c>
       <c r="F28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="1"/>
@@ -9384,13 +9384,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" t="s">
         <v>54</v>
-      </c>
-      <c r="B29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" t="s">
-        <v>55</v>
       </c>
       <c r="D29" t="str">
         <f t="shared" si="5"/>
@@ -9401,7 +9401,7 @@
         <v>KULAI_TOL_PLAZA</v>
       </c>
       <c r="F29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G29" t="str">
         <f t="shared" si="1"/>
@@ -9422,13 +9422,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" t="s">
         <v>56</v>
-      </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" t="s">
-        <v>57</v>
       </c>
       <c r="D30" t="str">
         <f t="shared" si="5"/>
@@ -9439,7 +9439,7 @@
         <v>EAST_JOHOR_BAHRU_AIRFIELD</v>
       </c>
       <c r="F30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="1"/>
@@ -9460,13 +9460,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
         <v>58</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" t="s">
-        <v>59</v>
       </c>
       <c r="D31" t="str">
         <f t="shared" si="5"/>
@@ -9477,7 +9477,7 @@
         <v>KOTA_TINGGI_BRIDGE</v>
       </c>
       <c r="F31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="1"/>
@@ -9498,13 +9498,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D32" t="str">
         <f t="shared" si="5"/>
@@ -9515,7 +9515,7 @@
         <v>EAST_KG_SG_TIRAM</v>
       </c>
       <c r="F32" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="1"/>
@@ -9536,13 +9536,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" t="s">
         <v>61</v>
-      </c>
-      <c r="B33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" t="s">
-        <v>62</v>
       </c>
       <c r="D33" t="str">
         <f t="shared" si="5"/>
@@ -9553,7 +9553,7 @@
         <v>EAST_JOHOR_BAHRU_TOWN</v>
       </c>
       <c r="F33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
@@ -9574,13 +9574,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" t="s">
         <v>63</v>
-      </c>
-      <c r="B34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" t="s">
-        <v>64</v>
       </c>
       <c r="D34" t="str">
         <f t="shared" si="5"/>
@@ -9591,7 +9591,7 @@
         <v>FELDA_ULU_TEBRAU</v>
       </c>
       <c r="F34" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" ref="G34:G65" si="6">B34</f>
@@ -9612,13 +9612,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" t="s">
         <v>65</v>
-      </c>
-      <c r="B35" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" t="s">
-        <v>66</v>
       </c>
       <c r="D35" t="str">
         <f t="shared" si="5"/>
@@ -9629,7 +9629,7 @@
         <v>TEBRAU_CITY_MALL</v>
       </c>
       <c r="F35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="6"/>
@@ -9650,13 +9650,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B36" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D36" t="str">
         <f t="shared" si="5"/>
@@ -9667,7 +9667,7 @@
         <v>SOUTH_KG_SEMANGAR</v>
       </c>
       <c r="F36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="6"/>
@@ -9688,13 +9688,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B37" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D37" t="str">
         <f t="shared" si="5"/>
@@ -9705,7 +9705,7 @@
         <v>KG_SEDILI_BESAR</v>
       </c>
       <c r="F37" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="6"/>
@@ -9726,13 +9726,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D38" t="str">
         <f t="shared" si="5"/>
@@ -9743,7 +9743,7 @@
         <v>SIMPANG_RENGGAM_TOWN</v>
       </c>
       <c r="F38" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G38" t="str">
         <f t="shared" si="6"/>
@@ -9764,13 +9764,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" t="s">
         <v>70</v>
-      </c>
-      <c r="B39" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" t="s">
-        <v>71</v>
       </c>
       <c r="D39" t="str">
         <f t="shared" si="5"/>
@@ -9781,7 +9781,7 @@
         <v>AIR_HITAM</v>
       </c>
       <c r="F39" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="6"/>
@@ -9802,13 +9802,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" t="s">
         <v>72</v>
-      </c>
-      <c r="B40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" t="s">
-        <v>73</v>
       </c>
       <c r="D40" t="str">
         <f t="shared" si="5"/>
@@ -9819,7 +9819,7 @@
         <v>YONG_PENG</v>
       </c>
       <c r="F40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="6"/>
@@ -9840,13 +9840,13 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D41" t="str">
         <f t="shared" si="5"/>
@@ -9857,7 +9857,7 @@
         <v>POINT_XRAY</v>
       </c>
       <c r="F41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G41" t="str">
         <f t="shared" si="6"/>
@@ -9878,13 +9878,13 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D42" t="str">
         <f t="shared" si="5"/>
@@ -9895,7 +9895,7 @@
         <v>TASS_ANDRASSY</v>
       </c>
       <c r="F42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="6"/>
@@ -9916,13 +9916,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D43" t="str">
         <f t="shared" si="5"/>
@@ -9933,7 +9933,7 @@
         <v>OLD_AIRPORT</v>
       </c>
       <c r="F43" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="6"/>
@@ -9954,13 +9954,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D44" t="str">
         <f t="shared" si="5"/>
@@ -9971,7 +9971,7 @@
         <v>SEBATIK_IS</v>
       </c>
       <c r="F44" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G44" t="str">
         <f t="shared" si="6"/>
@@ -9992,13 +9992,13 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D45" t="str">
         <f t="shared" si="5"/>
@@ -10009,7 +10009,7 @@
         <v>KALABAKAN</v>
       </c>
       <c r="F45" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G45" t="str">
         <f t="shared" si="6"/>
@@ -10030,13 +10030,13 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D46" t="str">
         <f t="shared" si="5"/>
@@ -10047,7 +10047,7 @@
         <v>BALUNG</v>
       </c>
       <c r="F46" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G46" t="str">
         <f t="shared" si="6"/>
@@ -10068,13 +10068,13 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D47" t="str">
         <f t="shared" si="5"/>
@@ -10085,7 +10085,7 @@
         <v>KAWA_HILL</v>
       </c>
       <c r="F47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G47" t="str">
         <f t="shared" si="6"/>
@@ -10106,13 +10106,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" t="str">
         <f t="shared" si="5"/>
@@ -10123,7 +10123,7 @@
         <v>MT_PYRAMID</v>
       </c>
       <c r="F48" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G48" t="str">
         <f t="shared" si="6"/>
@@ -10144,13 +10144,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49" t="str">
         <f t="shared" si="5"/>
@@ -10161,7 +10161,7 @@
         <v>BATURONG</v>
       </c>
       <c r="F49" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G49" t="str">
         <f t="shared" si="6"/>
@@ -10182,13 +10182,13 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D50" t="str">
         <f t="shared" si="5"/>
@@ -10199,7 +10199,7 @@
         <v>DANUM</v>
       </c>
       <c r="F50" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G50" t="str">
         <f t="shared" si="6"/>
@@ -10220,13 +10220,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D51" t="str">
         <f>SUBSTITUTE(UPPER(A51), " ", "_")</f>
@@ -10237,7 +10237,7 @@
         <v>JUNCTION_(49KM)</v>
       </c>
       <c r="F51" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G51" t="str">
         <f t="shared" si="6"/>
@@ -10258,13 +10258,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B52" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D52" t="str">
         <f t="shared" si="5"/>
@@ -10275,7 +10275,7 @@
         <v>KG_AMAN</v>
       </c>
       <c r="F52" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G52" t="str">
         <f t="shared" si="6"/>
@@ -10296,13 +10296,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B53" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D53" t="str">
         <f t="shared" si="5"/>
@@ -10313,7 +10313,7 @@
         <v>TJ_BATAI</v>
       </c>
       <c r="F53" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G53" t="str">
         <f t="shared" si="6"/>
@@ -10334,13 +10334,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D54" t="str">
         <f t="shared" si="5"/>
@@ -10351,7 +10351,7 @@
         <v>SADDLE_HILL</v>
       </c>
       <c r="F54" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G54" t="str">
         <f t="shared" si="6"/>
@@ -10372,13 +10372,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D55" t="str">
         <f t="shared" si="5"/>
@@ -10389,7 +10389,7 @@
         <v>NAGOS</v>
       </c>
       <c r="F55" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G55" t="str">
         <f t="shared" si="6"/>
@@ -10410,13 +10410,13 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D56" t="str">
         <f t="shared" si="5"/>
@@ -10427,7 +10427,7 @@
         <v>SEMPORNA</v>
       </c>
       <c r="F56" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G56" t="str">
         <f t="shared" si="6"/>
@@ -10448,13 +10448,13 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D57" t="str">
         <f t="shared" si="5"/>
@@ -10465,7 +10465,7 @@
         <v>GAYA_IS</v>
       </c>
       <c r="F57" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G57" t="str">
         <f t="shared" si="6"/>
@@ -10486,13 +10486,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C58" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D58" t="str">
         <f t="shared" si="5"/>
@@ -10503,7 +10503,7 @@
         <v>SIPADAN_IS</v>
       </c>
       <c r="F58" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G58" t="str">
         <f t="shared" si="6"/>
@@ -10524,13 +10524,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C59" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D59" t="str">
         <f t="shared" si="5"/>
@@ -10541,7 +10541,7 @@
         <v>BANDAR_INDAH_(ROAD_JUNCTION)</v>
       </c>
       <c r="F59" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G59" t="str">
         <f t="shared" si="6"/>
@@ -10562,13 +10562,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B60" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D60" t="str">
         <f t="shared" si="5"/>
@@ -10579,7 +10579,7 @@
         <v>KAMPONG_TOBANKA</v>
       </c>
       <c r="F60" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G60" t="str">
         <f t="shared" si="6"/>
@@ -10600,13 +10600,13 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D61" t="str">
         <f t="shared" si="5"/>
@@ -10617,7 +10617,7 @@
         <v>BAI_IS</v>
       </c>
       <c r="F61" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G61" t="str">
         <f t="shared" si="6"/>
@@ -10638,13 +10638,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D62" t="str">
         <f t="shared" si="5"/>
@@ -10655,7 +10655,7 @@
         <v>TJ_BIDADARI</v>
       </c>
       <c r="F62" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G62" t="str">
         <f t="shared" si="6"/>
@@ -10676,13 +10676,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D63" t="str">
         <f t="shared" si="5"/>
@@ -10693,7 +10693,7 @@
         <v>KUALA_KINABATANGAN_BESAR</v>
       </c>
       <c r="F63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G63" t="str">
         <f t="shared" si="6"/>
@@ -10714,13 +10714,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D64" t="str">
         <f t="shared" si="5"/>
@@ -10731,7 +10731,7 @@
         <v>KG_BILIT</v>
       </c>
       <c r="F64" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G64" t="str">
         <f t="shared" si="6"/>
@@ -10752,13 +10752,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D65" t="str">
         <f t="shared" si="5"/>
@@ -10769,7 +10769,7 @@
         <v>SG_SEGUNTOR</v>
       </c>
       <c r="F65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G65" t="str">
         <f t="shared" si="6"/>
@@ -10790,13 +10790,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B66" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D66" t="str">
         <f t="shared" si="5"/>
@@ -10807,7 +10807,7 @@
         <v>KOTA_KINABATANGAN</v>
       </c>
       <c r="F66" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G66" t="str">
         <f t="shared" ref="G66:G97" si="9">B66</f>
@@ -10828,13 +10828,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B67" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D67" t="str">
         <f t="shared" si="5"/>
@@ -10845,7 +10845,7 @@
         <v>KG_KUALA_LOKAN</v>
       </c>
       <c r="F67" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G67" t="str">
         <f t="shared" si="9"/>
@@ -10866,13 +10866,13 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B68" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D68" t="str">
         <f t="shared" si="5"/>
@@ -10883,7 +10883,7 @@
         <v>MILE_32_RD_JUNCTION</v>
       </c>
       <c r="F68" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G68" t="str">
         <f t="shared" si="9"/>
@@ -10904,13 +10904,13 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C69" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D69" t="str">
         <f t="shared" si="5"/>
@@ -10921,7 +10921,7 @@
         <v>TELUPID</v>
       </c>
       <c r="F69" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G69" t="str">
         <f t="shared" si="9"/>
@@ -10942,13 +10942,13 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B70" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C70" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D70" t="str">
         <f t="shared" si="5"/>
@@ -10959,7 +10959,7 @@
         <v>KG_GUMGUM_LAUT</v>
       </c>
       <c r="F70" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G70" t="str">
         <f t="shared" si="9"/>
@@ -10980,13 +10980,13 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C71" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D71" t="str">
         <f t="shared" si="5"/>
@@ -10997,7 +10997,7 @@
         <v>KG_SEMAWANG</v>
       </c>
       <c r="F71" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="9"/>
@@ -11018,13 +11018,13 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D72" t="str">
         <f t="shared" si="5"/>
@@ -11035,7 +11035,7 @@
         <v>BELURAN</v>
       </c>
       <c r="F72" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G72" t="str">
         <f t="shared" si="9"/>
@@ -11056,13 +11056,13 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B73" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D73" t="str">
         <f t="shared" si="5"/>
@@ -11073,7 +11073,7 @@
         <v>KENAWI_IS</v>
       </c>
       <c r="F73" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G73" t="str">
         <f t="shared" si="9"/>
@@ -11094,13 +11094,13 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B74" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D74" t="str">
         <f t="shared" si="5"/>
@@ -11111,7 +11111,7 @@
         <v>KG_SG-SG</v>
       </c>
       <c r="F74" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G74" t="str">
         <f t="shared" si="9"/>
@@ -11132,13 +11132,13 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C75" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D75" t="str">
         <f t="shared" si="5"/>
@@ -11149,7 +11149,7 @@
         <v>KG_TERUSAN</v>
       </c>
       <c r="F75" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G75" t="str">
         <f t="shared" si="9"/>
@@ -11170,13 +11170,13 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B76" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C76" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D76" t="str">
         <f t="shared" si="5"/>
@@ -11187,7 +11187,7 @@
         <v>SELINGAN_IS</v>
       </c>
       <c r="F76" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G76" t="str">
         <f t="shared" si="9"/>
@@ -11208,13 +11208,13 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B77" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C77" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D77" t="str">
         <f t="shared" si="5"/>
@@ -11225,7 +11225,7 @@
         <v>LANKAYAN_IS</v>
       </c>
       <c r="F77" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G77" t="str">
         <f t="shared" si="9"/>
@@ -11246,13 +11246,13 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B78" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C78" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D78" t="str">
         <f t="shared" si="5"/>
@@ -11263,7 +11263,7 @@
         <v>SOUTH_BERHALA_IS</v>
       </c>
       <c r="F78" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G78" t="str">
         <f t="shared" si="9"/>
@@ -11284,13 +11284,13 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B79" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C79" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D79" t="str">
         <f t="shared" si="5"/>
@@ -11301,7 +11301,7 @@
         <v>LUANG_MANIS</v>
       </c>
       <c r="F79" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G79" t="str">
         <f t="shared" si="9"/>
@@ -11322,13 +11322,13 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B80" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C80" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D80" t="str">
         <f t="shared" si="5"/>
@@ -11339,7 +11339,7 @@
         <v>PAMAGUAN_PRIMARY_SCHOOL</v>
       </c>
       <c r="F80" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G80" t="str">
         <f t="shared" si="9"/>
@@ -11360,13 +11360,13 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B81" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C81" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D81" t="str">
         <f t="shared" si="5"/>
@@ -11377,7 +11377,7 @@
         <v>PORT_WELD</v>
       </c>
       <c r="F81" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G81" t="str">
         <f t="shared" si="9"/>
@@ -11398,13 +11398,13 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B82" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C82" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D82" t="str">
         <f t="shared" si="5"/>
@@ -11415,7 +11415,7 @@
         <v>TJ_PIANDANG</v>
       </c>
       <c r="F82" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G82" t="str">
         <f t="shared" si="9"/>
@@ -11436,13 +11436,13 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B83" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C83" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D83" t="str">
         <f t="shared" si="5"/>
@@ -11453,7 +11453,7 @@
         <v>SOUTH_P_AMAN</v>
       </c>
       <c r="F83" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G83" t="str">
         <f t="shared" si="9"/>
@@ -11474,13 +11474,13 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B84" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C84" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D84" t="str">
         <f t="shared" si="5"/>
@@ -11491,7 +11491,7 @@
         <v>KEDAH_PEAK_WEST</v>
       </c>
       <c r="F84" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G84" t="str">
         <f t="shared" si="9"/>
@@ -11512,13 +11512,13 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B85" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D85" t="str">
         <f t="shared" si="5"/>
@@ -11529,7 +11529,7 @@
         <v>KUALA_SG_MUDA</v>
       </c>
       <c r="F85" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G85" t="str">
         <f t="shared" si="9"/>
@@ -11550,13 +11550,13 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C86" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D86" t="str">
         <f t="shared" si="5"/>
@@ -11567,7 +11567,7 @@
         <v>NORTH_GEORGE_TOWN</v>
       </c>
       <c r="F86" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G86" t="str">
         <f t="shared" si="9"/>
@@ -11588,13 +11588,13 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>152</v>
+      </c>
+      <c r="B87" t="s">
+        <v>152</v>
+      </c>
+      <c r="C87" t="s">
         <v>153</v>
-      </c>
-      <c r="B87" t="s">
-        <v>153</v>
-      </c>
-      <c r="C87" t="s">
-        <v>154</v>
       </c>
       <c r="D87" t="str">
         <f t="shared" si="5"/>
@@ -11605,7 +11605,7 @@
         <v>WEST_P_GAYA</v>
       </c>
       <c r="F87" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G87" t="str">
         <f t="shared" si="9"/>
@@ -11626,13 +11626,13 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>154</v>
+      </c>
+      <c r="B88" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" t="s">
         <v>155</v>
-      </c>
-      <c r="B88" t="s">
-        <v>155</v>
-      </c>
-      <c r="C88" t="s">
-        <v>156</v>
       </c>
       <c r="D88" t="str">
         <f t="shared" si="5"/>
@@ -11643,7 +11643,7 @@
         <v>P_SULUG</v>
       </c>
       <c r="F88" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G88" t="str">
         <f t="shared" si="9"/>
@@ -11664,13 +11664,13 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>156</v>
+      </c>
+      <c r="B89" t="s">
+        <v>156</v>
+      </c>
+      <c r="C89" t="s">
         <v>157</v>
-      </c>
-      <c r="B89" t="s">
-        <v>157</v>
-      </c>
-      <c r="C89" t="s">
-        <v>158</v>
       </c>
       <c r="D89" t="str">
         <f t="shared" si="5"/>
@@ -11681,7 +11681,7 @@
         <v>P_TIGA</v>
       </c>
       <c r="F89" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G89" t="str">
         <f t="shared" si="9"/>
@@ -11702,13 +11702,13 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" t="s">
+        <v>158</v>
+      </c>
+      <c r="C90" t="s">
         <v>159</v>
-      </c>
-      <c r="B90" t="s">
-        <v>159</v>
-      </c>
-      <c r="C90" t="s">
-        <v>160</v>
       </c>
       <c r="D90" t="str">
         <f t="shared" si="5"/>
@@ -11719,7 +11719,7 @@
         <v>KUALA_PENYU</v>
       </c>
       <c r="F90" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G90" t="str">
         <f t="shared" si="9"/>
@@ -11740,13 +11740,13 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>160</v>
+      </c>
+      <c r="B91" t="s">
+        <v>160</v>
+      </c>
+      <c r="C91" t="s">
         <v>161</v>
-      </c>
-      <c r="B91" t="s">
-        <v>161</v>
-      </c>
-      <c r="C91" t="s">
-        <v>162</v>
       </c>
       <c r="D91" t="str">
         <f t="shared" si="5"/>
@@ -11757,7 +11757,7 @@
         <v>BONGAWAN</v>
       </c>
       <c r="F91" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G91" t="str">
         <f t="shared" si="9"/>
@@ -11778,13 +11778,13 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>162</v>
+      </c>
+      <c r="B92" t="s">
+        <v>162</v>
+      </c>
+      <c r="C92" t="s">
         <v>163</v>
-      </c>
-      <c r="B92" t="s">
-        <v>163</v>
-      </c>
-      <c r="C92" t="s">
-        <v>164</v>
       </c>
       <c r="D92" t="str">
         <f t="shared" ref="D92:D156" si="13">SUBSTITUTE(UPPER(A92), " ", "_")</f>
@@ -11795,7 +11795,7 @@
         <v>EAST_PAPAR</v>
       </c>
       <c r="F92" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G92" t="str">
         <f t="shared" si="9"/>
@@ -11816,13 +11816,13 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>164</v>
+      </c>
+      <c r="B93" t="s">
+        <v>164</v>
+      </c>
+      <c r="C93" t="s">
         <v>165</v>
-      </c>
-      <c r="B93" t="s">
-        <v>165</v>
-      </c>
-      <c r="C93" t="s">
-        <v>166</v>
       </c>
       <c r="D93" t="str">
         <f t="shared" si="13"/>
@@ -11833,7 +11833,7 @@
         <v>EAST_KAWANG</v>
       </c>
       <c r="F93" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G93" t="str">
         <f t="shared" si="9"/>
@@ -11854,13 +11854,13 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>166</v>
+      </c>
+      <c r="B94" t="s">
+        <v>166</v>
+      </c>
+      <c r="C94" t="s">
         <v>167</v>
-      </c>
-      <c r="B94" t="s">
-        <v>167</v>
-      </c>
-      <c r="C94" t="s">
-        <v>168</v>
       </c>
       <c r="D94" t="str">
         <f t="shared" si="13"/>
@@ -11871,7 +11871,7 @@
         <v>EAST_KINARUT_TOWN</v>
       </c>
       <c r="F94" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G94" t="str">
         <f t="shared" si="9"/>
@@ -11892,13 +11892,13 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>168</v>
+      </c>
+      <c r="B95" t="s">
+        <v>168</v>
+      </c>
+      <c r="C95" t="s">
         <v>169</v>
-      </c>
-      <c r="B95" t="s">
-        <v>169</v>
-      </c>
-      <c r="C95" t="s">
-        <v>170</v>
       </c>
       <c r="D95" t="str">
         <f t="shared" si="13"/>
@@ -11909,7 +11909,7 @@
         <v>KEPAYAN</v>
       </c>
       <c r="F95" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G95" t="str">
         <f t="shared" si="9"/>
@@ -11930,13 +11930,13 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>170</v>
+      </c>
+      <c r="B96" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" t="s">
         <v>171</v>
-      </c>
-      <c r="B96" t="s">
-        <v>171</v>
-      </c>
-      <c r="C96" t="s">
-        <v>172</v>
       </c>
       <c r="D96" t="str">
         <f t="shared" si="13"/>
@@ -11947,7 +11947,7 @@
         <v>EAST_INANAM_TOWN</v>
       </c>
       <c r="F96" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G96" t="str">
         <f t="shared" si="9"/>
@@ -11968,13 +11968,13 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>172</v>
+      </c>
+      <c r="B97" t="s">
+        <v>172</v>
+      </c>
+      <c r="C97" t="s">
         <v>173</v>
-      </c>
-      <c r="B97" t="s">
-        <v>173</v>
-      </c>
-      <c r="C97" t="s">
-        <v>174</v>
       </c>
       <c r="D97" t="str">
         <f t="shared" si="13"/>
@@ -11985,7 +11985,7 @@
         <v>EAST_TELIPOK</v>
       </c>
       <c r="F97" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G97" t="str">
         <f t="shared" si="9"/>
@@ -12006,13 +12006,13 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>174</v>
+      </c>
+      <c r="B98" t="s">
+        <v>174</v>
+      </c>
+      <c r="C98" t="s">
         <v>175</v>
-      </c>
-      <c r="B98" t="s">
-        <v>175</v>
-      </c>
-      <c r="C98" t="s">
-        <v>176</v>
       </c>
       <c r="D98" t="str">
         <f t="shared" si="13"/>
@@ -12023,7 +12023,7 @@
         <v>KG_KIULU</v>
       </c>
       <c r="F98" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G98" t="str">
         <f t="shared" ref="G98:G129" si="14">B98</f>
@@ -12044,13 +12044,13 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" t="s">
+        <v>176</v>
+      </c>
+      <c r="C99" t="s">
         <v>177</v>
-      </c>
-      <c r="B99" t="s">
-        <v>177</v>
-      </c>
-      <c r="C99" t="s">
-        <v>178</v>
       </c>
       <c r="D99" t="str">
         <f t="shared" si="13"/>
@@ -12061,7 +12061,7 @@
         <v>KG_BALABAKAN</v>
       </c>
       <c r="F99" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G99" t="str">
         <f t="shared" si="14"/>
@@ -12082,13 +12082,13 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>178</v>
+      </c>
+      <c r="B100" t="s">
+        <v>178</v>
+      </c>
+      <c r="C100" t="s">
         <v>179</v>
-      </c>
-      <c r="B100" t="s">
-        <v>179</v>
-      </c>
-      <c r="C100" t="s">
-        <v>180</v>
       </c>
       <c r="D100" t="str">
         <f t="shared" si="13"/>
@@ -12099,7 +12099,7 @@
         <v>RANAU</v>
       </c>
       <c r="F100" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G100" t="str">
         <f t="shared" si="14"/>
@@ -12120,13 +12120,13 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>180</v>
+      </c>
+      <c r="B101" t="s">
+        <v>180</v>
+      </c>
+      <c r="C101" t="s">
         <v>181</v>
-      </c>
-      <c r="B101" t="s">
-        <v>181</v>
-      </c>
-      <c r="C101" t="s">
-        <v>182</v>
       </c>
       <c r="D101" t="str">
         <f t="shared" si="13"/>
@@ -12137,7 +12137,7 @@
         <v>WEST_HILL_1040</v>
       </c>
       <c r="F101" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G101" t="str">
         <f t="shared" si="14"/>
@@ -12158,13 +12158,13 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>182</v>
+      </c>
+      <c r="B102" t="s">
+        <v>182</v>
+      </c>
+      <c r="C102" t="s">
         <v>183</v>
-      </c>
-      <c r="B102" t="s">
-        <v>183</v>
-      </c>
-      <c r="C102" t="s">
-        <v>184</v>
       </c>
       <c r="D102" t="str">
         <f t="shared" si="13"/>
@@ -12175,7 +12175,7 @@
         <v>TJ_DALIT</v>
       </c>
       <c r="F102" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G102" t="str">
         <f t="shared" si="14"/>
@@ -12196,13 +12196,13 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>184</v>
+      </c>
+      <c r="B103" t="s">
+        <v>184</v>
+      </c>
+      <c r="C103" t="s">
         <v>185</v>
-      </c>
-      <c r="B103" t="s">
-        <v>185</v>
-      </c>
-      <c r="C103" t="s">
-        <v>186</v>
       </c>
       <c r="D103" t="str">
         <f t="shared" si="13"/>
@@ -12213,7 +12213,7 @@
         <v>KOTA_BELUD</v>
       </c>
       <c r="F103" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G103" t="str">
         <f t="shared" si="14"/>
@@ -12234,13 +12234,13 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>223</v>
+      </c>
+      <c r="B104" t="s">
+        <v>223</v>
+      </c>
+      <c r="C104" t="s">
         <v>224</v>
-      </c>
-      <c r="B104" t="s">
-        <v>224</v>
-      </c>
-      <c r="C104" t="s">
-        <v>225</v>
       </c>
       <c r="D104" t="str">
         <f t="shared" si="13"/>
@@ -12251,7 +12251,7 @@
         <v>TERENDAK</v>
       </c>
       <c r="F104" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G104" t="str">
         <f t="shared" si="14"/>
@@ -12272,13 +12272,13 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>225</v>
+      </c>
+      <c r="B105" t="s">
+        <v>225</v>
+      </c>
+      <c r="C105" t="s">
         <v>226</v>
-      </c>
-      <c r="B105" t="s">
-        <v>226</v>
-      </c>
-      <c r="C105" t="s">
-        <v>227</v>
       </c>
       <c r="D105" t="str">
         <f t="shared" si="13"/>
@@ -12289,7 +12289,7 @@
         <v>REMBIA</v>
       </c>
       <c r="F105" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G105" t="str">
         <f t="shared" si="14"/>
@@ -12310,13 +12310,13 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>227</v>
+      </c>
+      <c r="B106" t="s">
+        <v>227</v>
+      </c>
+      <c r="C106" t="s">
         <v>228</v>
-      </c>
-      <c r="B106" t="s">
-        <v>228</v>
-      </c>
-      <c r="C106" t="s">
-        <v>229</v>
       </c>
       <c r="D106" t="str">
         <f t="shared" si="13"/>
@@ -12327,7 +12327,7 @@
         <v>TAMPIN</v>
       </c>
       <c r="F106" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G106" t="str">
         <f t="shared" si="14"/>
@@ -12348,13 +12348,13 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>229</v>
+      </c>
+      <c r="B107" t="s">
+        <v>229</v>
+      </c>
+      <c r="C107" t="s">
         <v>230</v>
-      </c>
-      <c r="B107" t="s">
-        <v>230</v>
-      </c>
-      <c r="C107" t="s">
-        <v>231</v>
       </c>
       <c r="D107" t="str">
         <f t="shared" si="13"/>
@@ -12365,7 +12365,7 @@
         <v>CHIN_CHIN</v>
       </c>
       <c r="F107" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G107" t="str">
         <f t="shared" si="14"/>
@@ -12386,13 +12386,13 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>231</v>
+      </c>
+      <c r="B108" t="s">
+        <v>231</v>
+      </c>
+      <c r="C108" t="s">
         <v>232</v>
-      </c>
-      <c r="B108" t="s">
-        <v>232</v>
-      </c>
-      <c r="C108" t="s">
-        <v>233</v>
       </c>
       <c r="D108" t="str">
         <f t="shared" si="13"/>
@@ -12403,7 +12403,7 @@
         <v>BT_BERUANG</v>
       </c>
       <c r="F108" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G108" t="str">
         <f t="shared" si="14"/>
@@ -12424,13 +12424,13 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>233</v>
+      </c>
+      <c r="B109" t="s">
+        <v>233</v>
+      </c>
+      <c r="C109" t="s">
         <v>234</v>
-      </c>
-      <c r="B109" t="s">
-        <v>234</v>
-      </c>
-      <c r="C109" t="s">
-        <v>235</v>
       </c>
       <c r="D109" t="str">
         <f t="shared" si="13"/>
@@ -12441,7 +12441,7 @@
         <v>UMBAI</v>
       </c>
       <c r="F109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G109" t="str">
         <f t="shared" si="14"/>
@@ -12462,13 +12462,13 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>235</v>
+      </c>
+      <c r="B110" t="s">
+        <v>235</v>
+      </c>
+      <c r="C110" t="s">
         <v>236</v>
-      </c>
-      <c r="B110" t="s">
-        <v>236</v>
-      </c>
-      <c r="C110" t="s">
-        <v>237</v>
       </c>
       <c r="D110" t="str">
         <f t="shared" si="13"/>
@@ -12479,7 +12479,7 @@
         <v>MALACCA_CITY</v>
       </c>
       <c r="F110" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G110" t="str">
         <f t="shared" si="14"/>
@@ -12500,13 +12500,13 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>237</v>
+      </c>
+      <c r="B111" t="s">
+        <v>237</v>
+      </c>
+      <c r="C111" t="s">
         <v>238</v>
-      </c>
-      <c r="B111" t="s">
-        <v>238</v>
-      </c>
-      <c r="C111" t="s">
-        <v>239</v>
       </c>
       <c r="D111" t="str">
         <f t="shared" si="13"/>
@@ -12517,7 +12517,7 @@
         <v>MUAR</v>
       </c>
       <c r="F111" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G111" t="str">
         <f t="shared" si="14"/>
@@ -12538,13 +12538,13 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>239</v>
+      </c>
+      <c r="B112" t="s">
+        <v>239</v>
+      </c>
+      <c r="C112" t="s">
         <v>240</v>
-      </c>
-      <c r="B112" t="s">
-        <v>240</v>
-      </c>
-      <c r="C112" t="s">
-        <v>241</v>
       </c>
       <c r="D112" t="str">
         <f t="shared" si="13"/>
@@ -12555,7 +12555,7 @@
         <v>TANGKAK</v>
       </c>
       <c r="F112" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G112" t="str">
         <f t="shared" si="14"/>
@@ -12576,13 +12576,13 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>241</v>
+      </c>
+      <c r="B113" t="s">
+        <v>241</v>
+      </c>
+      <c r="C113" t="s">
         <v>242</v>
-      </c>
-      <c r="B113" t="s">
-        <v>242</v>
-      </c>
-      <c r="C113" t="s">
-        <v>243</v>
       </c>
       <c r="D113" t="str">
         <f t="shared" si="13"/>
@@ -12593,7 +12593,7 @@
         <v>PAGOH</v>
       </c>
       <c r="F113" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G113" t="str">
         <f t="shared" si="14"/>
@@ -12614,13 +12614,13 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>398</v>
+      </c>
+      <c r="B114" t="s">
+        <v>398</v>
+      </c>
+      <c r="C114" t="s">
         <v>399</v>
-      </c>
-      <c r="B114" t="s">
-        <v>399</v>
-      </c>
-      <c r="C114" t="s">
-        <v>400</v>
       </c>
       <c r="D114" t="str">
         <f t="shared" si="13"/>
@@ -12631,7 +12631,7 @@
         <v>PENARIK</v>
       </c>
       <c r="F114" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G114" t="str">
         <f t="shared" si="14"/>
@@ -12652,13 +12652,13 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>400</v>
+      </c>
+      <c r="B115" t="s">
+        <v>400</v>
+      </c>
+      <c r="C115" t="s">
         <v>401</v>
-      </c>
-      <c r="B115" t="s">
-        <v>401</v>
-      </c>
-      <c r="C115" t="s">
-        <v>402</v>
       </c>
       <c r="D115" t="str">
         <f t="shared" si="13"/>
@@ -12669,7 +12669,7 @@
         <v>BANDAR_PERMAISURI</v>
       </c>
       <c r="F115" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G115" t="str">
         <f t="shared" si="14"/>
@@ -12690,13 +12690,13 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>402</v>
+      </c>
+      <c r="B116" t="s">
+        <v>402</v>
+      </c>
+      <c r="C116" t="s">
         <v>403</v>
-      </c>
-      <c r="B116" t="s">
-        <v>403</v>
-      </c>
-      <c r="C116" t="s">
-        <v>404</v>
       </c>
       <c r="D116" t="str">
         <f t="shared" si="13"/>
@@ -12707,7 +12707,7 @@
         <v>KG_MERANG</v>
       </c>
       <c r="F116" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G116" t="str">
         <f t="shared" si="14"/>
@@ -12728,13 +12728,13 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>404</v>
+      </c>
+      <c r="B117" t="s">
+        <v>404</v>
+      </c>
+      <c r="C117" t="s">
         <v>405</v>
-      </c>
-      <c r="B117" t="s">
-        <v>405</v>
-      </c>
-      <c r="C117" t="s">
-        <v>406</v>
       </c>
       <c r="D117" t="str">
         <f t="shared" si="13"/>
@@ -12745,7 +12745,7 @@
         <v>BATU_RAKIT</v>
       </c>
       <c r="F117" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G117" t="str">
         <f t="shared" si="14"/>
@@ -12766,13 +12766,13 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>406</v>
+      </c>
+      <c r="B118" t="s">
+        <v>406</v>
+      </c>
+      <c r="C118" t="s">
         <v>407</v>
-      </c>
-      <c r="B118" t="s">
-        <v>407</v>
-      </c>
-      <c r="C118" t="s">
-        <v>408</v>
       </c>
       <c r="D118" t="str">
         <f t="shared" si="13"/>
@@ -12783,7 +12783,7 @@
         <v>KG_CHENERING</v>
       </c>
       <c r="F118" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G118" t="str">
         <f t="shared" si="14"/>
@@ -12804,13 +12804,13 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>408</v>
+      </c>
+      <c r="B119" t="s">
+        <v>408</v>
+      </c>
+      <c r="C119" t="s">
         <v>409</v>
-      </c>
-      <c r="B119" t="s">
-        <v>409</v>
-      </c>
-      <c r="C119" t="s">
-        <v>410</v>
       </c>
       <c r="D119" t="str">
         <f t="shared" si="13"/>
@@ -12821,7 +12821,7 @@
         <v>MARANG</v>
       </c>
       <c r="F119" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G119" t="str">
         <f t="shared" si="14"/>
@@ -12842,13 +12842,13 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>410</v>
+      </c>
+      <c r="B120" t="s">
+        <v>410</v>
+      </c>
+      <c r="C120" t="s">
         <v>411</v>
-      </c>
-      <c r="B120" t="s">
-        <v>411</v>
-      </c>
-      <c r="C120" t="s">
-        <v>412</v>
       </c>
       <c r="D120" t="str">
         <f t="shared" si="13"/>
@@ -12859,7 +12859,7 @@
         <v>KUALA_BERANG</v>
       </c>
       <c r="F120" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G120" t="str">
         <f t="shared" si="14"/>
@@ -12880,13 +12880,13 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>412</v>
+      </c>
+      <c r="B121" t="s">
+        <v>412</v>
+      </c>
+      <c r="C121" t="s">
         <v>413</v>
-      </c>
-      <c r="B121" t="s">
-        <v>413</v>
-      </c>
-      <c r="C121" t="s">
-        <v>414</v>
       </c>
       <c r="D121" t="str">
         <f t="shared" si="13"/>
@@ -12897,7 +12897,7 @@
         <v>TASIK_KENYIR</v>
       </c>
       <c r="F121" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G121" t="str">
         <f t="shared" si="14"/>
@@ -12918,13 +12918,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>414</v>
+      </c>
+      <c r="B122" t="s">
+        <v>414</v>
+      </c>
+      <c r="C122" t="s">
         <v>415</v>
-      </c>
-      <c r="B122" t="s">
-        <v>415</v>
-      </c>
-      <c r="C122" t="s">
-        <v>416</v>
       </c>
       <c r="D122" t="str">
         <f t="shared" si="13"/>
@@ -12935,7 +12935,7 @@
         <v>PENERAK</v>
       </c>
       <c r="F122" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G122" t="str">
         <f t="shared" si="14"/>
@@ -12956,13 +12956,13 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B123" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C123" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D123" t="str">
         <f t="shared" si="13"/>
@@ -12973,7 +12973,7 @@
         <v>NENASI</v>
       </c>
       <c r="F123" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G123" t="str">
         <f t="shared" si="14"/>
@@ -12994,13 +12994,13 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B124" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C124" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D124" t="str">
         <f t="shared" si="13"/>
@@ -13011,7 +13011,7 @@
         <v>PEKAN</v>
       </c>
       <c r="F124" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G124" t="str">
         <f t="shared" si="14"/>
@@ -13032,13 +13032,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B125" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C125" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D125" t="str">
         <f t="shared" si="13"/>
@@ -13049,7 +13049,7 @@
         <v>KUANTAN_TOWN</v>
       </c>
       <c r="F125" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G125" t="str">
         <f t="shared" si="14"/>
@@ -13070,13 +13070,13 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B126" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C126" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D126" t="str">
         <f t="shared" si="13"/>
@@ -13087,7 +13087,7 @@
         <v>TJ_GELANG</v>
       </c>
       <c r="F126" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G126" t="str">
         <f t="shared" si="14"/>
@@ -13108,13 +13108,13 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B127" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C127" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D127" t="str">
         <f t="shared" si="13"/>
@@ -13125,7 +13125,7 @@
         <v>CHUKAI</v>
       </c>
       <c r="F127" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G127" t="str">
         <f t="shared" si="14"/>
@@ -13146,13 +13146,13 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B128" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C128" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D128" t="str">
         <f t="shared" si="13"/>
@@ -13163,7 +13163,7 @@
         <v>MARAN</v>
       </c>
       <c r="F128" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G128" t="str">
         <f t="shared" si="14"/>
@@ -13184,13 +13184,13 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B129" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C129" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D129" t="str">
         <f t="shared" si="13"/>
@@ -13201,7 +13201,7 @@
         <v>GAMBANG</v>
       </c>
       <c r="F129" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G129" t="str">
         <f t="shared" si="14"/>
@@ -13222,13 +13222,13 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B130" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C130" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D130" t="str">
         <f t="shared" si="13"/>
@@ -13239,7 +13239,7 @@
         <v>LEPAR</v>
       </c>
       <c r="F130" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G130" t="str">
         <f t="shared" ref="G130:G161" si="17">B130</f>
@@ -13260,13 +13260,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B131" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C131" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D131" t="str">
         <f t="shared" si="13"/>
@@ -13277,7 +13277,7 @@
         <v>MUADZAM</v>
       </c>
       <c r="F131" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G131" t="str">
         <f t="shared" si="17"/>
@@ -13298,13 +13298,13 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B132" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C132" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D132" t="str">
         <f t="shared" si="13"/>
@@ -13315,7 +13315,7 @@
         <v>SG_LEMBING</v>
       </c>
       <c r="F132" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G132" t="str">
         <f t="shared" si="17"/>
@@ -13336,13 +13336,13 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>466</v>
+      </c>
+      <c r="B133" t="s">
+        <v>466</v>
+      </c>
+      <c r="C133" t="s">
         <v>467</v>
-      </c>
-      <c r="B133" t="s">
-        <v>467</v>
-      </c>
-      <c r="C133" t="s">
-        <v>468</v>
       </c>
       <c r="D133" t="str">
         <f t="shared" si="13"/>
@@ -13353,7 +13353,7 @@
         <v>LUNDU</v>
       </c>
       <c r="F133" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G133" t="str">
         <f t="shared" si="17"/>
@@ -13374,13 +13374,13 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>468</v>
+      </c>
+      <c r="B134" t="s">
+        <v>468</v>
+      </c>
+      <c r="C134" t="s">
         <v>469</v>
-      </c>
-      <c r="B134" t="s">
-        <v>469</v>
-      </c>
-      <c r="C134" t="s">
-        <v>470</v>
       </c>
       <c r="D134" t="str">
         <f t="shared" si="13"/>
@@ -13391,7 +13391,7 @@
         <v>KG_RAMBUNGAN</v>
       </c>
       <c r="F134" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G134" t="str">
         <f t="shared" si="17"/>
@@ -13412,13 +13412,13 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>470</v>
+      </c>
+      <c r="B135" t="s">
+        <v>470</v>
+      </c>
+      <c r="C135" t="s">
         <v>471</v>
-      </c>
-      <c r="B135" t="s">
-        <v>471</v>
-      </c>
-      <c r="C135" t="s">
-        <v>472</v>
       </c>
       <c r="D135" t="str">
         <f t="shared" si="13"/>
@@ -13429,7 +13429,7 @@
         <v>KG_STINGGANG</v>
       </c>
       <c r="F135" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G135" t="str">
         <f t="shared" si="17"/>
@@ -13450,13 +13450,13 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>472</v>
+      </c>
+      <c r="B136" t="s">
+        <v>472</v>
+      </c>
+      <c r="C136" t="s">
         <v>473</v>
-      </c>
-      <c r="B136" t="s">
-        <v>473</v>
-      </c>
-      <c r="C136" t="s">
-        <v>474</v>
       </c>
       <c r="D136" t="str">
         <f t="shared" si="13"/>
@@ -13467,7 +13467,7 @@
         <v>MUARA_TEBAS</v>
       </c>
       <c r="F136" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G136" t="str">
         <f t="shared" si="17"/>
@@ -13488,13 +13488,13 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B137" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C137" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D137" t="str">
         <f t="shared" si="13"/>
@@ -13505,7 +13505,7 @@
         <v>ABM_SEMERA</v>
       </c>
       <c r="F137" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G137" t="str">
         <f t="shared" si="17"/>
@@ -13526,13 +13526,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>475</v>
+      </c>
+      <c r="B138" t="s">
+        <v>475</v>
+      </c>
+      <c r="C138" t="s">
         <v>476</v>
-      </c>
-      <c r="B138" t="s">
-        <v>476</v>
-      </c>
-      <c r="C138" t="s">
-        <v>477</v>
       </c>
       <c r="D138" t="str">
         <f t="shared" si="13"/>
@@ -13543,7 +13543,7 @@
         <v>TEBEDU</v>
       </c>
       <c r="F138" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G138" t="str">
         <f t="shared" si="17"/>
@@ -13564,13 +13564,13 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>477</v>
+      </c>
+      <c r="B139" t="s">
+        <v>477</v>
+      </c>
+      <c r="C139" t="s">
         <v>478</v>
-      </c>
-      <c r="B139" t="s">
-        <v>478</v>
-      </c>
-      <c r="C139" t="s">
-        <v>479</v>
       </c>
       <c r="D139" t="str">
         <f t="shared" si="13"/>
@@ -13581,7 +13581,7 @@
         <v>SERIAN</v>
       </c>
       <c r="F139" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G139" t="str">
         <f t="shared" si="17"/>
@@ -13602,13 +13602,13 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>479</v>
+      </c>
+      <c r="B140" t="s">
+        <v>479</v>
+      </c>
+      <c r="C140" t="s">
         <v>480</v>
-      </c>
-      <c r="B140" t="s">
-        <v>480</v>
-      </c>
-      <c r="C140" t="s">
-        <v>481</v>
       </c>
       <c r="D140" t="str">
         <f t="shared" si="13"/>
@@ -13619,7 +13619,7 @@
         <v>SIMUNJAN</v>
       </c>
       <c r="F140" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G140" t="str">
         <f t="shared" si="17"/>
@@ -13640,13 +13640,13 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>481</v>
+      </c>
+      <c r="B141" t="s">
+        <v>481</v>
+      </c>
+      <c r="C141" t="s">
         <v>482</v>
-      </c>
-      <c r="B141" t="s">
-        <v>482</v>
-      </c>
-      <c r="C141" t="s">
-        <v>483</v>
       </c>
       <c r="D141" t="str">
         <f t="shared" si="13"/>
@@ -13657,7 +13657,7 @@
         <v>KG_TRISO</v>
       </c>
       <c r="F141" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G141" t="str">
         <f t="shared" si="17"/>
@@ -13678,13 +13678,13 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>491</v>
+      </c>
+      <c r="B142" t="s">
+        <v>491</v>
+      </c>
+      <c r="C142" t="s">
         <v>492</v>
-      </c>
-      <c r="B142" t="s">
-        <v>492</v>
-      </c>
-      <c r="C142" t="s">
-        <v>493</v>
       </c>
       <c r="D142" t="str">
         <f t="shared" si="13"/>
@@ -13695,7 +13695,7 @@
         <v>KG_KUAP</v>
       </c>
       <c r="F142" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G142" t="str">
         <f t="shared" si="17"/>
@@ -13716,13 +13716,13 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>493</v>
+      </c>
+      <c r="B143" t="s">
+        <v>493</v>
+      </c>
+      <c r="C143" t="s">
         <v>494</v>
-      </c>
-      <c r="B143" t="s">
-        <v>494</v>
-      </c>
-      <c r="C143" t="s">
-        <v>495</v>
       </c>
       <c r="D143" t="str">
         <f t="shared" si="13"/>
@@ -13733,7 +13733,7 @@
         <v>BT_SIOL</v>
       </c>
       <c r="F143" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G143" t="str">
         <f t="shared" si="17"/>
@@ -13754,13 +13754,13 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B144" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C144" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D144" t="str">
         <f t="shared" si="13"/>
@@ -13771,7 +13771,7 @@
         <v>ABM_NARUB</v>
       </c>
       <c r="F144" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G144" t="str">
         <f t="shared" si="17"/>
@@ -13792,13 +13792,13 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>498</v>
+      </c>
+      <c r="B145" t="s">
+        <v>498</v>
+      </c>
+      <c r="C145" t="s">
         <v>499</v>
-      </c>
-      <c r="B145" t="s">
-        <v>499</v>
-      </c>
-      <c r="C145" t="s">
-        <v>500</v>
       </c>
       <c r="D145" t="str">
         <f t="shared" si="13"/>
@@ -13809,7 +13809,7 @@
         <v>NANGA_TAMIN</v>
       </c>
       <c r="F145" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G145" t="str">
         <f t="shared" si="17"/>
@@ -13830,13 +13830,13 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>500</v>
+      </c>
+      <c r="B146" t="s">
+        <v>500</v>
+      </c>
+      <c r="C146" t="s">
         <v>501</v>
-      </c>
-      <c r="B146" t="s">
-        <v>501</v>
-      </c>
-      <c r="C146" t="s">
-        <v>502</v>
       </c>
       <c r="D146" t="str">
         <f t="shared" si="13"/>
@@ -13847,7 +13847,7 @@
         <v>LASSA_RIVER</v>
       </c>
       <c r="F146" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G146" t="str">
         <f t="shared" si="17"/>
@@ -13868,13 +13868,13 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B147" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C147" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D147" t="str">
         <f t="shared" si="13"/>
@@ -13885,7 +13885,7 @@
         <v>SELANGAU</v>
       </c>
       <c r="F147" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G147" t="str">
         <f t="shared" si="17"/>
@@ -13906,13 +13906,13 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>503</v>
+      </c>
+      <c r="B148" t="s">
+        <v>503</v>
+      </c>
+      <c r="C148" t="s">
         <v>504</v>
-      </c>
-      <c r="B148" t="s">
-        <v>504</v>
-      </c>
-      <c r="C148" t="s">
-        <v>505</v>
       </c>
       <c r="D148" t="str">
         <f t="shared" si="13"/>
@@ -13923,7 +13923,7 @@
         <v>STAPANG</v>
       </c>
       <c r="F148" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G148" t="str">
         <f t="shared" si="17"/>
@@ -13944,13 +13944,13 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>505</v>
+      </c>
+      <c r="B149" t="s">
+        <v>505</v>
+      </c>
+      <c r="C149" t="s">
         <v>506</v>
-      </c>
-      <c r="B149" t="s">
-        <v>506</v>
-      </c>
-      <c r="C149" t="s">
-        <v>507</v>
       </c>
       <c r="D149" t="str">
         <f t="shared" si="13"/>
@@ -13961,7 +13961,7 @@
         <v>T_RIVER_JUNCTION</v>
       </c>
       <c r="F149" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G149" t="str">
         <f t="shared" si="17"/>
@@ -13982,13 +13982,13 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>508</v>
+      </c>
+      <c r="B150" t="s">
+        <v>508</v>
+      </c>
+      <c r="C150" t="s">
         <v>509</v>
-      </c>
-      <c r="B150" t="s">
-        <v>509</v>
-      </c>
-      <c r="C150" t="s">
-        <v>510</v>
       </c>
       <c r="D150" t="str">
         <f t="shared" si="13"/>
@@ -13999,7 +13999,7 @@
         <v>P_DUDONG</v>
       </c>
       <c r="F150" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G150" t="str">
         <f t="shared" si="17"/>
@@ -14020,13 +14020,13 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>510</v>
+      </c>
+      <c r="B151" t="s">
+        <v>510</v>
+      </c>
+      <c r="C151" t="s">
         <v>511</v>
-      </c>
-      <c r="B151" t="s">
-        <v>511</v>
-      </c>
-      <c r="C151" t="s">
-        <v>512</v>
       </c>
       <c r="D151" t="str">
         <f t="shared" si="13"/>
@@ -14037,7 +14037,7 @@
         <v>MERUAN</v>
       </c>
       <c r="F151" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G151" t="str">
         <f t="shared" si="17"/>
@@ -14058,13 +14058,13 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>512</v>
+      </c>
+      <c r="B152" t="s">
+        <v>512</v>
+      </c>
+      <c r="C152" t="s">
         <v>513</v>
-      </c>
-      <c r="B152" t="s">
-        <v>513</v>
-      </c>
-      <c r="C152" t="s">
-        <v>514</v>
       </c>
       <c r="D152" t="str">
         <f t="shared" si="13"/>
@@ -14075,7 +14075,7 @@
         <v>LENG</v>
       </c>
       <c r="F152" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G152" t="str">
         <f t="shared" si="17"/>
@@ -14096,13 +14096,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>514</v>
+      </c>
+      <c r="B153" t="s">
+        <v>514</v>
+      </c>
+      <c r="C153" t="s">
         <v>515</v>
-      </c>
-      <c r="B153" t="s">
-        <v>515</v>
-      </c>
-      <c r="C153" t="s">
-        <v>516</v>
       </c>
       <c r="D153" t="str">
         <f t="shared" si="13"/>
@@ -14113,7 +14113,7 @@
         <v>PAKAN_ROAD</v>
       </c>
       <c r="F153" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G153" t="str">
         <f t="shared" si="17"/>
@@ -14134,13 +14134,13 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>516</v>
+      </c>
+      <c r="B154" t="s">
+        <v>516</v>
+      </c>
+      <c r="C154" t="s">
         <v>517</v>
-      </c>
-      <c r="B154" t="s">
-        <v>517</v>
-      </c>
-      <c r="C154" t="s">
-        <v>518</v>
       </c>
       <c r="D154" t="str">
         <f t="shared" si="13"/>
@@ -14151,7 +14151,7 @@
         <v>DURIN_TOWN</v>
       </c>
       <c r="F154" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G154" t="str">
         <f t="shared" si="17"/>
@@ -14172,13 +14172,13 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>518</v>
+      </c>
+      <c r="B155" t="s">
+        <v>518</v>
+      </c>
+      <c r="C155" t="s">
         <v>519</v>
-      </c>
-      <c r="B155" t="s">
-        <v>519</v>
-      </c>
-      <c r="C155" t="s">
-        <v>520</v>
       </c>
       <c r="D155" t="str">
         <f t="shared" si="13"/>
@@ -14189,7 +14189,7 @@
         <v>KANOWIT</v>
       </c>
       <c r="F155" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G155" t="str">
         <f t="shared" si="17"/>
@@ -14210,13 +14210,13 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B156" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C156" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D156" t="str">
         <f t="shared" si="13"/>
@@ -14227,7 +14227,7 @@
         <v>PENARIK</v>
       </c>
       <c r="F156" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G156" t="str">
         <f t="shared" si="17"/>
@@ -14248,13 +14248,13 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>521</v>
+      </c>
+      <c r="B157" t="s">
+        <v>521</v>
+      </c>
+      <c r="C157" t="s">
         <v>522</v>
-      </c>
-      <c r="B157" t="s">
-        <v>522</v>
-      </c>
-      <c r="C157" t="s">
-        <v>523</v>
       </c>
       <c r="D157" t="str">
         <f t="shared" ref="D157:D184" si="23">SUBSTITUTE(UPPER(A157), " ", "_")</f>
@@ -14265,7 +14265,7 @@
         <v>KG_SETIU_LAMA</v>
       </c>
       <c r="F157" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G157" t="str">
         <f t="shared" si="17"/>
@@ -14286,13 +14286,13 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>523</v>
+      </c>
+      <c r="B158" t="s">
+        <v>523</v>
+      </c>
+      <c r="C158" t="s">
         <v>524</v>
-      </c>
-      <c r="B158" t="s">
-        <v>524</v>
-      </c>
-      <c r="C158" t="s">
-        <v>525</v>
       </c>
       <c r="D158" t="str">
         <f t="shared" si="23"/>
@@ -14303,7 +14303,7 @@
         <v>BETING_LINTANG</v>
       </c>
       <c r="F158" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G158" t="str">
         <f t="shared" si="17"/>
@@ -14324,13 +14324,13 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B159" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C159" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D159" t="str">
         <f t="shared" si="23"/>
@@ -14341,7 +14341,7 @@
         <v>P_RU</v>
       </c>
       <c r="F159" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G159" t="str">
         <f t="shared" si="17"/>
@@ -14362,13 +14362,13 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>527</v>
+      </c>
+      <c r="B160" t="s">
+        <v>527</v>
+      </c>
+      <c r="C160" t="s">
         <v>528</v>
-      </c>
-      <c r="B160" t="s">
-        <v>528</v>
-      </c>
-      <c r="C160" t="s">
-        <v>529</v>
       </c>
       <c r="D160" t="str">
         <f t="shared" si="23"/>
@@ -14379,7 +14379,7 @@
         <v>KG_BESUT</v>
       </c>
       <c r="F160" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G160" t="str">
         <f t="shared" si="17"/>
@@ -14400,13 +14400,13 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>529</v>
+      </c>
+      <c r="B161" t="s">
+        <v>529</v>
+      </c>
+      <c r="C161" t="s">
         <v>530</v>
-      </c>
-      <c r="B161" t="s">
-        <v>530</v>
-      </c>
-      <c r="C161" t="s">
-        <v>531</v>
       </c>
       <c r="D161" t="str">
         <f t="shared" si="23"/>
@@ -14417,7 +14417,7 @@
         <v>KG_TOK_BALI</v>
       </c>
       <c r="F161" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G161" t="str">
         <f t="shared" si="17"/>
@@ -14438,13 +14438,13 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>531</v>
+      </c>
+      <c r="B162" t="s">
+        <v>531</v>
+      </c>
+      <c r="C162" t="s">
         <v>532</v>
-      </c>
-      <c r="B162" t="s">
-        <v>532</v>
-      </c>
-      <c r="C162" t="s">
-        <v>533</v>
       </c>
       <c r="D162" t="str">
         <f t="shared" si="23"/>
@@ -14455,7 +14455,7 @@
         <v>KG_KANDIS</v>
       </c>
       <c r="F162" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G162" t="str">
         <f t="shared" ref="G162:G168" si="24">B162</f>
@@ -14476,13 +14476,13 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>533</v>
+      </c>
+      <c r="B163" t="s">
+        <v>533</v>
+      </c>
+      <c r="C163" t="s">
         <v>534</v>
-      </c>
-      <c r="B163" t="s">
-        <v>534</v>
-      </c>
-      <c r="C163" t="s">
-        <v>535</v>
       </c>
       <c r="D163" t="str">
         <f t="shared" si="23"/>
@@ -14493,7 +14493,7 @@
         <v>BACHOK</v>
       </c>
       <c r="F163" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G163" t="str">
         <f t="shared" si="24"/>
@@ -14514,13 +14514,13 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>535</v>
+      </c>
+      <c r="B164" t="s">
+        <v>535</v>
+      </c>
+      <c r="C164" t="s">
         <v>536</v>
-      </c>
-      <c r="B164" t="s">
-        <v>536</v>
-      </c>
-      <c r="C164" t="s">
-        <v>537</v>
       </c>
       <c r="D164" t="str">
         <f t="shared" si="23"/>
@@ -14531,7 +14531,7 @@
         <v>KOTA_BHARU_TOWN</v>
       </c>
       <c r="F164" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G164" t="str">
         <f t="shared" si="24"/>
@@ -14552,13 +14552,13 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>537</v>
+      </c>
+      <c r="B165" t="s">
+        <v>537</v>
+      </c>
+      <c r="C165" t="s">
         <v>538</v>
-      </c>
-      <c r="B165" t="s">
-        <v>538</v>
-      </c>
-      <c r="C165" t="s">
-        <v>539</v>
       </c>
       <c r="D165" t="str">
         <f t="shared" si="23"/>
@@ -14569,7 +14569,7 @@
         <v>KUALA_KRAI</v>
       </c>
       <c r="F165" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G165" t="str">
         <f t="shared" si="24"/>
@@ -14590,13 +14590,13 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>539</v>
+      </c>
+      <c r="B166" t="s">
+        <v>539</v>
+      </c>
+      <c r="C166" t="s">
         <v>540</v>
-      </c>
-      <c r="B166" t="s">
-        <v>540</v>
-      </c>
-      <c r="C166" t="s">
-        <v>541</v>
       </c>
       <c r="D166" t="str">
         <f t="shared" si="23"/>
@@ -14607,7 +14607,7 @@
         <v>TANAH_MERAH</v>
       </c>
       <c r="F166" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G166" t="str">
         <f t="shared" si="24"/>
@@ -14628,13 +14628,13 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>541</v>
+      </c>
+      <c r="B167" t="s">
+        <v>541</v>
+      </c>
+      <c r="C167" t="s">
         <v>542</v>
-      </c>
-      <c r="B167" t="s">
-        <v>542</v>
-      </c>
-      <c r="C167" t="s">
-        <v>543</v>
       </c>
       <c r="D167" t="str">
         <f t="shared" si="23"/>
@@ -14645,7 +14645,7 @@
         <v>BT_MELINTANG</v>
       </c>
       <c r="F167" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G167" t="str">
         <f t="shared" si="24"/>
@@ -14666,13 +14666,13 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>543</v>
+      </c>
+      <c r="B168" t="s">
+        <v>543</v>
+      </c>
+      <c r="C168" t="s">
         <v>544</v>
-      </c>
-      <c r="B168" t="s">
-        <v>544</v>
-      </c>
-      <c r="C168" t="s">
-        <v>545</v>
       </c>
       <c r="D168" t="str">
         <f t="shared" si="23"/>
@@ -14683,7 +14683,7 @@
         <v>JELI</v>
       </c>
       <c r="F168" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G168" t="str">
         <f t="shared" si="24"/>
@@ -14704,13 +14704,13 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B169" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C169" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D169" t="str">
         <f t="shared" si="23"/>
@@ -14721,7 +14721,7 @@
         <v>KUAH</v>
       </c>
       <c r="F169" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G169" t="str">
         <f t="shared" ref="G169:G177" si="27">B169</f>
@@ -14740,13 +14740,13 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B170" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C170" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D170" t="str">
         <f t="shared" si="23"/>
@@ -14757,7 +14757,7 @@
         <v>P_TIMUN</v>
       </c>
       <c r="F170" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G170" t="str">
         <f t="shared" si="27"/>
@@ -14778,13 +14778,13 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B171" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C171" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D171" t="str">
         <f t="shared" si="23"/>
@@ -14795,7 +14795,7 @@
         <v>ABM_P_TUBA</v>
       </c>
       <c r="F171" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G171" t="str">
         <f t="shared" si="27"/>
@@ -14816,13 +14816,13 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B172" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C172" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D172" t="str">
         <f t="shared" si="23"/>
@@ -14833,7 +14833,7 @@
         <v>P_PAYA</v>
       </c>
       <c r="F172" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G172" t="str">
         <f t="shared" si="27"/>
@@ -14852,13 +14852,13 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B173" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C173" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D173" t="str">
         <f t="shared" si="23"/>
@@ -14869,7 +14869,7 @@
         <v>KUALA_PERLIS</v>
       </c>
       <c r="F173" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G173" t="str">
         <f t="shared" si="27"/>
@@ -14890,13 +14890,13 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B174" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C174" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D174" t="str">
         <f t="shared" si="23"/>
@@ -14907,7 +14907,7 @@
         <v>AYER_HITAM</v>
       </c>
       <c r="F174" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G174" t="str">
         <f t="shared" si="27"/>
@@ -14928,13 +14928,13 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B175" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C175" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D175" t="str">
         <f t="shared" si="23"/>
@@ -14945,7 +14945,7 @@
         <v>KUALA_KEDAH</v>
       </c>
       <c r="F175" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G175" t="str">
         <f t="shared" si="27"/>
@@ -14964,13 +14964,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B176" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C176" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D176" t="str">
         <f t="shared" si="23"/>
@@ -14981,7 +14981,7 @@
         <v>SIMPANG_EMPAT</v>
       </c>
       <c r="F176" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G176" t="str">
         <f t="shared" si="27"/>
@@ -15002,13 +15002,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B177" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C177" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D177" t="str">
         <f t="shared" si="23"/>
@@ -15019,7 +15019,7 @@
         <v>KOTA_SARANG_SEMUT</v>
       </c>
       <c r="F177" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G177" t="str">
         <f t="shared" si="27"/>
@@ -15040,13 +15040,13 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B178" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C178" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D178" t="str">
         <f t="shared" si="23"/>
@@ -15057,7 +15057,7 @@
         <v>BATU_HAMPAR</v>
       </c>
       <c r="F178" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G178" t="str">
         <f t="shared" ref="G178:G184" si="31">B178</f>
@@ -15078,13 +15078,13 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B179" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C179" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D179" t="str">
         <f t="shared" si="23"/>
@@ -15095,7 +15095,7 @@
         <v>PARIT</v>
       </c>
       <c r="F179" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G179" t="str">
         <f t="shared" si="31"/>
@@ -15116,13 +15116,13 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B180" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C180" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D180" t="str">
         <f t="shared" si="23"/>
@@ -15133,7 +15133,7 @@
         <v>BATU_GAJAH</v>
       </c>
       <c r="F180" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G180" t="str">
         <f t="shared" si="31"/>
@@ -15154,13 +15154,13 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B181" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C181" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D181" t="str">
         <f t="shared" si="23"/>
@@ -15171,7 +15171,7 @@
         <v>GOPENG</v>
       </c>
       <c r="F181" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G181" t="str">
         <f t="shared" si="31"/>
@@ -15192,13 +15192,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B182" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C182" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D182" t="str">
         <f t="shared" si="23"/>
@@ -15209,7 +15209,7 @@
         <v>KAMPAR</v>
       </c>
       <c r="F182" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G182" t="str">
         <f t="shared" si="31"/>
@@ -15228,13 +15228,13 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B183" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C183" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D183" t="str">
         <f t="shared" si="23"/>
@@ -15245,7 +15245,7 @@
         <v>TELUK_INTAN</v>
       </c>
       <c r="F183" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G183" t="str">
         <f t="shared" si="31"/>
@@ -15264,13 +15264,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B184" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C184" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D184" t="str">
         <f t="shared" si="23"/>
@@ -15281,7 +15281,7 @@
         <v>BIDOR</v>
       </c>
       <c r="F184" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G184" t="str">
         <f t="shared" si="31"/>
@@ -15317,98 +15317,98 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" t="s">
         <v>246</v>
-      </c>
-      <c r="B1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" t="s">
         <v>249</v>
-      </c>
-      <c r="B3" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" t="s">
         <v>271</v>
-      </c>
-      <c r="B4" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" t="s">
         <v>251</v>
-      </c>
-      <c r="B5" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" t="s">
         <v>258</v>
-      </c>
-      <c r="B6" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7" t="s">
         <v>260</v>
-      </c>
-      <c r="B7" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" t="s">
         <v>262</v>
-      </c>
-      <c r="B8" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" t="s">
         <v>264</v>
-      </c>
-      <c r="B9" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" t="s">
         <v>576</v>
-      </c>
-      <c r="B10" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>316</v>
+      </c>
+      <c r="B11" t="s">
         <v>317</v>
-      </c>
-      <c r="B11" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>265</v>
+      </c>
+      <c r="B12" t="s">
         <v>266</v>
-      </c>
-      <c r="B12" t="s">
-        <v>267</v>
       </c>
     </row>
   </sheetData>
